--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 00:40:43</t>
+          <t>2026-05-30 03:07:22</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 00:40:43</t>
+          <t>2026-05-30 03:07:22</t>
         </is>
       </c>
     </row>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
         <v>2.16</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 00:40:43</t>
+          <t>2026-05-30 03:07:22</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 00:40:43</t>
+          <t>2026-05-30 03:07:22</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 00:40:43</t>
+          <t>2026-05-30 03:07:22</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
         <v>2.56</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 00:40:43</t>
+          <t>2026-05-30 03:07:22</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
         <v>2.84</v>
@@ -2405,34 +2405,34 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>1.02</v>
+        <v>5.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
@@ -2447,7 +2447,7 @@
         <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC8" t="n">
         <v>8.6</v>
@@ -2471,79 +2471,79 @@
         <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL8" t="n">
         <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN8" t="n">
         <v>42</v>
       </c>
       <c r="AO8" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.85</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.94</v>
+        <v>5.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.75</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG8" t="n">
         <v>4.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI8" t="n">
         <v>2.24</v>
@@ -2561,7 +2561,7 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO8" t="n">
         <v>1.01</v>
@@ -2582,7 +2582,7 @@
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 00:40:43</t>
+          <t>2026-05-30 03:07:22</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2668,19 +2668,19 @@
         <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
         <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
         <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V9" t="n">
         <v>1.14</v>
@@ -2689,7 +2689,7 @@
         <v>2.62</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y9" t="n">
         <v>25</v>
@@ -2788,16 +2788,16 @@
         <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
         <v>7.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI9" t="n">
         <v>2.84</v>
@@ -2806,59 +2806,59 @@
         <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP9" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR9" t="n">
         <v>28</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT9" t="n">
         <v>10.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>21</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 00:40:43</t>
+          <t>2026-05-30 03:07:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>2.84</v>
@@ -2414,7 +2414,7 @@
         <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
@@ -2432,7 +2432,7 @@
         <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 05:32:46</t>
+          <t>2026-05-30 07:57:43</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 05:32:46</t>
+          <t>2026-05-30 07:57:43</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 05:32:46</t>
+          <t>2026-05-30 07:57:43</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 05:32:46</t>
+          <t>2026-05-30 07:57:43</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 05:32:46</t>
+          <t>2026-05-30 07:57:43</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
         <v>2.54</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 05:32:46</t>
+          <t>2026-05-30 07:57:43</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
@@ -2393,7 +2393,7 @@
         <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K8" t="n">
         <v>3.35</v>
@@ -2408,7 +2408,7 @@
         <v>2.58</v>
       </c>
       <c r="O8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P8" t="n">
         <v>1.53</v>
@@ -2519,7 +2519,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 05:32:46</t>
+          <t>2026-05-30 07:57:43</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 05:32:46</t>
+          <t>2026-05-30 07:57:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 07:57:43</t>
+          <t>2026-05-30 10:22:09</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 07:57:43</t>
+          <t>2026-05-30 10:22:09</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G4" t="n">
         <v>4.2</v>
@@ -1380,7 +1380,7 @@
         <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q4" t="n">
         <v>2.16</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 07:57:43</t>
+          <t>2026-05-30 10:22:09</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 07:57:43</t>
+          <t>2026-05-30 10:22:09</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 07:57:43</t>
+          <t>2026-05-30 10:22:09</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 07:57:43</t>
+          <t>2026-05-30 10:22:09</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
@@ -2411,7 +2411,7 @@
         <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
         <v>2.56</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 07:57:43</t>
+          <t>2026-05-30 10:22:09</t>
         </is>
       </c>
     </row>
@@ -2662,19 +2662,19 @@
         <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R9" t="n">
         <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.02</v>
@@ -2701,10 +2701,10 @@
         <v>270</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9" t="n">
         <v>32</v>
@@ -2749,10 +2749,10 @@
         <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
@@ -2764,7 +2764,7 @@
         <v>20</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
         <v>7</v>
@@ -2776,7 +2776,7 @@
         <v>18.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB9" t="n">
         <v>11</v>
@@ -2785,16 +2785,16 @@
         <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.45</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 07:57:43</t>
+          <t>2026-05-30 10:22:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -1386,10 +1386,10 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
         <v>1.4</v>
@@ -1419,79 +1419,79 @@
         <v>1.32</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
         <v>1.03</v>
@@ -1500,7 +1500,7 @@
         <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.03</v>
@@ -1521,10 +1521,10 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
         <v>2.86</v>
@@ -2411,10 +2411,10 @@
         <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
@@ -2429,7 +2429,7 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
         <v>1.66</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -875,28 +875,28 @@
         <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1019,68 +1019,68 @@
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 12:44:29</t>
+          <t>2026-05-30 15:07:29</t>
         </is>
       </c>
     </row>
@@ -1129,28 +1129,28 @@
         <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1273,68 +1273,68 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 12:44:29</t>
+          <t>2026-05-30 15:07:29</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>3.4</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H4" t="n">
         <v>2.2</v>
@@ -1377,7 +1377,7 @@
         <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
         <v>3.65</v>
@@ -1404,7 +1404,7 @@
         <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1416,7 +1416,7 @@
         <v>1.66</v>
       </c>
       <c r="W4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
         <v>13</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 12:44:29</t>
+          <t>2026-05-30 15:07:29</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 12:44:29</t>
+          <t>2026-05-30 15:07:29</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 12:44:29</t>
+          <t>2026-05-30 15:07:29</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 12:44:29</t>
+          <t>2026-05-30 15:07:29</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
@@ -2411,10 +2411,10 @@
         <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 12:44:29</t>
+          <t>2026-05-30 15:07:29</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 12:44:29</t>
+          <t>2026-05-30 15:07:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -860,16 +860,16 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -890,13 +890,13 @@
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 15:07:29</t>
+          <t>2026-05-30 17:29:50</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,19 +1135,19 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.02</v>
       </c>
       <c r="P3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.07</v>
       </c>
       <c r="S3" t="n">
         <v>1.26</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 15:07:29</t>
+          <t>2026-05-30 17:29:50</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
         <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 15:07:29</t>
+          <t>2026-05-30 17:29:50</t>
         </is>
       </c>
     </row>
@@ -1622,31 +1622,31 @@
         <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
@@ -1655,184 +1655,184 @@
         <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 15:07:29</t>
+          <t>2026-05-30 17:29:50</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 15:07:29</t>
+          <t>2026-05-30 17:29:50</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 15:07:29</t>
+          <t>2026-05-30 17:29:50</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
@@ -2393,7 +2393,7 @@
         <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K8" t="n">
         <v>3.35</v>
@@ -2411,7 +2411,7 @@
         <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
         <v>2.56</v>
@@ -2432,7 +2432,7 @@
         <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 15:07:29</t>
+          <t>2026-05-30 17:29:50</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 15:07:29</t>
+          <t>2026-05-30 17:29:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -869,7 +869,7 @@
         <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 17:29:50</t>
+          <t>2026-05-30 19:51:16</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
         <v>1.02</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 17:29:50</t>
+          <t>2026-05-30 19:51:16</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 17:29:50</t>
+          <t>2026-05-30 19:51:16</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
@@ -1652,13 +1652,13 @@
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R5" t="n">
         <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 17:29:50</t>
+          <t>2026-05-30 19:51:16</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 17:29:50</t>
+          <t>2026-05-30 19:51:16</t>
         </is>
       </c>
     </row>
@@ -2145,212 +2145,212 @@
         <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P7" t="n">
         <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 17:29:50</t>
+          <t>2026-05-30 19:51:16</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
@@ -2429,10 +2429,10 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 17:29:50</t>
+          <t>2026-05-30 19:51:16</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 17:29:50</t>
+          <t>2026-05-30 19:51:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -869,7 +869,7 @@
         <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 19:51:16</t>
+          <t>2026-05-30 22:11:03</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 19:51:16</t>
+          <t>2026-05-30 22:11:03</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>3.4</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>2.2</v>
@@ -1383,13 +1383,13 @@
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>1.4</v>
@@ -1401,19 +1401,19 @@
         <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W4" t="n">
         <v>1.33</v>
@@ -1527,68 +1527,68 @@
         <v>19</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 19:51:16</t>
+          <t>2026-05-30 22:11:03</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 19:51:16</t>
+          <t>2026-05-30 22:11:03</t>
         </is>
       </c>
     </row>
@@ -1876,55 +1876,55 @@
         <v>2.8</v>
       </c>
       <c r="G6" t="n">
-        <v>160</v>
+        <v>3.15</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="n">
-        <v>110</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.54</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="O6" t="n">
         <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X6" t="n">
         <v>9.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 19:51:16</t>
+          <t>2026-05-30 22:11:03</t>
         </is>
       </c>
     </row>
@@ -2145,10 +2145,10 @@
         <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
         <v>2.58</v>
@@ -2157,22 +2157,22 @@
         <v>1.52</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
         <v>1.59</v>
@@ -2181,176 +2181,176 @@
         <v>1.36</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD7" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>10</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>22</v>
-      </c>
       <c r="BN7" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS7" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BW7" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 19:51:16</t>
+          <t>2026-05-30 22:11:03</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G8" t="n">
         <v>2.24</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.58</v>
-      </c>
       <c r="H8" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
         <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH8" t="n">
         <v>32</v>
       </c>
-      <c r="AA8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>28</v>
-      </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AN8" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AO8" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>3.95</v>
       </c>
       <c r="AS8" t="n">
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
         <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>19.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>19.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
         <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>19.5</v>
       </c>
       <c r="BG8" t="n">
         <v>4.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 19:51:16</t>
+          <t>2026-05-30 22:11:03</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 19:51:16</t>
+          <t>2026-05-30 22:11:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 22:11:03</t>
+          <t>2026-05-31 00:30:23</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 22:11:03</t>
+          <t>2026-05-31 00:30:23</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>3.4</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H4" t="n">
         <v>2.2</v>
@@ -1404,7 +1404,7 @@
         <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
         <v>1.86</v>
@@ -1530,7 +1530,7 @@
         <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 22:11:03</t>
+          <t>2026-05-31 00:30:23</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 22:11:03</t>
+          <t>2026-05-31 00:30:23</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H6" t="n">
         <v>2.82</v>
@@ -1891,28 +1891,28 @@
         <v>3.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P6" t="n">
         <v>1.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="R6" t="n">
         <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T6" t="n">
         <v>2.06</v>
@@ -1924,179 +1924,179 @@
         <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="X6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
         <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
         <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.43</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.42</v>
+        <v>7.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.69</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.64</v>
+        <v>5.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.42</v>
+        <v>7.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.69</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.69</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.69</v>
+        <v>5.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.55</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.69</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.69</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.69</v>
+        <v>5.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.64</v>
+        <v>5.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.69</v>
+        <v>5.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.69</v>
+        <v>5.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.69</v>
+        <v>5.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.69</v>
+        <v>5.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.69</v>
+        <v>5.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 22:11:03</t>
+          <t>2026-05-31 00:30:23</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
         <v>5.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BV7" t="n">
         <v>23</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 22:11:03</t>
+          <t>2026-05-31 00:30:23</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
         <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="T8" t="n">
         <v>2.12</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 22:11:03</t>
+          <t>2026-05-31 00:30:23</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,515 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 22:11:03</t>
+          <t>2026-05-31 00:30:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K10" t="n">
+        <v>950</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:30:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:30:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Skovde Aik</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,23 +881,23 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
         <v>1.02</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.29</v>
-      </c>
       <c r="T2" t="n">
         <v>1.01</v>
       </c>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>
@@ -1097,30 +1097,30 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Skovde Aik</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Jonkopings Sodra</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J3" t="n">
         <v>1.09</v>
@@ -1144,13 +1144,13 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,147 +1351,147 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1</v>
+        <v>970</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>970</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>1.26</v>
       </c>
       <c r="R4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S4" t="n">
         <v>1.26</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.85</v>
-      </c>
       <c r="T4" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
         <v>1.03</v>
@@ -1500,7 +1500,7 @@
         <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.03</v>
@@ -1521,81 +1521,81 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1652,14 +1652,14 @@
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
         <v>1.02</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.47</v>
-      </c>
       <c r="T5" t="n">
         <v>1.01</v>
       </c>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1835,21 +1835,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="W6" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP6" t="n">
         <v>9</v>
       </c>
-      <c r="Z6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AQ6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
         <v>9</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AU6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AW6" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BV6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>3.75</v>
+        <v>110</v>
       </c>
       <c r="H7" t="n">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>110</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S7" t="n">
         <v>1.47</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.3</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>2.24</v>
+        <v>1.66</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="X8" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA8" t="n">
         <v>4.7</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="BB8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>5.1</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="X8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS8" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1.62</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,244 +2875,244 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>1.24</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.21</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>1.21</v>
+        <v>5.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>
@@ -3129,244 +3129,1260 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I11" t="n">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="O11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P11" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.9</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Barra FC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Brusque FC</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:49:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:49:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:49:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -857,100 +857,100 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -959,70 +959,70 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1652,13 +1652,13 @@
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>2.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
@@ -1897,7 +1897,7 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>1.4</v>
@@ -1906,7 +1906,7 @@
         <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
         <v>1.26</v>
@@ -1918,28 +1918,28 @@
         <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
         <v>38</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
         <v>8.6</v>
@@ -1954,7 +1954,7 @@
         <v>29</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
         <v>23</v>
@@ -2038,19 +2038,19 @@
         <v>3.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
         <v>7</v>
@@ -2062,13 +2062,13 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
         <v>5.2</v>
@@ -2080,23 +2080,23 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
         <v>1.02</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H8" t="n">
         <v>4.5</v>
@@ -2393,7 +2393,7 @@
         <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
         <v>5.7</v>
@@ -2432,7 +2432,7 @@
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="X8" t="n">
         <v>44</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
@@ -2904,7 +2904,7 @@
         <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>1.57</v>
@@ -3051,22 +3051,22 @@
         <v>5.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ10" t="n">
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN10" t="n">
         <v>6</v>
@@ -3078,13 +3078,13 @@
         <v>29</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR10" t="n">
         <v>55</v>
       </c>
       <c r="BS10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10" t="n">
         <v>5.9</v>
@@ -3096,23 +3096,23 @@
         <v>29</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
         <v>55</v>
       </c>
       <c r="CA10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
         <v>2.48</v>
       </c>
       <c r="I11" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="J11" t="n">
         <v>2.9</v>
@@ -3254,7 +3254,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AR11" t="n">
         <v>12.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
         <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
         <v>19.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>6.8</v>
       </c>
       <c r="I13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
@@ -3687,13 +3687,13 @@
         <v>1.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
         <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
         <v>1.83</v>
@@ -3816,7 +3816,7 @@
         <v>3.45</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="BJ13" t="n">
         <v>11.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>2.6</v>
       </c>
       <c r="H14" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="I14" t="n">
         <v>3.45</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>3.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I15" t="n">
         <v>2.86</v>
@@ -4177,7 +4177,7 @@
         <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
@@ -4213,7 +4213,7 @@
         <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
         <v>970</v>
@@ -4231,7 +4231,7 @@
         <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
         <v>46</v>
@@ -4321,10 +4321,10 @@
         <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4339,10 +4339,10 @@
         <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4357,10 +4357,10 @@
         <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,55 +860,55 @@
         <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="K2" t="n">
         <v>3.1</v>
       </c>
       <c r="L2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.52</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -920,7 +920,7 @@
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
@@ -932,7 +932,7 @@
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
         <v>970</v>
@@ -941,94 +941,94 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO2" t="n">
         <v>60</v>
       </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="n">
         <v>3.6</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AV2" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.84</v>
+        <v>6.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.83</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1058,29 +1058,29 @@
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
         <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
         <v>1.29</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.26</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
         <v>1.26</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.46</v>
@@ -1900,7 +1900,7 @@
         <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P6" t="n">
         <v>1.69</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.02</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
         <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.2</v>
@@ -2405,7 +2405,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
         <v>1.13</v>
@@ -2426,13 +2426,13 @@
         <v>1.53</v>
       </c>
       <c r="U8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
         <v>44</v>
@@ -2447,7 +2447,7 @@
         <v>140</v>
       </c>
       <c r="AB8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC8" t="n">
         <v>15.5</v>
@@ -2492,7 +2492,7 @@
         <v>4.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR8" t="n">
         <v>4.8</v>
@@ -2504,7 +2504,7 @@
         <v>4</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AV8" t="n">
         <v>4.3</v>
@@ -2528,7 +2528,7 @@
         <v>4.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>4.3</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -2638,43 +2638,43 @@
         <v>2.02</v>
       </c>
       <c r="G9" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="H9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
         <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="T9" t="n">
         <v>2.22</v>
@@ -2686,22 +2686,22 @@
         <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA9" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC9" t="n">
         <v>8.4</v>
@@ -2728,10 +2728,10 @@
         <v>34</v>
       </c>
       <c r="AK9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM9" t="n">
         <v>280</v>
@@ -2740,97 +2740,97 @@
         <v>34</v>
       </c>
       <c r="AO9" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="BJ9" t="n">
         <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO9" t="n">
         <v>3.25</v>
       </c>
       <c r="BP9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BT9" t="n">
         <v>8.199999999999999</v>
@@ -2842,23 +2842,23 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
         <v>2.08</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>2.06</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
@@ -2904,7 +2904,7 @@
         <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.57</v>
@@ -2919,7 +2919,7 @@
         <v>1.51</v>
       </c>
       <c r="P10" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q10" t="n">
         <v>2.58</v>
@@ -2949,7 +2949,7 @@
         <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
         <v>55</v>
@@ -2958,7 +2958,7 @@
         <v>9</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
         <v>16.5</v>
@@ -3006,7 +3006,7 @@
         <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -3018,7 +3018,7 @@
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX10" t="n">
         <v>15</v>
@@ -3030,25 +3030,25 @@
         <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF10" t="n">
         <v>6.2</v>
       </c>
-      <c r="BF10" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG10" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="n">
         <v>2.76</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -3152,10 +3152,10 @@
         <v>2.48</v>
       </c>
       <c r="I11" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K11" t="n">
         <v>3.25</v>
@@ -3194,7 +3194,7 @@
         <v>1.58</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
         <v>10.5</v>
@@ -3227,7 +3227,7 @@
         <v>18.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>70</v>
@@ -3245,7 +3245,7 @@
         <v>220</v>
       </c>
       <c r="AN11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO11" t="n">
         <v>46</v>
@@ -3260,7 +3260,7 @@
         <v>12.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT11" t="n">
         <v>8.4</v>
@@ -3272,7 +3272,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX11" t="n">
         <v>19.5</v>
@@ -3284,28 +3284,28 @@
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BC11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG11" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI11" t="n">
         <v>2.22</v>
@@ -3314,31 +3314,31 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
         <v>6.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP11" t="n">
         <v>34</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11" t="n">
         <v>60</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11" t="n">
         <v>5.5</v>
@@ -3350,23 +3350,23 @@
         <v>24</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
         <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11" t="n">
         <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
         <v>3.2</v>
@@ -3415,7 +3415,7 @@
         <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
@@ -3430,7 +3430,7 @@
         <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
@@ -3445,13 +3445,13 @@
         <v>1.74</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="n">
         <v>16</v>
@@ -3466,7 +3466,7 @@
         <v>7.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
         <v>26</v>
@@ -3499,19 +3499,19 @@
         <v>250</v>
       </c>
       <c r="AN12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO12" t="n">
         <v>150</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12" t="n">
         <v>9.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AS12" t="n">
         <v>4.2</v>
@@ -3520,13 +3520,13 @@
         <v>4.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
         <v>15</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
@@ -3541,28 +3541,28 @@
         <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC12" t="n">
         <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG12" t="n">
         <v>4.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BN12" t="n">
         <v>4.8</v>
@@ -3586,13 +3586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT12" t="n">
         <v>7.4</v>
@@ -3604,30 +3604,30 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Club Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1.62</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>1.31</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,33 +3891,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.71</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>2.84</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.21</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3953,10 +3953,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4121,21 +4121,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,244 +4145,752 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.05</v>
+        <v>1.54</v>
       </c>
       <c r="G15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.9</v>
       </c>
       <c r="T15" t="n">
         <v>2.04</v>
       </c>
       <c r="U15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-05-31 07:27:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-31 07:27:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.76</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V17" t="n">
         <v>1.56</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W17" t="n">
         <v>1.4</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X17" t="n">
         <v>970</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y17" t="n">
         <v>970</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z17" t="n">
         <v>970</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA17" t="n">
         <v>55</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AB17" t="n">
         <v>970</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC17" t="n">
         <v>970</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AD17" t="n">
         <v>970</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE17" t="n">
         <v>46</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AF17" t="n">
         <v>25</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AG17" t="n">
         <v>970</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AH17" t="n">
         <v>27</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AI17" t="n">
         <v>80</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AJ17" t="n">
         <v>80</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK17" t="n">
         <v>60</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AL17" t="n">
         <v>90</v>
       </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
         <v>80</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AO17" t="n">
         <v>55</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AP17" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AQ17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU15" t="n">
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU17" t="n">
         <v>5.5</v>
       </c>
-      <c r="AV15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH15" t="n">
+      <c r="AV17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
         <v>2.78</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BI17" t="n">
         <v>2.28</v>
       </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT15" t="n">
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT17" t="n">
         <v>5.6</v>
       </c>
-      <c r="BU15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>2026-05-31 05:09:01</t>
+      <c r="BU17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,7 +899,7 @@
         <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
         <v>1.86</v>
@@ -965,7 +965,7 @@
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.2</v>
@@ -1070,7 +1070,7 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Peruvian Segunda Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Skovde Aik</t>
+          <t>Pirata FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra</t>
+          <t>Deportivo Llacuabamba</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1.28</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.29</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Skovde Aik</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Jonkopings Sodra</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,33 +1605,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,169 +1864,169 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>2.48</v>
+        <v>110</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>1.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>1.54</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.68</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2035,75 +2035,75 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,174 +2113,174 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I7" t="n">
-        <v>110</v>
+        <v>2.48</v>
       </c>
       <c r="J7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M7" t="n">
         <v>1.09</v>
       </c>
-      <c r="K7" t="n">
-        <v>950</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N7" t="n">
-        <v>1.29</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2289,75 +2289,75 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>110</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8</v>
+        <v>110</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>1.31</v>
       </c>
       <c r="O8" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>1.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.83</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>1.33</v>
       </c>
       <c r="X8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="G9" t="n">
-        <v>2.28</v>
+        <v>1.56</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="L9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.53</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="X9" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN9" t="n">
         <v>5.7</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>34</v>
-      </c>
       <c r="AO9" t="n">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BG9" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE9" t="n">
+      <c r="BH9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS9" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>2.06</v>
-      </c>
       <c r="BT9" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.08</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.08</v>
+        <v>5.3</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.66</v>
+        <v>1.08</v>
       </c>
       <c r="O10" t="n">
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.58</v>
+        <v>1.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>5.3</v>
+        <v>1.08</v>
       </c>
       <c r="T10" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.2</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>2.28</v>
       </c>
       <c r="H11" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>2.72</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="K11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO11" t="n">
         <v>3.25</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT11" t="n">
+      <c r="BP11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BT11" t="n">
         <v>8.4</v>
       </c>
-      <c r="AU11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO11" t="n">
+      <c r="BU11" t="n">
         <v>4.7</v>
       </c>
-      <c r="BP11" t="n">
-        <v>34</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>4</v>
-      </c>
       <c r="BV11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.4</v>
+        <v>2.02</v>
       </c>
       <c r="BX11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.800000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9</v>
+        <v>2.02</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Peruvian Segunda Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Sport Huancayo Res</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Ayacucho Futbol Club</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.64</v>
+        <v>1.08</v>
       </c>
       <c r="O12" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.56</v>
+        <v>1.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Club Deportes Santa Cruz</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>2.94</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.31</v>
+        <v>2.56</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>2.68</v>
+        <v>5.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>2.92</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.28</v>
+        <v>2.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="G15" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="H15" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.83</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.62</v>
-      </c>
       <c r="X15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Y15" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Z15" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AA15" t="n">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH15" t="n">
         <v>32</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>28</v>
       </c>
       <c r="AI15" t="n">
         <v>130</v>
       </c>
       <c r="AJ15" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="AN15" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AO15" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AP15" t="n">
-        <v>11.5</v>
+        <v>3.15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>3.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="AS15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
         <v>5.6</v>
       </c>
-      <c r="AT15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BZ15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Club Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,22 +4437,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4461,10 +4461,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4629,268 +4629,1030 @@
         <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Curico Unido</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-31 09:46:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>9</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-31 09:46:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-05-31 09:46:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Tecnico Universitario</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Barcelona (Ecu)</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="n">
         <v>3.5</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N20" t="n">
         <v>2.54</v>
       </c>
-      <c r="I17" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="O20" t="n">
         <v>1.52</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="P20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.18</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S20" t="n">
         <v>5.1</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T20" t="n">
         <v>2.04</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V17" t="n">
+      <c r="U20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.56</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W20" t="n">
         <v>1.4</v>
       </c>
-      <c r="X17" t="n">
+      <c r="X20" t="n">
         <v>970</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y20" t="n">
         <v>970</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z20" t="n">
         <v>970</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA20" t="n">
         <v>55</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AB20" t="n">
         <v>970</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AC20" t="n">
         <v>970</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD20" t="n">
         <v>970</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE20" t="n">
         <v>46</v>
       </c>
-      <c r="AF17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AF20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG20" t="n">
         <v>970</v>
       </c>
-      <c r="AH17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK17" t="n">
+      <c r="AH20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK20" t="n">
         <v>60</v>
       </c>
-      <c r="AL17" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO17" t="n">
+      <c r="AL20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO20" t="n">
         <v>55</v>
       </c>
-      <c r="AP17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU17" t="n">
+      <c r="AP20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU20" t="n">
         <v>5.5</v>
       </c>
-      <c r="AV17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-05-31 07:27:48</t>
+      <c r="AV20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K2" t="n">
         <v>3.1</v>
@@ -887,7 +887,7 @@
         <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
         <v>2.32</v>
@@ -908,7 +908,7 @@
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -950,7 +950,7 @@
         <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
         <v>65</v>
@@ -959,82 +959,82 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO2" t="n">
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AQ2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT2" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4</v>
-      </c>
       <c r="AU2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BD2" t="n">
         <v>1.76</v>
       </c>
-      <c r="AY2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BE2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG2" t="n">
         <v>1.76</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.73</v>
       </c>
       <c r="BH2" t="n">
         <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -1365,160 +1365,160 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="G4" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="I4" t="n">
-        <v>970</v>
+        <v>1.69</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1527,13 +1527,13 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
@@ -1545,7 +1545,7 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO4" t="n">
         <v>1.01</v>
@@ -1563,13 +1563,13 @@
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
@@ -1581,14 +1581,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -1619,175 +1619,175 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>970</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>970</v>
+        <v>5.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1.43</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.26</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI5" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,13 +1799,13 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
@@ -1817,7 +1817,7 @@
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
@@ -1835,14 +1835,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -1873,175 +1873,175 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>3.85</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.54</v>
+        <v>3.95</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2053,13 +2053,13 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO6" t="n">
         <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
@@ -2071,13 +2071,13 @@
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
         <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -2381,112 +2381,112 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>1.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.31</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.09</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP8" t="n">
         <v>1.03</v>
@@ -2537,19 +2537,19 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK8" t="n">
         <v>1.01</v>
@@ -2561,25 +2561,25 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
         <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS8" t="n">
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>1.53</v>
       </c>
       <c r="G9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I9" t="n">
         <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.2</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,19 +2913,19 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
         <v>1.08</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -3155,19 +3155,19 @@
         <v>5.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
         <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
         <v>1.62</v>
@@ -3176,13 +3176,13 @@
         <v>1.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="T11" t="n">
         <v>2.3</v>
@@ -3209,10 +3209,10 @@
         <v>150</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
         <v>24</v>
@@ -3221,7 +3221,7 @@
         <v>110</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
@@ -3245,70 +3245,70 @@
         <v>330</v>
       </c>
       <c r="AN11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
         <v>220</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AT11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW11" t="n">
+      <c r="BA11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA11" t="n">
+      <c r="BD11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF11" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6</v>
-      </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH11" t="n">
         <v>2.62</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ11" t="n">
         <v>13.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H12" t="n">
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R12" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3505,52 +3505,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H13" t="n">
         <v>2.82</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>3.25</v>
@@ -3678,16 +3678,16 @@
         <v>2.66</v>
       </c>
       <c r="O13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
         <v>1.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
         <v>5.3</v>
@@ -3696,13 +3696,13 @@
         <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V13" t="n">
         <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
         <v>9.4</v>
@@ -3756,10 +3756,10 @@
         <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
         <v>7.2</v>
@@ -3768,7 +3768,7 @@
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>7.4</v>
@@ -3780,7 +3780,7 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
         <v>15</v>
@@ -3792,37 +3792,37 @@
         <v>19</v>
       </c>
       <c r="BA13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE13" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
         <v>6.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ13" t="n">
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3837,10 +3837,10 @@
         <v>4.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR13" t="n">
         <v>55</v>
@@ -3852,7 +3852,7 @@
         <v>6</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV13" t="n">
         <v>29</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -3917,13 +3917,13 @@
         <v>2.76</v>
       </c>
       <c r="J14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K14" t="n">
         <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.12</v>
@@ -3953,10 +3953,10 @@
         <v>1.76</v>
       </c>
       <c r="V14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
         <v>10.5</v>
@@ -4070,7 +4070,7 @@
         <v>2.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ14" t="n">
         <v>11.5</v>
@@ -4088,7 +4088,7 @@
         <v>6.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP14" t="n">
         <v>34</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
         <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>1.46</v>
@@ -4207,7 +4207,7 @@
         <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
         <v>1.83</v>
@@ -4267,10 +4267,10 @@
         <v>150</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR15" t="n">
         <v>3.9</v>
@@ -4279,34 +4279,34 @@
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.76</v>
+        <v>4.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.98</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.7</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>4.1</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.8</v>
+        <v>18.5</v>
       </c>
       <c r="BA15" t="n">
         <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.8</v>
+        <v>19.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.8</v>
+        <v>19.5</v>
       </c>
       <c r="BD15" t="n">
         <v>4</v>
@@ -4315,7 +4315,7 @@
         <v>4.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.8</v>
+        <v>19</v>
       </c>
       <c r="BG15" t="n">
         <v>4.2</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -4413,175 +4413,175 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>1.26</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
         <v>1.01</v>
@@ -4593,7 +4593,7 @@
         <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO16" t="n">
         <v>1.01</v>
@@ -4611,7 +4611,7 @@
         <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -4667,79 +4667,79 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H17" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I17" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
         <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P17" t="n">
         <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T17" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="U17" t="n">
         <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z17" t="n">
         <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
         <v>32</v>
@@ -4748,19 +4748,19 @@
         <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ17" t="n">
         <v>46</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL17" t="n">
         <v>44</v>
@@ -4769,28 +4769,28 @@
         <v>90</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO17" t="n">
         <v>26</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR17" t="n">
         <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
         <v>9.199999999999999</v>
@@ -4805,49 +4805,49 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
         <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO17" t="n">
         <v>4.4</v>
@@ -4856,31 +4856,31 @@
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G18" t="n">
         <v>1.61</v>
@@ -4933,10 +4933,10 @@
         <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
         <v>1.35</v>
@@ -4945,40 +4945,40 @@
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
         <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z18" t="n">
         <v>70</v>
@@ -4987,7 +4987,7 @@
         <v>270</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>9.800000000000001</v>
@@ -4999,7 +4999,7 @@
         <v>140</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG18" t="n">
         <v>11.5</v>
@@ -5014,7 +5014,7 @@
         <v>17</v>
       </c>
       <c r="AK18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="n">
         <v>48</v>
@@ -5035,10 +5035,10 @@
         <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT18" t="n">
         <v>6</v>
@@ -5050,7 +5050,7 @@
         <v>20</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -5062,7 +5062,7 @@
         <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
         <v>11</v>
@@ -5071,16 +5071,16 @@
         <v>13.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF18" t="n">
         <v>7.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH18" t="n">
         <v>3.45</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -5178,172 +5178,172 @@
         <v>2.44</v>
       </c>
       <c r="G19" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H19" t="n">
         <v>2.94</v>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.45</v>
       </c>
-      <c r="K19" t="n">
+      <c r="O19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X19" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4</v>
       </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI19" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK19" t="n">
         <v>1.01</v>
@@ -5355,7 +5355,7 @@
         <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO19" t="n">
         <v>1.01</v>
@@ -5373,7 +5373,7 @@
         <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -5429,31 +5429,31 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
         <v>3.5</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="I20" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J20" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O20" t="n">
         <v>1.52</v>
@@ -5462,7 +5462,7 @@
         <v>1.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
@@ -5471,13 +5471,13 @@
         <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U20" t="n">
         <v>1.77</v>
       </c>
       <c r="V20" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W20" t="n">
         <v>1.4</v>
@@ -5591,68 +5591,68 @@
         <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G2" t="n">
         <v>2.88</v>
@@ -869,10 +869,10 @@
         <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
         <v>1.45</v>
@@ -881,19 +881,19 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="O2" t="n">
         <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q2" t="n">
         <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
         <v>4.4</v>
@@ -902,10 +902,10 @@
         <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
         <v>1.53</v>
@@ -965,58 +965,58 @@
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.93</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.82</v>
+        <v>5.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AT2" t="n">
         <v>4.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.97</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
         <v>6.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.02</v>
+        <v>5.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.97</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD2" t="n">
         <v>1.81</v>
       </c>
-      <c r="BA2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BB2" t="n">
+      <c r="BE2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF2" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG2" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BH2" t="n">
         <v>4.2</v>
@@ -1028,16 +1028,16 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO2" t="n">
         <v>3.65</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>110</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I3" t="n">
         <v>110</v>
@@ -1150,7 +1150,7 @@
         <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
@@ -1365,175 +1365,175 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
         <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
         <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="V4" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP4" t="n">
         <v>11</v>
       </c>
-      <c r="AA4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>240</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
@@ -1545,7 +1545,7 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
         <v>1.01</v>
@@ -1563,13 +1563,13 @@
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
@@ -1581,14 +1581,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
         <v>5.8</v>
@@ -1673,10 +1673,10 @@
         <v>2.12</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
         <v>48</v>
@@ -1691,7 +1691,7 @@
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
         <v>80</v>
@@ -1727,122 +1727,122 @@
         <v>90</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP5" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ5" t="n">
         <v>22</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
@@ -1873,64 +1873,64 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2.82</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.44</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
@@ -1948,19 +1948,19 @@
         <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
         <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="n">
         <v>80</v>
@@ -1969,55 +1969,55 @@
         <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM6" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AN6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AO6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="AS6" t="n">
         <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.88</v>
+        <v>5.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.7</v>
+        <v>14</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.8</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
         <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
         <v>4.1</v>
@@ -2029,74 +2029,74 @@
         <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
         <v>4.1</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV6" t="n">
         <v>29</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
         <v>1.94</v>
@@ -2244,7 +2244,7 @@
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
         <v>9</v>
@@ -2256,10 +2256,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AY7" t="n">
         <v>11.5</v>
@@ -2286,16 +2286,16 @@
         <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH7" t="n">
         <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
         <v>5.4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>1.9</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
         <v>8</v>
@@ -2420,7 +2420,7 @@
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
         <v>2.18</v>
@@ -2489,58 +2489,58 @@
         <v>300</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
         <v>3</v>
@@ -2552,49 +2552,49 @@
         <v>14</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN8" t="n">
         <v>4.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BP8" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR8" t="n">
         <v>42</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT8" t="n">
         <v>11</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>CA Atlas</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
-        <v>1.57</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S9" t="n">
         <v>1.02</v>
       </c>
-      <c r="N9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.97</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,61 +2875,61 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>CA Fenix</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S10" t="n">
         <v>1.02</v>
       </c>
-      <c r="G10" t="n">
-        <v>140</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I10" t="n">
-        <v>140</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K10" t="n">
-        <v>950</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="T10" t="n">
         <v>1.01</v>
       </c>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="G11" t="n">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.62</v>
+        <v>1.05</v>
       </c>
       <c r="P11" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>1.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>1.05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Peruvian Segunda Division</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sport Huancayo Res</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ayacucho Futbol Club</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3505,52 +3505,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.86</v>
+        <v>1.53</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="H13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.82</v>
       </c>
-      <c r="I13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.57</v>
-      </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>1.39</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="X13" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CA13" t="n">
         <v>5.3</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>29</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>29</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>55</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>9</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6</v>
+        <v>110</v>
       </c>
       <c r="H14" t="n">
-        <v>2.48</v>
+        <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>2.76</v>
+        <v>110</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="P14" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.58</v>
+        <v>1.07</v>
       </c>
       <c r="R14" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3</v>
+        <v>1.08</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="O15" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="P15" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="U15" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA15" t="n">
         <v>150</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI15" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="n">
-        <v>250</v>
+        <v>330</v>
       </c>
       <c r="AN15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO15" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB15" t="n">
+      <c r="BH15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP15" t="n">
         <v>19.5</v>
       </c>
-      <c r="BC15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU15" t="n">
         <v>4.7</v>
       </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Peruvian Segunda Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,189 +4399,189 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Club Deportes Santa Cruz</t>
+          <t>Sport Huancayo Res</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Ayacucho Futbol Club</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>110</v>
       </c>
       <c r="H16" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>110</v>
       </c>
       <c r="J16" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
         <v>1.01</v>
@@ -4593,7 +4593,7 @@
         <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
         <v>1.01</v>
@@ -4611,7 +4611,7 @@
         <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
         <v>1.01</v>
@@ -4629,21 +4629,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="I17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>2.66</v>
       </c>
       <c r="O17" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.76</v>
+        <v>2.58</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.96</v>
+        <v>5.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="X17" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AI17" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK17" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AO17" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
         <v>10</v>
       </c>
-      <c r="AR17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BN17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO17" t="n">
         <v>4.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.53</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="P18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>6.8</v>
       </c>
-      <c r="I18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AR18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>13.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE18" t="n">
         <v>6.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.1</v>
+        <v>2.22</v>
       </c>
       <c r="BJ18" t="n">
         <v>11.5</v>
       </c>
       <c r="BK18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN18" t="n">
         <v>6.6</v>
       </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BO18" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP18" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR18" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BS18" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW18" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY18" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="CA18" t="n">
         <v>9</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="G19" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="H19" t="n">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.5</v>
       </c>
-      <c r="K19" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="O19" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>1.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.63</v>
+        <v>2.46</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>5.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.56</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>1.74</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="X19" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z19" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AI19" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="AJ19" t="n">
         <v>34</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AL19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN19" t="n">
         <v>32</v>
       </c>
-      <c r="AM19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>970</v>
-      </c>
       <c r="AO19" t="n">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="AR19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT19" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT19" t="n">
+      <c r="AU19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW19" t="n">
         <v>4.1</v>
       </c>
-      <c r="AU19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AX19" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="AZ19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA19" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA19" t="n">
-        <v>5</v>
-      </c>
       <c r="BB19" t="n">
-        <v>4.9</v>
+        <v>19.5</v>
       </c>
       <c r="BC19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
         <v>4.7</v>
       </c>
-      <c r="BD19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,244 +5415,1260 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Club Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.1</v>
       </c>
-      <c r="G20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.52</v>
-      </c>
       <c r="O20" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="P20" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
         <v>970</v>
       </c>
       <c r="Y20" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AA20" t="n">
         <v>55</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD20" t="n">
         <v>970</v>
       </c>
       <c r="AE20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-31 14:16:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Curico Unido</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X21" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>46</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AK21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-31 14:16:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y22" t="n">
         <v>24</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="Z22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>9</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-31 14:16:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X23" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB23" t="n">
         <v>970</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AC23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-31 14:16:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH24" t="n">
         <v>26</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AI24" t="n">
         <v>75</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AJ24" t="n">
         <v>75</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AK24" t="n">
         <v>60</v>
       </c>
-      <c r="AL20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
+      <c r="AL24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
         <v>75</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AO24" t="n">
         <v>55</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AP24" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AQ24" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK20" t="n">
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
         <v>5.7</v>
       </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BT20" t="n">
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BT24" t="n">
         <v>5.6</v>
       </c>
-      <c r="BU20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
+      <c r="BU24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
         <v>3.5</v>
       </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>2026-05-31 12:02:48</t>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,13 +860,13 @@
         <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>2.96</v>
@@ -884,7 +884,7 @@
         <v>2.78</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
         <v>1.61</v>
@@ -896,7 +896,7 @@
         <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
         <v>1.92</v>
@@ -905,10 +905,10 @@
         <v>1.88</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -1022,7 +1022,7 @@
         <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>110</v>
       </c>
       <c r="H3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.3</v>
@@ -1150,16 +1150,16 @@
         <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="G4" t="n">
         <v>6.4</v>
@@ -1374,31 +1374,31 @@
         <v>1.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
         <v>1.35</v>
@@ -1410,67 +1410,67 @@
         <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="V4" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="W4" t="n">
         <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO4" t="n">
         <v>12</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>15.5</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1497,7 +1497,7 @@
         <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.18</v>
+        <v>7.2</v>
       </c>
       <c r="AY4" t="n">
         <v>15.5</v>
@@ -1506,89 +1506,89 @@
         <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.28</v>
+        <v>8</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.22</v>
+        <v>7.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.22</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.28</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.28</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
         <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.36</v>
@@ -1643,34 +1643,34 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
         <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1679,10 +1679,10 @@
         <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA5" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
         <v>10.5</v>
@@ -1691,10 +1691,10 @@
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF5" t="n">
         <v>13</v>
@@ -1703,10 +1703,10 @@
         <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
         <v>22</v>
@@ -1718,106 +1718,106 @@
         <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
         <v>12.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>5</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="BP5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU5" t="n">
         <v>4.6</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>22</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="G6" t="n">
         <v>3.45</v>
@@ -1882,49 +1882,49 @@
         <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
         <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
         <v>9</v>
@@ -1948,19 +1948,19 @@
         <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
         <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
         <v>80</v>
@@ -1969,134 +1969,134 @@
         <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM6" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="AR6" t="n">
         <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="AV6" t="n">
         <v>10</v>
       </c>
       <c r="AW6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>18</v>
-      </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BU6" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.95</v>
       </c>
       <c r="BV6" t="n">
         <v>29</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G7" t="n">
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I7" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -2166,7 +2166,7 @@
         <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.88</v>
@@ -2175,7 +2175,7 @@
         <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
         <v>1.33</v>
@@ -2187,7 +2187,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
         <v>38</v>
@@ -2202,7 +2202,7 @@
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
         <v>29</v>
@@ -2250,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>8.800000000000001</v>
@@ -2292,7 +2292,7 @@
         <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -2381,85 +2381,85 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
         <v>1.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W8" t="n">
         <v>2.18</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AB8" t="n">
         <v>6.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
         <v>30</v>
       </c>
       <c r="AE8" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
@@ -2480,121 +2480,121 @@
         <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AN8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO8" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="n">
         <v>3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BJ8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP8" t="n">
         <v>14</v>
       </c>
-      <c r="BK8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BQ8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU8" t="n">
         <v>4.9</v>
       </c>
-      <c r="BR8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.01</v>
@@ -2674,19 +2674,19 @@
         <v>1.12</v>
       </c>
       <c r="S9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.02</v>
       </c>
-      <c r="T9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H10" t="n">
         <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.01</v>
@@ -2937,10 +2937,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,186 +3129,186 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>FC Atletico Cearense</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ymir</t>
+          <t>Piaui EC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>2.78</v>
       </c>
       <c r="O11" t="n">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="H12" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
         <v>1.05</v>
@@ -3445,10 +3445,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3505,52 +3505,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="G13" t="n">
-        <v>1.57</v>
+        <v>110</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5</v>
+        <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>140</v>
       </c>
       <c r="J13" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>5.6</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.02</v>
       </c>
-      <c r="N13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.19</v>
-      </c>
       <c r="W13" t="n">
-        <v>2.74</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="G14" t="n">
         <v>110</v>
       </c>
       <c r="H14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="I14" t="n">
         <v>110</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
         <v>1.08</v>
@@ -3953,10 +3953,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>2.26</v>
+        <v>1.56</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="I15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X15" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>5.2</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="BR15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX15" t="n">
         <v>36</v>
       </c>
-      <c r="AA15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY15" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Peruvian Segunda Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sport Huancayo Res</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ayacucho Futbol Club</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE16" t="n">
         <v>110</v>
       </c>
-      <c r="H16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I16" t="n">
-        <v>110</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K16" t="n">
-        <v>950</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Peruvian Segunda Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Huancayo Res</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ayacucho Futbol Club</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.86</v>
+        <v>1.09</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1</v>
+        <v>110</v>
       </c>
       <c r="H17" t="n">
-        <v>2.82</v>
+        <v>1.09</v>
       </c>
       <c r="I17" t="n">
-        <v>3.05</v>
+        <v>110</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>1.18</v>
       </c>
       <c r="K17" t="n">
-        <v>3.25</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.66</v>
+        <v>1.29</v>
       </c>
       <c r="O17" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.58</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S17" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,148 +4912,148 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="G18" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="H18" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="I18" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
         <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
         <v>5.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="V18" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AA18" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AG18" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL18" t="n">
         <v>80</v>
       </c>
       <c r="AM18" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW18" t="n">
         <v>6</v>
       </c>
-      <c r="AV18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AX18" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AY18" t="n">
         <v>11.5</v>
@@ -5062,96 +5062,96 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN18" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BO18" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BP18" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BU18" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BV18" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX18" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
         <v>55</v>
       </c>
       <c r="CA18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2</v>
+        <v>3.55</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>2.76</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V19" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="W19" t="n">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF19" t="n">
         <v>26</v>
       </c>
-      <c r="AE19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AG19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR19" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AS19" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>19.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>19.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH19" t="n">
         <v>2.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS19" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW19" t="n">
         <v>7.4</v>
       </c>
-      <c r="BU19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY19" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,239 +5420,239 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Club Deportes Santa Cruz</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="G20" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="H20" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="O20" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.92</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="X20" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AA20" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AB20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG20" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AI20" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AJ20" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL20" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AN20" t="n">
         <v>32</v>
       </c>
       <c r="AO20" t="n">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="AQ20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO20" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS20" t="n">
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ20" t="n">
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
         <v>5.4</v>
       </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>6</v>
-      </c>
       <c r="BT20" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -5674,229 +5674,229 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Club Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I21" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O21" t="n">
         <v>1.31</v>
       </c>
-      <c r="M21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
       </c>
       <c r="AE21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN21" t="n">
         <v>32</v>
       </c>
-      <c r="AF21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>25</v>
-      </c>
       <c r="AO21" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>3.65</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.800000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>3.25</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.77</v>
+        <v>6.8</v>
       </c>
       <c r="BN21" t="n">
         <v>6.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,246 +5928,246 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T22" t="n">
         <v>1.61</v>
       </c>
-      <c r="H22" t="n">
+      <c r="U22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X22" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
         <v>6.8</v>
       </c>
-      <c r="I22" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BR22" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>10</v>
+        <v>1.7</v>
       </c>
       <c r="BT22" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>13</v>
+        <v>1.7</v>
       </c>
       <c r="BZ22" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,251 +6177,251 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.44</v>
+        <v>1.53</v>
       </c>
       <c r="G23" t="n">
-        <v>2.56</v>
+        <v>1.6</v>
       </c>
       <c r="H23" t="n">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="R23" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="T23" t="n">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>2.52</v>
+        <v>1.79</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>1.64</v>
+        <v>2.66</v>
       </c>
       <c r="X23" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="Z23" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="AA23" t="n">
-        <v>55</v>
+        <v>270</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="AJ23" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AM23" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="AN23" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="AP23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV23" t="n">
+      <c r="BN23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ23" t="n">
+      <c r="BQ23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA23" t="n">
         <v>9</v>
       </c>
-      <c r="BK23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,81 +6431,81 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="G24" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="H24" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="I24" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>2.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.54</v>
+        <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="S24" t="n">
-        <v>5.1</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="U24" t="n">
-        <v>1.79</v>
+        <v>2.46</v>
       </c>
       <c r="V24" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="X24" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Y24" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AA24" t="n">
         <v>55</v>
@@ -6514,161 +6514,415 @@
         <v>970</v>
       </c>
       <c r="AC24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH24" t="n">
         <v>970</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AI24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN24" t="n">
         <v>970</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AO24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-31 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X25" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE25" t="n">
         <v>46</v>
       </c>
-      <c r="AF24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH24" t="n">
+      <c r="AF25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH25" t="n">
         <v>26</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AI25" t="n">
         <v>75</v>
       </c>
-      <c r="AJ24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL24" t="n">
+      <c r="AJ25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL25" t="n">
         <v>80</v>
       </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO24" t="n">
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO25" t="n">
         <v>55</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AP25" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AQ25" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT24" t="n">
+      <c r="AR25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT25" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV24" t="n">
+      <c r="AU25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV25" t="n">
         <v>10</v>
       </c>
-      <c r="AW24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX24" t="n">
+      <c r="AW25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX25" t="n">
         <v>16</v>
       </c>
-      <c r="AY24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ24" t="n">
+      <c r="AY25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>17</v>
       </c>
-      <c r="BA24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH24" t="n">
+      <c r="BA25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
         <v>2.8</v>
       </c>
-      <c r="BI24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CB24" t="inlineStr">
-        <is>
-          <t>2026-05-31 14:16:41</t>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G2" t="n">
         <v>2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>3.5</v>
@@ -872,7 +872,7 @@
         <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
         <v>1.45</v>
@@ -887,52 +887,52 @@
         <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q2" t="n">
         <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF2" t="n">
         <v>970</v>
@@ -941,28 +941,28 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AO2" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
         <v>7.6</v>
@@ -971,13 +971,13 @@
         <v>7.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU2" t="n">
         <v>5.7</v>
@@ -986,40 +986,40 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.4</v>
+        <v>12.5</v>
       </c>
       <c r="AY2" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.53</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BI2" t="n">
         <v>2.58</v>
@@ -1028,7 +1028,7 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.45</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1058,7 +1058,7 @@
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.44</v>
       </c>
       <c r="I3" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="J3" t="n">
-        <v>1.15</v>
+        <v>2.68</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>1.34</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Q3" t="n">
         <v>1.3</v>
@@ -1159,64 +1159,64 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP3" t="n">
         <v>1.03</v>
@@ -1267,10 +1267,10 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="G4" t="n">
         <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X4" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="Z4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG4" t="n">
         <v>12</v>
       </c>
-      <c r="AA4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>9</v>
-      </c>
       <c r="BH4" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN4" t="n">
         <v>9.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BV4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
         <v>1.93</v>
@@ -1655,7 +1655,7 @@
         <v>1.81</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
         <v>3.05</v>
@@ -1676,67 +1676,67 @@
         <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT5" t="n">
         <v>7.4</v>
@@ -1745,10 +1745,10 @@
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
         <v>9.199999999999999</v>
@@ -1757,28 +1757,28 @@
         <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF5" t="n">
         <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
@@ -1820,7 +1820,7 @@
         <v>8.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -1873,40 +1873,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="I6" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="J6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
@@ -1915,43 +1915,43 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
         <v>9</v>
       </c>
       <c r="Y6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB6" t="n">
         <v>9.4</v>
       </c>
-      <c r="Z6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
         <v>16</v>
@@ -1960,91 +1960,91 @@
         <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AK6" t="n">
         <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AM6" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AO6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
         <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,31 +2053,31 @@
         <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BP6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
         <v>7.6</v>
@@ -2092,11 +2092,11 @@
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H7" t="n">
         <v>2.22</v>
@@ -2142,7 +2142,7 @@
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.46</v>
@@ -2160,16 +2160,16 @@
         <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
         <v>1.94</v>
@@ -2178,61 +2178,61 @@
         <v>1.7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
         <v>9</v>
@@ -2244,10 +2244,10 @@
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AU7" t="n">
         <v>6.4</v>
@@ -2259,31 +2259,31 @@
         <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="AY7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
         <v>19</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G8" t="n">
         <v>1.84</v>
@@ -2399,7 +2399,7 @@
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
@@ -2414,7 +2414,7 @@
         <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R8" t="n">
         <v>1.2</v>
@@ -2444,7 +2444,7 @@
         <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>6.6</v>
@@ -2456,91 +2456,91 @@
         <v>30</v>
       </c>
       <c r="AE8" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
         <v>9.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL8" t="n">
         <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>270</v>
+        <v>700</v>
       </c>
       <c r="AN8" t="n">
         <v>18</v>
       </c>
       <c r="AO8" t="n">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="AP8" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>5.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
         <v>7</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="n">
         <v>3</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.05</v>
+        <v>1.68</v>
       </c>
       <c r="G9" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="H9" t="n">
-        <v>1.05</v>
+        <v>2.8</v>
       </c>
       <c r="I9" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="J9" t="n">
-        <v>1.05</v>
+        <v>2.54</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,16 +2659,16 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="R9" t="n">
         <v>1.12</v>
@@ -2683,118 +2683,118 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="G10" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="J10" t="n">
-        <v>1.05</v>
+        <v>2.24</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2937,64 +2937,64 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
         <v>1.03</v>
@@ -3045,10 +3045,10 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="I11" t="n">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
         <v>2.78</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.83</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.78</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="W11" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB11" t="n">
         <v>16</v>
       </c>
-      <c r="AA11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AF11" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AG11" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AL11" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AO11" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AP11" t="n">
-        <v>8</v>
+        <v>2.06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.4</v>
+        <v>2.46</v>
       </c>
       <c r="AR11" t="n">
-        <v>10.5</v>
+        <v>2.46</v>
       </c>
       <c r="AS11" t="n">
-        <v>24</v>
+        <v>2.26</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>2.14</v>
       </c>
       <c r="AU11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK11" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ11" t="n">
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BV11" t="n">
         <v>15.5</v>
       </c>
-      <c r="BA11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.08</v>
+        <v>1.68</v>
       </c>
       <c r="G12" t="n">
-        <v>44</v>
+        <v>1.85</v>
       </c>
       <c r="H12" t="n">
-        <v>1.08</v>
+        <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>140</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.1</v>
       </c>
-      <c r="K12" t="n">
-        <v>950</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.05</v>
-      </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>1.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -3651,166 +3651,166 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>1.77</v>
       </c>
       <c r="H13" t="n">
-        <v>1.08</v>
+        <v>2.3</v>
       </c>
       <c r="I13" t="n">
-        <v>140</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="O13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="P13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.02</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>2.28</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -3905,166 +3905,166 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.07</v>
+        <v>4.5</v>
       </c>
       <c r="G14" t="n">
-        <v>110</v>
+        <v>7.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="I14" t="n">
-        <v>110</v>
+        <v>1.63</v>
       </c>
       <c r="J14" t="n">
-        <v>1.08</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>2.58</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G15" t="n">
         <v>1.56</v>
       </c>
       <c r="H15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I15" t="n">
         <v>6.2</v>
@@ -4174,7 +4174,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L15" t="n">
         <v>1.2</v>
@@ -4201,7 +4201,7 @@
         <v>1.98</v>
       </c>
       <c r="T15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U15" t="n">
         <v>2.52</v>
@@ -4213,10 +4213,10 @@
         <v>2.78</v>
       </c>
       <c r="X15" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Y15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="n">
         <v>65</v>
@@ -4225,100 +4225,100 @@
         <v>140</v>
       </c>
       <c r="AB15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC15" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
         <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AM15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AO15" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BH15" t="n">
         <v>5.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -4413,40 +4413,40 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="G16" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.56</v>
       </c>
-      <c r="M16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.63</v>
-      </c>
       <c r="P16" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
@@ -4455,112 +4455,112 @@
         <v>6.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W16" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="X16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AA16" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AI16" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AJ16" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL16" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
         <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="BA16" t="n">
         <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="BD16" t="n">
         <v>7.8</v>
@@ -4569,74 +4569,74 @@
         <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BN16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>9</v>
-      </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>1.09</v>
       </c>
       <c r="G17" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="H17" t="n">
         <v>1.09</v>
       </c>
       <c r="I17" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="J17" t="n">
-        <v>1.18</v>
+        <v>2.68</v>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
         <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.36</v>
@@ -4715,13 +4715,13 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y17" t="n">
         <v>1000</v>
@@ -4823,10 +4823,10 @@
         <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="G18" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="n">
         <v>2.86</v>
@@ -4933,10 +4933,10 @@
         <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K18" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L18" t="n">
         <v>1.58</v>
@@ -4945,7 +4945,7 @@
         <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
         <v>1.53</v>
@@ -4954,10 +4954,10 @@
         <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
         <v>5.3</v>
@@ -4966,13 +4966,13 @@
         <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X18" t="n">
         <v>9.4</v>
@@ -4996,7 +4996,7 @@
         <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF18" t="n">
         <v>19</v>
@@ -5005,28 +5005,28 @@
         <v>16.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI18" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK18" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AL18" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AM18" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN18" t="n">
         <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
         <v>8.199999999999999</v>
@@ -5038,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
         <v>7.4</v>
@@ -5050,7 +5050,7 @@
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>15</v>
@@ -5062,25 +5062,25 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="n">
         <v>2.76</v>
@@ -5092,31 +5092,31 @@
         <v>12</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP18" t="n">
         <v>29</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR18" t="n">
         <v>55</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT18" t="n">
         <v>6</v>
@@ -5128,23 +5128,23 @@
         <v>29</v>
       </c>
       <c r="BW18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX18" t="n">
         <v>55</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ18" t="n">
         <v>55</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -5178,10 +5178,10 @@
         <v>3.2</v>
       </c>
       <c r="G19" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="H19" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I19" t="n">
         <v>2.76</v>
@@ -5205,7 +5205,7 @@
         <v>1.53</v>
       </c>
       <c r="P19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q19" t="n">
         <v>2.58</v>
@@ -5226,7 +5226,7 @@
         <v>1.57</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X19" t="n">
         <v>10.5</v>
@@ -5268,19 +5268,19 @@
         <v>75</v>
       </c>
       <c r="AK19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AL19" t="n">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AM19" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
         <v>75</v>
       </c>
       <c r="AO19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP19" t="n">
         <v>6.4</v>
@@ -5292,7 +5292,7 @@
         <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
@@ -5304,7 +5304,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="AX19" t="n">
         <v>19.5</v>
@@ -5319,22 +5319,22 @@
         <v>5.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="BC19" t="n">
         <v>5.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE19" t="n">
         <v>6.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="n">
         <v>2.8</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -5429,43 +5429,43 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M20" t="n">
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
         <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
         <v>5.1</v>
@@ -5474,13 +5474,13 @@
         <v>2.12</v>
       </c>
       <c r="U20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="X20" t="n">
         <v>12</v>
@@ -5495,7 +5495,7 @@
         <v>150</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC20" t="n">
         <v>9.6</v>
@@ -5507,7 +5507,7 @@
         <v>100</v>
       </c>
       <c r="AF20" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -5519,10 +5519,10 @@
         <v>130</v>
       </c>
       <c r="AJ20" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
         <v>65</v>
@@ -5531,22 +5531,22 @@
         <v>250</v>
       </c>
       <c r="AN20" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO20" t="n">
         <v>150</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT20" t="n">
         <v>4.8</v>
@@ -5555,10 +5555,10 @@
         <v>6</v>
       </c>
       <c r="AV20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX20" t="n">
         <v>8.199999999999999</v>
@@ -5570,7 +5570,7 @@
         <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB20" t="n">
         <v>19.5</v>
@@ -5579,22 +5579,22 @@
         <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF20" t="n">
         <v>19</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
@@ -5609,40 +5609,40 @@
         <v>6</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.39</v>
@@ -5707,7 +5707,7 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
         <v>1.31</v>
@@ -5716,31 +5716,31 @@
         <v>1.77</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R21" t="n">
         <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
         <v>1.7</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
         <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z21" t="n">
         <v>23</v>
@@ -5752,7 +5752,7 @@
         <v>12.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
@@ -5794,7 +5794,7 @@
         <v>3.85</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR21" t="n">
         <v>4.2</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G23" t="n">
         <v>1.6</v>
@@ -6203,10 +6203,10 @@
         <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.41</v>
@@ -6224,7 +6224,7 @@
         <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
         <v>1.32</v>
@@ -6242,7 +6242,7 @@
         <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X23" t="n">
         <v>16.5</v>
@@ -6260,7 +6260,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AD23" t="n">
         <v>32</v>
@@ -6293,7 +6293,7 @@
         <v>180</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO23" t="n">
         <v>200</v>
@@ -6305,22 +6305,22 @@
         <v>16</v>
       </c>
       <c r="AR23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS23" t="n">
         <v>6</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>6.4</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX23" t="n">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>18.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB23" t="n">
         <v>11</v>
@@ -6341,16 +6341,16 @@
         <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF23" t="n">
         <v>7.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH23" t="n">
         <v>3.45</v>
@@ -6374,7 +6374,7 @@
         <v>3.95</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP23" t="n">
         <v>10.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -6454,13 +6454,13 @@
         <v>3.05</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.25</v>
@@ -6628,7 +6628,7 @@
         <v>5.8</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP24" t="n">
         <v>16.5</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
         <v>3.2</v>
       </c>
       <c r="H25" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I25" t="n">
         <v>2.88</v>
@@ -6777,7 +6777,7 @@
         <v>46</v>
       </c>
       <c r="AF25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG25" t="n">
         <v>16.5</v>
@@ -6816,7 +6816,7 @@
         <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT25" t="n">
         <v>7.2</v>
@@ -6828,7 +6828,7 @@
         <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX25" t="n">
         <v>16</v>
@@ -6840,25 +6840,25 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BB25" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BE25" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH25" t="n">
         <v>2.82</v>
@@ -6906,7 +6906,7 @@
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -902,7 +902,7 @@
         <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
@@ -1004,7 +1004,7 @@
         <v>2.06</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="BD2" t="n">
         <v>2.08</v>
@@ -1019,7 +1019,7 @@
         <v>2.08</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI2" t="n">
         <v>2.58</v>
@@ -1040,7 +1040,7 @@
         <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -1111,175 +1111,175 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>3.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.44</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>44</v>
+        <v>2.64</v>
       </c>
       <c r="J3" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.34</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
         <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AB3" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>500</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AO3" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK3" t="n">
         <v>1.01</v>
@@ -1291,50 +1291,50 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO3" t="n">
         <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ3" t="n">
         <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS3" t="n">
         <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU3" t="n">
         <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW3" t="n">
         <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY3" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA3" t="n">
         <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -1371,13 +1371,13 @@
         <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -1389,19 +1389,19 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1413,7 +1413,7 @@
         <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="W4" t="n">
         <v>1.19</v>
@@ -1440,19 +1440,19 @@
         <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AG4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AH4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
         <v>900</v>
@@ -1464,7 +1464,7 @@
         <v>700</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
         <v>700</v>
@@ -1497,7 +1497,7 @@
         <v>18.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY4" t="n">
         <v>19.5</v>
@@ -1506,10 +1506,10 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
         <v>10.5</v>
@@ -1518,10 +1518,10 @@
         <v>10.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG4" t="n">
         <v>12</v>
@@ -1560,7 +1560,7 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT4" t="n">
         <v>4.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
@@ -1655,19 +1655,19 @@
         <v>1.81</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
         <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
         <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
         <v>2.06</v>
@@ -1676,7 +1676,7 @@
         <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
         <v>100</v>
@@ -1691,7 +1691,7 @@
         <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>160</v>
@@ -1703,7 +1703,7 @@
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
         <v>320</v>
@@ -1730,13 +1730,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT5" t="n">
         <v>7.4</v>
@@ -1745,10 +1745,10 @@
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX5" t="n">
         <v>9.199999999999999</v>
@@ -1757,28 +1757,28 @@
         <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
         <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
@@ -1808,7 +1808,7 @@
         <v>13</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR5" t="n">
         <v>27</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
         <v>2.86</v>
       </c>
       <c r="J6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
         <v>3.25</v>
@@ -1900,7 +1900,7 @@
         <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
         <v>1.45</v>
@@ -1921,19 +1921,19 @@
         <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
         <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA6" t="n">
         <v>420</v>
@@ -1945,7 +1945,7 @@
         <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
         <v>290</v>
@@ -1954,10 +1954,10 @@
         <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
@@ -1978,7 +1978,7 @@
         <v>180</v>
       </c>
       <c r="AO6" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AP6" t="n">
         <v>6.4</v>
@@ -1990,10 +1990,10 @@
         <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
@@ -2002,37 +2002,37 @@
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG6" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
         <v>2.64</v>
@@ -2068,7 +2068,7 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
         <v>5.6</v>
@@ -2092,11 +2092,11 @@
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="G7" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H7" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.46</v>
@@ -2178,7 +2178,7 @@
         <v>1.7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
         <v>19.5</v>
@@ -2226,7 +2226,7 @@
         <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
         <v>500</v>
@@ -2268,22 +2268,22 @@
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC7" t="n">
         <v>8</v>
       </c>
-      <c r="BC7" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7" t="n">
         <v>19</v>
@@ -2310,7 +2310,7 @@
         <v>7</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -2384,34 +2384,34 @@
         <v>1.65</v>
       </c>
       <c r="G8" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q8" t="n">
         <v>2.36</v>
@@ -2420,28 +2420,28 @@
         <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2450,7 +2450,7 @@
         <v>6.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>30</v>
@@ -2459,7 +2459,7 @@
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
@@ -2471,7 +2471,7 @@
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK8" t="n">
         <v>25</v>
@@ -2483,22 +2483,22 @@
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT8" t="n">
         <v>5.2</v>
@@ -2510,7 +2510,7 @@
         <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AX8" t="n">
         <v>7</v>
@@ -2522,79 +2522,79 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ8" t="n">
         <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN8" t="n">
         <v>4.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BR8" t="n">
         <v>40</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -2635,109 +2635,109 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>38</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>44</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2.54</v>
+        <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>38</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="O9" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.24</v>
+        <v>2.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>4.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V9" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="X9" t="n">
-        <v>90</v>
+        <v>8.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="AC9" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
       </c>
       <c r="AF9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI9" t="n">
         <v>500</v>
       </c>
-      <c r="AG9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>540</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
         <v>500</v>
@@ -2746,13 +2746,13 @@
         <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.48</v>
+        <v>5.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.57</v>
+        <v>7.6</v>
       </c>
       <c r="AT9" t="n">
         <v>3.85</v>
@@ -2761,104 +2761,104 @@
         <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.54</v>
+        <v>5.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.57</v>
+        <v>7.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.49</v>
+        <v>5.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.49</v>
+        <v>4.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.54</v>
+        <v>6.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.57</v>
+        <v>7.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.57</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.57</v>
+        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.57</v>
+        <v>6.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.57</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -2889,97 +2889,97 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.14</v>
+        <v>2.44</v>
       </c>
       <c r="I10" t="n">
-        <v>44</v>
+        <v>2.86</v>
       </c>
       <c r="J10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.24</v>
       </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
         <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AI10" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2994,125 +2994,125 @@
         <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -3143,25 +3143,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G11" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H11" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
@@ -3170,61 +3170,61 @@
         <v>2.78</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
         <v>1.83</v>
       </c>
       <c r="V11" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="W11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AA11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF11" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AG11" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AH11" t="n">
         <v>23</v>
@@ -3236,79 +3236,79 @@
         <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
         <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>500</v>
       </c>
       <c r="AO11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.06</v>
+        <v>5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.46</v>
+        <v>5.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.26</v>
+        <v>6.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.14</v>
+        <v>5.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.06</v>
+        <v>5.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.28</v>
+        <v>6.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.34</v>
+        <v>7.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.46</v>
+        <v>6.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.24</v>
+        <v>6.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.36</v>
+        <v>7.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.42</v>
+        <v>8.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.46</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.42</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="n">
         <v>3.05</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11" t="n">
         <v>11.5</v>
@@ -3320,13 +3320,13 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BN11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
@@ -3338,16 +3338,16 @@
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BT11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BW11" t="n">
         <v>6.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
         <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
         <v>4.4</v>
@@ -3415,43 +3415,43 @@
         <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R12" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="S12" t="n">
         <v>1.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
         <v>2.16</v>
       </c>
       <c r="X12" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="Y12" t="n">
         <v>85</v>
@@ -3463,7 +3463,7 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC12" t="n">
         <v>14.5</v>
@@ -3505,122 +3505,122 @@
         <v>22</v>
       </c>
       <c r="AP12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW12" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="AX12" t="n">
         <v>5.5</v>
       </c>
-      <c r="AU12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="AY12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA12" t="n">
         <v>6.2</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BB12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC12" t="n">
         <v>5.3</v>
       </c>
-      <c r="AY12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB12" t="n">
+      <c r="BD12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG12" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.5</v>
       </c>
       <c r="BH12" t="n">
         <v>6.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ12" t="n">
         <v>9</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BN12" t="n">
         <v>5.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP12" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BT12" t="n">
         <v>9.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV12" t="n">
         <v>29</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX12" t="n">
         <v>28</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CA12" t="n">
         <v>4.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="G13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
         <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.14</v>
@@ -3675,25 +3675,25 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.02</v>
+        <v>9</v>
       </c>
       <c r="O13" t="n">
         <v>1.07</v>
       </c>
       <c r="P13" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q13" t="n">
         <v>1.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="S13" t="n">
         <v>1.58</v>
       </c>
       <c r="T13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="U13" t="n">
         <v>3.3</v>
@@ -3756,58 +3756,58 @@
         <v>5.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>280</v>
+        <v>970</v>
       </c>
       <c r="AP13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BA13" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BB13" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="BG13" t="n">
         <v>3.05</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H14" t="n">
         <v>1.47</v>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>1.09</v>
@@ -3941,16 +3941,16 @@
         <v>1.28</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S14" t="n">
         <v>1.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="U14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V14" t="n">
         <v>2.58</v>
@@ -3980,10 +3980,10 @@
         <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AF14" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="n">
         <v>65</v>
@@ -3998,7 +3998,7 @@
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AL14" t="n">
         <v>120</v>
@@ -4007,13 +4007,13 @@
         <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO14" t="n">
         <v>15</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AQ14" t="n">
         <v>4.9</v>
@@ -4022,7 +4022,7 @@
         <v>4.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
         <v>4.2</v>
@@ -4058,7 +4058,7 @@
         <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BF14" t="n">
         <v>4.3</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -4165,13 +4165,13 @@
         <v>1.56</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
         <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K15" t="n">
         <v>5.7</v>
@@ -4183,43 +4183,43 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
         <v>1.13</v>
       </c>
       <c r="P15" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R15" t="n">
         <v>1.83</v>
       </c>
       <c r="S15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T15" t="n">
         <v>1.54</v>
       </c>
       <c r="U15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
         <v>2.78</v>
       </c>
       <c r="X15" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Y15" t="n">
         <v>34</v>
       </c>
       <c r="Z15" t="n">
-        <v>65</v>
+        <v>350</v>
       </c>
       <c r="AA15" t="n">
         <v>140</v>
@@ -4246,7 +4246,7 @@
         <v>18.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ15" t="n">
         <v>17.5</v>
@@ -4258,73 +4258,73 @@
         <v>24</v>
       </c>
       <c r="AM15" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO15" t="n">
         <v>40</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU15" t="n">
         <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY15" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC15" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC15" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD15" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH15" t="n">
         <v>5.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.4</v>
@@ -4342,7 +4342,7 @@
         <v>5</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BP15" t="n">
         <v>9.800000000000001</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G16" t="n">
         <v>2.54</v>
@@ -4425,25 +4425,25 @@
         <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O16" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q16" t="n">
         <v>2.74</v>
@@ -4452,19 +4452,19 @@
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X16" t="n">
         <v>8.199999999999999</v>
@@ -4473,7 +4473,7 @@
         <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AA16" t="n">
         <v>700</v>
@@ -4488,7 +4488,7 @@
         <v>19</v>
       </c>
       <c r="AE16" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
@@ -4503,19 +4503,19 @@
         <v>700</v>
       </c>
       <c r="AJ16" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AK16" t="n">
         <v>38</v>
       </c>
       <c r="AL16" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM16" t="n">
         <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AO16" t="n">
         <v>700</v>
@@ -4530,7 +4530,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>6</v>
@@ -4554,7 +4554,7 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16" t="n">
         <v>11.5</v>
@@ -4575,10 +4575,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ16" t="n">
         <v>12.5</v>
@@ -4596,10 +4596,10 @@
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BP16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ16" t="n">
         <v>7</v>
@@ -4614,13 +4614,13 @@
         <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4632,11 +4632,11 @@
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -4667,230 +4667,230 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.09</v>
+        <v>1.98</v>
       </c>
       <c r="G17" t="n">
-        <v>44</v>
+        <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>1.09</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X17" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
         <v>1.04</v>
       </c>
-      <c r="W17" t="n">
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
         <v>1.04</v>
       </c>
-      <c r="X17" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H18" t="n">
         <v>2.92</v>
       </c>
-      <c r="G18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.86</v>
-      </c>
       <c r="I18" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>3.15</v>
@@ -4948,7 +4948,7 @@
         <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P18" t="n">
         <v>1.57</v>
@@ -4957,64 +4957,64 @@
         <v>2.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
         <v>5.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W18" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="X18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Z18" t="n">
         <v>22</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF18" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
         <v>160</v>
       </c>
       <c r="AJ18" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AK18" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL18" t="n">
         <v>160</v>
@@ -5023,13 +5023,13 @@
         <v>500</v>
       </c>
       <c r="AN18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO18" t="n">
         <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.2</v>
@@ -5038,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT18" t="n">
         <v>7.4</v>
@@ -5050,7 +5050,7 @@
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX18" t="n">
         <v>15</v>
@@ -5062,19 +5062,19 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
         <v>8.4</v>
@@ -5086,65 +5086,65 @@
         <v>2.76</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="BJ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
         <v>12</v>
       </c>
-      <c r="BK18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
+      <c r="BN18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS18" t="n">
         <v>10</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>29</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>9</v>
       </c>
       <c r="BT18" t="n">
         <v>6</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BV18" t="n">
         <v>29</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -5187,28 +5187,28 @@
         <v>2.76</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.53</v>
       </c>
       <c r="P19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R19" t="n">
         <v>1.19</v>
@@ -5220,7 +5220,7 @@
         <v>2.08</v>
       </c>
       <c r="U19" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V19" t="n">
         <v>1.57</v>
@@ -5229,7 +5229,7 @@
         <v>1.41</v>
       </c>
       <c r="X19" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y19" t="n">
         <v>8.199999999999999</v>
@@ -5253,10 +5253,10 @@
         <v>44</v>
       </c>
       <c r="AF19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AG19" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
@@ -5316,22 +5316,22 @@
         <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG19" t="n">
         <v>7.4</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN19" t="n">
         <v>6.6</v>
@@ -5364,10 +5364,10 @@
         <v>34</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
         <v>9.199999999999999</v>
@@ -5382,23 +5382,23 @@
         <v>24</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX19" t="n">
         <v>48</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ19" t="n">
         <v>55</v>
       </c>
       <c r="CA19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.97</v>
       </c>
       <c r="G20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H20" t="n">
         <v>4.7</v>
@@ -5444,7 +5444,7 @@
         <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L20" t="n">
         <v>1.54</v>
@@ -5459,10 +5459,10 @@
         <v>1.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R20" t="n">
         <v>1.21</v>
@@ -5474,13 +5474,13 @@
         <v>2.12</v>
       </c>
       <c r="U20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V20" t="n">
         <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X20" t="n">
         <v>12</v>
@@ -5528,7 +5528,7 @@
         <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN20" t="n">
         <v>28</v>
@@ -5549,7 +5549,7 @@
         <v>4.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU20" t="n">
         <v>6</v>
@@ -5564,7 +5564,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ20" t="n">
         <v>18.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="G21" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="H21" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="I21" t="n">
         <v>3.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L21" t="n">
         <v>1.39</v>
@@ -5707,52 +5707,52 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.31</v>
       </c>
       <c r="P21" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB21" t="n">
         <v>12.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
@@ -5761,142 +5761,142 @@
         <v>40</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
         <v>55</v>
       </c>
       <c r="AJ21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL21" t="n">
         <v>48</v>
       </c>
-      <c r="AK21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>50</v>
-      </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.7</v>
+        <v>9.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW21" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW21" t="n">
+      <c r="AX21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF21" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB21" t="n">
+      <c r="BG21" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
         <v>3.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BJ21" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN21" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G22" t="n">
         <v>2.9</v>
@@ -5949,40 +5949,40 @@
         <v>2.98</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
         <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="T22" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U22" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V22" t="n">
         <v>1.51</v>
@@ -6024,7 +6024,7 @@
         <v>970</v>
       </c>
       <c r="AI22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ22" t="n">
         <v>46</v>
@@ -6033,16 +6033,16 @@
         <v>30</v>
       </c>
       <c r="AL22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN22" t="n">
         <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP22" t="n">
         <v>1.03</v>
@@ -6057,10 +6057,10 @@
         <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV22" t="n">
         <v>9.199999999999999</v>
@@ -6099,58 +6099,58 @@
         <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN22" t="n">
         <v>6.2</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -6194,55 +6194,55 @@
         <v>1.54</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H23" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U23" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V23" t="n">
         <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X23" t="n">
         <v>16.5</v>
@@ -6257,7 +6257,7 @@
         <v>270</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC23" t="n">
         <v>11.5</v>
@@ -6269,34 +6269,34 @@
         <v>140</v>
       </c>
       <c r="AF23" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AI23" t="n">
         <v>130</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>48</v>
       </c>
       <c r="AM23" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN23" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO23" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AP23" t="n">
         <v>11.5</v>
@@ -6305,10 +6305,10 @@
         <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
@@ -6320,7 +6320,7 @@
         <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AX23" t="n">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>18.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
         <v>11</v>
@@ -6341,43 +6341,43 @@
         <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF23" t="n">
         <v>7.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BJ23" t="n">
         <v>11.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BP23" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ23" t="n">
         <v>6.2</v>
@@ -6386,35 +6386,35 @@
         <v>28</v>
       </c>
       <c r="BS23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU23" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BZ23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CA23" t="n">
         <v>9</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
         <v>1.65</v>
@@ -6499,7 +6499,7 @@
         <v>1.62</v>
       </c>
       <c r="X24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y24" t="n">
         <v>19.5</v>
@@ -6556,16 +6556,16 @@
         <v>4.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU24" t="n">
         <v>3.5</v>
@@ -6586,13 +6586,13 @@
         <v>4.2</v>
       </c>
       <c r="BA24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB24" t="n">
         <v>5</v>
       </c>
-      <c r="BB24" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD24" t="n">
         <v>5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G25" t="n">
         <v>3.2</v>
@@ -6708,7 +6708,7 @@
         <v>2.68</v>
       </c>
       <c r="I25" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>2.94</v>
@@ -6729,7 +6729,7 @@
         <v>1.52</v>
       </c>
       <c r="P25" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q25" t="n">
         <v>2.5</v>
@@ -6906,7 +6906,7 @@
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
         <v>2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
         <v>3.5</v>
@@ -872,7 +872,7 @@
         <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.45</v>
@@ -890,19 +890,19 @@
         <v>1.59</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
         <v>4.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
@@ -914,7 +914,7 @@
         <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -923,22 +923,22 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC2" t="n">
         <v>42</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH2" t="n">
         <v>500</v>
@@ -974,7 +974,7 @@
         <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="AT2" t="n">
         <v>4.4</v>
@@ -995,19 +995,19 @@
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.78</v>
+        <v>3.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.08</v>
+        <v>3.15</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="BE2" t="n">
         <v>8.199999999999999</v>
@@ -1016,13 +1016,13 @@
         <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BH2" t="n">
         <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>2.64</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
@@ -1165,7 +1165,7 @@
         <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y3" t="n">
         <v>11</v>
@@ -1222,55 +1222,55 @@
         <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG3" t="n">
         <v>5.3</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.5</v>
@@ -1282,59 +1282,59 @@
         <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BN3" t="n">
         <v>6.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
         <v>27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>40</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BT3" t="n">
         <v>5.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV3" t="n">
         <v>19</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX3" t="n">
         <v>34</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>29</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -1377,13 +1377,13 @@
         <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1401,19 +1401,19 @@
         <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
         <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="W4" t="n">
         <v>1.19</v>
@@ -1440,7 +1440,7 @@
         <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
         <v>220</v>
@@ -1488,7 +1488,7 @@
         <v>14</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
         <v>9</v>
@@ -1497,7 +1497,7 @@
         <v>18.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
         <v>19.5</v>
@@ -1506,7 +1506,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
@@ -1631,10 +1631,10 @@
         <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.36</v>
@@ -1670,7 +1670,7 @@
         <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1730,10 +1730,10 @@
         <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AS5" t="n">
         <v>7.8</v>
@@ -1757,19 +1757,19 @@
         <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
         <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BE5" t="n">
         <v>7.8</v>
@@ -1778,7 +1778,7 @@
         <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -1912,16 +1912,16 @@
         <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T6" t="n">
         <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
         <v>1.37</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V7" t="n">
         <v>1.7</v>
@@ -2184,7 +2184,7 @@
         <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z7" t="n">
         <v>25</v>
@@ -2193,22 +2193,22 @@
         <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
         <v>60</v>
@@ -2259,7 +2259,7 @@
         <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
         <v>8.4</v>
@@ -2268,25 +2268,25 @@
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC7" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC7" t="n">
-        <v>8</v>
-      </c>
       <c r="BD7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG7" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BH7" t="n">
         <v>3.15</v>
@@ -2328,7 +2328,7 @@
         <v>5.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H8" t="n">
         <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
@@ -2432,7 +2432,7 @@
         <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
@@ -2477,7 +2477,7 @@
         <v>25</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
@@ -2492,13 +2492,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.6</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
         <v>5.2</v>
@@ -2510,7 +2510,7 @@
         <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX8" t="n">
         <v>7</v>
@@ -2525,7 +2525,7 @@
         <v>7.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
@@ -2534,13 +2534,13 @@
         <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
         <v>13.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="n">
         <v>3.05</v>
@@ -2552,7 +2552,7 @@
         <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2570,19 +2570,19 @@
         <v>13.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR8" t="n">
         <v>40</v>
       </c>
       <c r="BS8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT8" t="n">
         <v>11</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.53</v>
@@ -2674,7 +2674,7 @@
         <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>4.8</v>
+        <v>1.05</v>
       </c>
       <c r="T9" t="n">
         <v>2.16</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I10" t="n">
         <v>2.86</v>
@@ -2904,7 +2904,7 @@
         <v>2.68</v>
       </c>
       <c r="K10" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.56</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J11" t="n">
         <v>3.25</v>
@@ -3161,10 +3161,10 @@
         <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
         <v>2.78</v>
@@ -3188,10 +3188,10 @@
         <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W11" t="n">
         <v>1.25</v>
@@ -3224,7 +3224,7 @@
         <v>36</v>
       </c>
       <c r="AG11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH11" t="n">
         <v>23</v>
@@ -3260,55 +3260,55 @@
         <v>5.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV11" t="n">
         <v>5.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY11" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA11" t="n">
         <v>7.8</v>
       </c>
       <c r="BB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD11" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF11" t="n">
         <v>8.6</v>
       </c>
-      <c r="BF11" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH11" t="n">
         <v>3.05</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
         <v>11.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
         <v>6.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="BG12" t="n">
         <v>5.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3654,13 @@
         <v>1.61</v>
       </c>
       <c r="G13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H13" t="n">
         <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="n">
         <v>4.3</v>
@@ -3669,40 +3669,40 @@
         <v>11.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P13" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R13" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="S13" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="T13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V13" t="n">
         <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X13" t="n">
         <v>150</v>
@@ -3720,7 +3720,7 @@
         <v>500</v>
       </c>
       <c r="AC13" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AD13" t="n">
         <v>42</v>
@@ -3732,149 +3732,149 @@
         <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="n">
         <v>100</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
         <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="AO13" t="n">
-        <v>970</v>
+        <v>280</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AQ13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BF13" t="n">
         <v>3.3</v>
       </c>
-      <c r="AR13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BG13" t="n">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
         <v>42</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE14" t="n">
         <v>65</v>
@@ -4013,16 +4013,16 @@
         <v>15</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="AQ14" t="n">
         <v>4.9</v>
       </c>
       <c r="AR14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS14" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
         <v>4.2</v>
@@ -4055,10 +4055,10 @@
         <v>4.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="BF14" t="n">
         <v>4.3</v>
@@ -4070,65 +4070,65 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
         <v>1.13</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q15" t="n">
         <v>1.4</v>
@@ -4201,10 +4201,10 @@
         <v>1.99</v>
       </c>
       <c r="T15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V15" t="n">
         <v>1.2</v>
@@ -4213,7 +4213,7 @@
         <v>2.78</v>
       </c>
       <c r="X15" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="Y15" t="n">
         <v>34</v>
@@ -4273,13 +4273,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS15" t="n">
         <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU15" t="n">
         <v>6.4</v>
@@ -4288,31 +4288,31 @@
         <v>19.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB15" t="n">
         <v>6.8</v>
       </c>
-      <c r="BA15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BC15" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD15" t="n">
         <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
         <v>4.4</v>
@@ -4342,7 +4342,7 @@
         <v>5</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BP15" t="n">
         <v>9.800000000000001</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -4461,10 +4461,10 @@
         <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
         <v>8.199999999999999</v>
@@ -4563,7 +4563,7 @@
         <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE16" t="n">
         <v>8.4</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K17" t="n">
         <v>4.3</v>
@@ -4691,7 +4691,7 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
@@ -4700,7 +4700,7 @@
         <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R17" t="n">
         <v>1.26</v>
@@ -4715,16 +4715,16 @@
         <v>1.89</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X17" t="n">
         <v>500</v>
       </c>
       <c r="Y17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
         <v>500</v>
@@ -4733,13 +4733,13 @@
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC17" t="n">
         <v>42</v>
       </c>
       <c r="AD17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
         <v>500</v>
@@ -4751,7 +4751,7 @@
         <v>500</v>
       </c>
       <c r="AH17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
         <v>500</v>
@@ -4775,55 +4775,55 @@
         <v>500</v>
       </c>
       <c r="AP17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE17" t="n">
         <v>2.02</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AZ17" t="n">
+      <c r="BF17" t="n">
         <v>2.08</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.98</v>
       </c>
       <c r="BG17" t="n">
         <v>2.24</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="G18" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H18" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="I18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.58</v>
@@ -4945,40 +4945,40 @@
         <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="O18" t="n">
         <v>1.54</v>
       </c>
       <c r="P18" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V18" t="n">
         <v>1.45</v>
       </c>
       <c r="W18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z18" t="n">
         <v>22</v>
@@ -5026,7 +5026,7 @@
         <v>50</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AP18" t="n">
         <v>7.8</v>
@@ -5038,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" t="n">
         <v>7.4</v>
@@ -5050,7 +5050,7 @@
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX18" t="n">
         <v>15</v>
@@ -5062,25 +5062,25 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB18" t="n">
         <v>8</v>
       </c>
-      <c r="BB18" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BC18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD18" t="n">
         <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
         <v>8.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH18" t="n">
         <v>2.76</v>
@@ -5131,7 +5131,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
         <v>10</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -5235,13 +5235,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA19" t="n">
         <v>44</v>
       </c>
       <c r="AB19" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC19" t="n">
         <v>7.4</v>
@@ -5283,7 +5283,7 @@
         <v>44</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>6.8</v>
@@ -5292,7 +5292,7 @@
         <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
@@ -5304,10 +5304,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AX19" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
         <v>11.5</v>
@@ -5316,25 +5316,25 @@
         <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BH19" t="n">
         <v>2.8</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="G20" t="n">
         <v>2.06</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.54</v>
@@ -5453,7 +5453,7 @@
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O20" t="n">
         <v>1.5</v>
@@ -5462,7 +5462,7 @@
         <v>1.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R20" t="n">
         <v>1.21</v>
@@ -5474,10 +5474,10 @@
         <v>2.12</v>
       </c>
       <c r="U20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W20" t="n">
         <v>1.94</v>
@@ -5498,7 +5498,7 @@
         <v>7.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD20" t="n">
         <v>26</v>
@@ -5543,10 +5543,10 @@
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT20" t="n">
         <v>4.9</v>
@@ -5558,7 +5558,7 @@
         <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX20" t="n">
         <v>8.199999999999999</v>
@@ -5570,7 +5570,7 @@
         <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB20" t="n">
         <v>19.5</v>
@@ -5579,16 +5579,16 @@
         <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BF20" t="n">
         <v>19</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH20" t="n">
         <v>2.84</v>
@@ -5600,13 +5600,13 @@
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>6</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
@@ -5624,10 +5624,10 @@
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU20" t="n">
         <v>5.8</v>
@@ -5648,11 +5648,11 @@
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -5686,16 +5686,16 @@
         <v>2.38</v>
       </c>
       <c r="G21" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H21" t="n">
         <v>2.84</v>
       </c>
       <c r="I21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
         <v>3.85</v>
@@ -5707,7 +5707,7 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
         <v>1.31</v>
@@ -5716,10 +5716,10 @@
         <v>1.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
         <v>3.3</v>
@@ -5728,19 +5728,19 @@
         <v>1.71</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
         <v>25</v>
@@ -5752,7 +5752,7 @@
         <v>12.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
@@ -5767,7 +5767,7 @@
         <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AI21" t="n">
         <v>55</v>
@@ -5779,7 +5779,7 @@
         <v>34</v>
       </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="AO21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
@@ -5839,7 +5839,7 @@
         <v>5.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="BG21" t="n">
         <v>4.6</v>
@@ -5851,10 +5851,10 @@
         <v>2.8</v>
       </c>
       <c r="BJ21" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="BK21" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5884,7 +5884,7 @@
         <v>6.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H22" t="n">
         <v>2.58</v>
       </c>
       <c r="I22" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J22" t="n">
         <v>3.5</v>
@@ -5955,34 +5955,34 @@
         <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U22" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="V22" t="n">
         <v>1.51</v>
@@ -6033,7 +6033,7 @@
         <v>30</v>
       </c>
       <c r="AL22" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
         <v>85</v>
@@ -6042,22 +6042,22 @@
         <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ22" t="n">
         <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
         <v>6.8</v>
@@ -6066,10 +6066,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY22" t="n">
         <v>9.199999999999999</v>
@@ -6078,37 +6078,37 @@
         <v>11.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
         <v>3.9</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6132,13 +6132,13 @@
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
@@ -6150,7 +6150,7 @@
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.34</v>
@@ -6236,7 +6236,7 @@
         <v>2.12</v>
       </c>
       <c r="U23" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V23" t="n">
         <v>1.14</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>2.44</v>
       </c>
       <c r="G24" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H24" t="n">
         <v>3.05</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H25" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I25" t="n">
         <v>2.9</v>
       </c>
       <c r="J25" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L25" t="n">
         <v>1.49</v>
@@ -6732,7 +6732,7 @@
         <v>1.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R25" t="n">
         <v>1.2</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
@@ -6888,13 +6888,13 @@
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>2.72</v>
+        <v>3.55</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BT25" t="n">
         <v>5.7</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
         <v>1.45</v>
@@ -887,10 +887,10 @@
         <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R2" t="n">
         <v>1.21</v>
@@ -905,16 +905,16 @@
         <v>1.89</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
         <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -923,13 +923,13 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC2" t="n">
         <v>42</v>
       </c>
       <c r="AD2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
@@ -938,10 +938,10 @@
         <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
@@ -959,10 +959,10 @@
         <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
         <v>7.6</v>
@@ -974,10 +974,10 @@
         <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU2" t="n">
         <v>5.7</v>
@@ -986,7 +986,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -995,40 +995,40 @@
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BA2" t="n">
         <v>3.15</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.06</v>
+        <v>3.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,10 +1037,10 @@
         <v>1.36</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1064,13 +1064,13 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -1123,13 +1123,13 @@
         <v>2.64</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I4" t="n">
         <v>1.8</v>
@@ -1380,7 +1380,7 @@
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
@@ -1389,13 +1389,13 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
         <v>2.18</v>
@@ -1410,10 +1410,10 @@
         <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="W4" t="n">
         <v>1.19</v>
@@ -1437,7 +1437,7 @@
         <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE4" t="n">
         <v>34</v>
@@ -1479,16 +1479,16 @@
         <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AT4" t="n">
         <v>14</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
         <v>9</v>
@@ -1500,28 +1500,28 @@
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
         <v>10</v>
       </c>
       <c r="BB4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>11</v>
       </c>
-      <c r="BC4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
         <v>12</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -1619,46 +1619,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
         <v>1.76</v>
@@ -1667,19 +1667,19 @@
         <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y5" t="n">
-        <v>18</v>
-      </c>
       <c r="Z5" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1688,13 +1688,13 @@
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="AF5" t="n">
         <v>12.5</v>
@@ -1709,7 +1709,7 @@
         <v>320</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
         <v>20</v>
@@ -1721,7 +1721,7 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
         <v>500</v>
@@ -1730,13 +1730,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
         <v>7.4</v>
@@ -1760,7 +1760,7 @@
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
         <v>17</v>
@@ -1772,77 +1772,77 @@
         <v>18</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
         <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5" t="n">
         <v>27</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I6" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="J6" t="n">
         <v>2.78</v>
@@ -1891,40 +1891,40 @@
         <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
         <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
         <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X6" t="n">
         <v>9</v>
@@ -1933,25 +1933,25 @@
         <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
         <v>420</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
         <v>290</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AG6" t="n">
         <v>17</v>
@@ -1975,16 +1975,16 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
         <v>120</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
         <v>12.5</v>
@@ -2005,22 +2005,22 @@
         <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY6" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC6" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>7.2</v>
       </c>
       <c r="BD6" t="n">
         <v>7.6</v>
@@ -2029,22 +2029,22 @@
         <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG6" t="n">
         <v>7.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,31 +2053,31 @@
         <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW6" t="n">
         <v>7.6</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -2127,46 +2127,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="I7" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
         <v>1.9</v>
@@ -2175,7 +2175,7 @@
         <v>1.95</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W7" t="n">
         <v>1.35</v>
@@ -2256,10 +2256,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
         <v>8.4</v>
@@ -2295,7 +2295,7 @@
         <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
         <v>5.4</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
         <v>7</v>
@@ -2316,41 +2316,41 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BT7" t="n">
         <v>5.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -2381,67 +2381,67 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2450,31 +2450,31 @@
         <v>6.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
         <v>150</v>
@@ -2483,7 +2483,7 @@
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
@@ -2492,28 +2492,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="AS8" t="n">
         <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AU8" t="n">
         <v>4.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="n">
         <v>7.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8" t="n">
         <v>6.4</v>
@@ -2543,58 +2543,58 @@
         <v>8</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BJ8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BR8" t="n">
         <v>40</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="n">
         <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
         <v>1.53</v>
@@ -2674,16 +2674,16 @@
         <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
         <v>1.76</v>
@@ -2692,7 +2692,7 @@
         <v>8.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
         <v>36</v>
@@ -2737,7 +2737,7 @@
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO9" t="n">
         <v>500</v>
@@ -2749,7 +2749,7 @@
         <v>5.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
         <v>7.6</v>
@@ -2761,7 +2761,7 @@
         <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW9" t="n">
         <v>7.4</v>
@@ -2770,13 +2770,13 @@
         <v>5.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ9" t="n">
         <v>6.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
         <v>6.4</v>
@@ -2791,10 +2791,10 @@
         <v>7.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="n">
         <v>2.74</v>
@@ -2821,7 +2821,7 @@
         <v>3.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ9" t="n">
         <v>6.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>3.25</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I10" t="n">
         <v>2.86</v>
@@ -3024,19 +3024,19 @@
         <v>5.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BA10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC10" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
         <v>6.8</v>
@@ -3054,22 +3054,22 @@
         <v>2.56</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BJ10" t="n">
         <v>13</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO10" t="n">
         <v>4.1</v>
@@ -3078,41 +3078,41 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BT10" t="n">
         <v>5.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV10" t="n">
         <v>27</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
         <v>1.95</v>
       </c>
       <c r="I11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J11" t="n">
         <v>3.25</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H12" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>4.8</v>
@@ -3415,40 +3415,40 @@
         <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q12" t="n">
         <v>1.33</v>
       </c>
       <c r="R12" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="T12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V12" t="n">
         <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X12" t="n">
         <v>120</v>
@@ -3520,10 +3520,10 @@
         <v>5.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW12" t="n">
         <v>6.4</v>
@@ -3532,10 +3532,10 @@
         <v>5.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA12" t="n">
         <v>6.2</v>
@@ -3547,80 +3547,80 @@
         <v>5.3</v>
       </c>
       <c r="BD12" t="n">
-        <v>16</v>
+        <v>5.7</v>
       </c>
       <c r="BE12" t="n">
         <v>6.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH12" t="n">
         <v>6.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ12" t="n">
         <v>9</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BN12" t="n">
         <v>5.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP12" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BT12" t="n">
         <v>9.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV12" t="n">
         <v>29</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX12" t="n">
         <v>28</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA12" t="n">
         <v>4.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H13" t="n">
         <v>4.1</v>
@@ -3666,49 +3666,49 @@
         <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.08</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="R13" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="S13" t="n">
         <v>1.61</v>
       </c>
       <c r="T13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="U13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
         <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="X13" t="n">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
         <v>130</v>
@@ -3717,13 +3717,13 @@
         <v>340</v>
       </c>
       <c r="AB13" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC13" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AD13" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
         <v>120</v>
@@ -3732,10 +3732,10 @@
         <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH13" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI13" t="n">
         <v>100</v>
@@ -3750,7 +3750,7 @@
         <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN13" t="n">
         <v>15</v>
@@ -3759,64 +3759,64 @@
         <v>280</v>
       </c>
       <c r="AP13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>2.92</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>2.96</v>
-      </c>
       <c r="AR13" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>2.6</v>
       </c>
-      <c r="AV13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.64</v>
-      </c>
       <c r="BA13" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3870,11 +3870,11 @@
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -3917,52 +3917,52 @@
         <v>1.63</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>1.09</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q14" t="n">
         <v>1.28</v>
       </c>
       <c r="R14" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
         <v>1.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U14" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="V14" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="W14" t="n">
         <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
         <v>500</v>
@@ -3971,7 +3971,7 @@
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="AC14" t="n">
         <v>42</v>
@@ -3986,10 +3986,10 @@
         <v>180</v>
       </c>
       <c r="AG14" t="n">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -4007,22 +4007,22 @@
         <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
         <v>15</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AT14" t="n">
         <v>4.2</v>
@@ -4034,19 +4034,19 @@
         <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX14" t="n">
         <v>4.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>4.2</v>
@@ -4055,22 +4055,22 @@
         <v>4.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="BF14" t="n">
         <v>4.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4124,11 +4124,11 @@
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -4159,40 +4159,40 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G15" t="n">
         <v>1.56</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I15" t="n">
         <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K15" t="n">
         <v>5.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.13</v>
       </c>
       <c r="P15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R15" t="n">
         <v>1.83</v>
@@ -4201,10 +4201,10 @@
         <v>1.99</v>
       </c>
       <c r="T15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V15" t="n">
         <v>1.2</v>
@@ -4264,19 +4264,19 @@
         <v>5.1</v>
       </c>
       <c r="AO15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP15" t="n">
         <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AR15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
         <v>6.6</v>
@@ -4324,65 +4324,65 @@
         <v>5.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN15" t="n">
         <v>5</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BP15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BQ15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU15" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5.3</v>
       </c>
       <c r="BV15" t="n">
         <v>38</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ15" t="n">
         <v>10.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -4413,40 +4413,40 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="H16" t="n">
         <v>3.75</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="M16" t="n">
         <v>1.14</v>
       </c>
       <c r="N16" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O16" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="P16" t="n">
         <v>1.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
@@ -4461,16 +4461,16 @@
         <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="X16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z16" t="n">
         <v>48</v>
@@ -4497,25 +4497,25 @@
         <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="AI16" t="n">
         <v>700</v>
       </c>
       <c r="AJ16" t="n">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="AK16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL16" t="n">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="AM16" t="n">
         <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO16" t="n">
         <v>700</v>
@@ -4530,19 +4530,19 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT16" t="n">
         <v>6</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
@@ -4551,10 +4551,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB16" t="n">
         <v>11.5</v>
@@ -4566,13 +4566,13 @@
         <v>8.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH16" t="n">
         <v>2.68</v>
@@ -4596,13 +4596,13 @@
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BP16" t="n">
         <v>22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -4667,58 +4667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K17" t="n">
         <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
         <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U17" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X17" t="n">
         <v>500</v>
@@ -4775,70 +4775,70 @@
         <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="AR17" t="n">
         <v>2.88</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="AT17" t="n">
         <v>4.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.28</v>
+        <v>2.86</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.96</v>
+        <v>2.68</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.24</v>
+        <v>2.98</v>
       </c>
       <c r="BH17" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.15</v>
+        <v>2.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4856,25 +4856,25 @@
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
         <v>1.04</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>1.05</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="G18" t="n">
         <v>2.9</v>
@@ -4939,7 +4939,7 @@
         <v>3.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
         <v>1.12</v>
@@ -4948,7 +4948,7 @@
         <v>2.64</v>
       </c>
       <c r="O18" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="P18" t="n">
         <v>1.54</v>
@@ -4957,19 +4957,19 @@
         <v>2.66</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
         <v>5.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
         <v>1.83</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W18" t="n">
         <v>1.52</v>
@@ -5008,7 +5008,7 @@
         <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="n">
         <v>50</v>
@@ -5032,7 +5032,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR18" t="n">
         <v>15</v>
@@ -5113,7 +5113,7 @@
         <v>8.6</v>
       </c>
       <c r="BR18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS18" t="n">
         <v>10</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>2.56</v>
       </c>
       <c r="I19" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J19" t="n">
         <v>2.94</v>
@@ -5208,13 +5208,13 @@
         <v>1.54</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T19" t="n">
         <v>2.08</v>
@@ -5223,7 +5223,7 @@
         <v>1.79</v>
       </c>
       <c r="V19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W19" t="n">
         <v>1.41</v>
@@ -5250,7 +5250,7 @@
         <v>13.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="n">
         <v>23</v>
@@ -5292,7 +5292,7 @@
         <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
@@ -5316,7 +5316,7 @@
         <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
@@ -5325,13 +5325,13 @@
         <v>7.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG19" t="n">
         <v>29</v>
@@ -5340,7 +5340,7 @@
         <v>2.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ19" t="n">
         <v>11.5</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN19" t="n">
         <v>6.6</v>
@@ -5364,10 +5364,10 @@
         <v>34</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS19" t="n">
         <v>9.199999999999999</v>
@@ -5382,23 +5382,23 @@
         <v>24</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX19" t="n">
         <v>48</v>
       </c>
       <c r="BY19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>55</v>
       </c>
       <c r="CA19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -5429,40 +5429,40 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G20" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O20" t="n">
         <v>1.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
         <v>1.21</v>
@@ -5471,28 +5471,28 @@
         <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U20" t="n">
         <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
         <v>42</v>
       </c>
       <c r="AA20" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB20" t="n">
         <v>7.4</v>
@@ -5501,7 +5501,7 @@
         <v>8.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
         <v>100</v>
@@ -5519,7 +5519,7 @@
         <v>130</v>
       </c>
       <c r="AJ20" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK20" t="n">
         <v>32</v>
@@ -5531,128 +5531,128 @@
         <v>240</v>
       </c>
       <c r="AN20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO20" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.4</v>
+        <v>3.95</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AU20" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="AY20" t="n">
-        <v>7.8</v>
+        <v>3.75</v>
       </c>
       <c r="AZ20" t="n">
         <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>19.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF20" t="n">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BT20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H21" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="I21" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="J21" t="n">
         <v>3.25</v>
@@ -5707,10 +5707,10 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P21" t="n">
         <v>1.87</v>
@@ -5719,22 +5719,22 @@
         <v>1.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U21" t="n">
         <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
@@ -5743,40 +5743,40 @@
         <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA21" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB21" t="n">
         <v>12.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
         <v>20</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>19.5</v>
       </c>
       <c r="AI21" t="n">
         <v>55</v>
       </c>
       <c r="AJ21" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL21" t="n">
         <v>46</v>
@@ -5785,64 +5785,64 @@
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.4</v>
+        <v>3.9</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="AS21" t="n">
         <v>4.9</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AU21" t="n">
         <v>6.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
         <v>4.7</v>
       </c>
       <c r="AX21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
         <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
-        <v>17</v>
+        <v>4.3</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH21" t="n">
         <v>3.55</v>
@@ -5851,7 +5851,7 @@
         <v>2.8</v>
       </c>
       <c r="BJ21" t="n">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="BK21" t="n">
         <v>4.9</v>
@@ -5860,19 +5860,19 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
@@ -5881,16 +5881,16 @@
         <v>7.6</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G22" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H22" t="n">
         <v>2.58</v>
       </c>
       <c r="I22" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
         <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
@@ -5970,25 +5970,25 @@
         <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T22" t="n">
         <v>1.63</v>
       </c>
       <c r="U22" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W22" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
         <v>970</v>
@@ -6102,13 +6102,13 @@
         <v>3.9</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6132,13 +6132,13 @@
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.4</v>
+        <v>2.94</v>
       </c>
       <c r="BT22" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
@@ -6150,7 +6150,7 @@
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>2.94</v>
+        <v>7.4</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -6209,13 +6209,13 @@
         <v>4.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>1.34</v>
@@ -6230,7 +6230,7 @@
         <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
         <v>2.12</v>
@@ -6356,19 +6356,19 @@
         <v>3.5</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ23" t="n">
         <v>11.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN23" t="n">
         <v>3.9</v>
@@ -6380,16 +6380,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR23" t="n">
         <v>28</v>
       </c>
       <c r="BS23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU23" t="n">
         <v>6.6</v>
@@ -6398,23 +6398,23 @@
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BZ23" t="n">
         <v>19</v>
       </c>
       <c r="CA23" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -6705,16 +6705,16 @@
         <v>3.15</v>
       </c>
       <c r="H25" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J25" t="n">
         <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L25" t="n">
         <v>1.49</v>
@@ -6723,7 +6723,7 @@
         <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O25" t="n">
         <v>1.52</v>
@@ -6732,19 +6732,19 @@
         <v>1.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R25" t="n">
         <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V25" t="n">
         <v>1.53</v>
@@ -6783,7 +6783,7 @@
         <v>16.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI25" t="n">
         <v>75</v>
@@ -6804,7 +6804,7 @@
         <v>70</v>
       </c>
       <c r="AO25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP25" t="n">
         <v>6.8</v>
@@ -6816,7 +6816,7 @@
         <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT25" t="n">
         <v>7.2</v>
@@ -6828,7 +6828,7 @@
         <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX25" t="n">
         <v>16</v>
@@ -6846,13 +6846,13 @@
         <v>3.65</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BF25" t="n">
         <v>3.65</v>
@@ -6861,10 +6861,10 @@
         <v>5.6</v>
       </c>
       <c r="BH25" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
@@ -6894,7 +6894,7 @@
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BT25" t="n">
         <v>5.7</v>
@@ -6918,11 +6918,11 @@
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -857,61 +857,61 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T2" t="n">
         <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
         <v>950</v>
@@ -923,7 +923,7 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>950</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>42</v>
@@ -965,22 +965,22 @@
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
         <v>7.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
@@ -995,19 +995,19 @@
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.85</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.15</v>
+        <v>42</v>
       </c>
       <c r="BE2" t="n">
         <v>8.4</v>
@@ -1016,28 +1016,28 @@
         <v>7.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.95</v>
+        <v>2.98</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.36</v>
+        <v>2.94</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO2" t="n">
         <v>4.6</v>
@@ -1046,41 +1046,41 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.37</v>
+        <v>2.64</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.33</v>
+        <v>2.72</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.35</v>
+        <v>2.82</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -1111,79 +1111,79 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
         <v>36</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>29</v>
@@ -1192,149 +1192,149 @@
         <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL3" t="n">
         <v>130</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AV3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK3" t="n">
         <v>5.2</v>
       </c>
-      <c r="AY3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.52</v>
+        <v>9.6</v>
       </c>
       <c r="BN3" t="n">
         <v>6.8</v>
       </c>
       <c r="BO3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU3" t="n">
         <v>4</v>
       </c>
-      <c r="BP3" t="n">
-        <v>27</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BV3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -1365,88 +1365,88 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
         <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AB4" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>10.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AH4" t="n">
         <v>42</v>
@@ -1470,125 +1470,125 @@
         <v>700</v>
       </c>
       <c r="AO4" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AS4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AT4" t="n">
-        <v>14</v>
-      </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AY4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>20</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC4" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC4" t="n">
-        <v>11</v>
-      </c>
       <c r="BD4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>12</v>
       </c>
-      <c r="BH4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
         <v>1.96</v>
@@ -1628,7 +1628,7 @@
         <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
@@ -1649,13 +1649,13 @@
         <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
         <v>1.84</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
         <v>3.15</v>
@@ -1676,7 +1676,7 @@
         <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
         <v>85</v>
@@ -1691,7 +1691,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>320</v>
@@ -1703,7 +1703,7 @@
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
         <v>320</v>
@@ -1721,7 +1721,7 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO5" t="n">
         <v>500</v>
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT5" t="n">
         <v>7.4</v>
@@ -1748,7 +1748,7 @@
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
         <v>9.199999999999999</v>
@@ -1760,7 +1760,7 @@
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
         <v>17</v>
@@ -1772,13 +1772,13 @@
         <v>18</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
         <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="n">
         <v>3.7</v>
@@ -1802,31 +1802,31 @@
         <v>4.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP5" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BR5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="G6" t="n">
         <v>3.85</v>
       </c>
       <c r="H6" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="L6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N6" t="n">
         <v>2.44</v>
       </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P6" t="n">
         <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
         <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>9</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.8</v>
+        <v>950</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.5</v>
+        <v>50</v>
       </c>
       <c r="AA6" t="n">
         <v>420</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>950</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
         <v>290</v>
       </c>
       <c r="AF6" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>170</v>
+        <v>420</v>
       </c>
       <c r="AK6" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AL6" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK6" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BN6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BA6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BO6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU6" t="n">
         <v>4.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H7" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I7" t="n">
         <v>2.4</v>
@@ -2142,7 +2142,7 @@
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
@@ -2169,19 +2169,19 @@
         <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V7" t="n">
         <v>1.71</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
         <v>8.800000000000001</v>
@@ -2193,7 +2193,7 @@
         <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
@@ -2205,10 +2205,10 @@
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
         <v>60</v>
@@ -2229,22 +2229,22 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
         <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT7" t="n">
         <v>6.2</v>
@@ -2253,61 +2253,61 @@
         <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
         <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="n">
         <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>11</v>
       </c>
-      <c r="BK7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>10</v>
-      </c>
       <c r="BN7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO7" t="n">
         <v>5.2</v>
@@ -2316,41 +2316,41 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT7" t="n">
         <v>5.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -2381,82 +2381,82 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
         <v>6.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
         <v>3.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T8" t="n">
         <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
         <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="n">
         <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="n">
         <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AF8" t="n">
         <v>10.5</v>
@@ -2465,7 +2465,7 @@
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
@@ -2477,7 +2477,7 @@
         <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
@@ -2489,70 +2489,70 @@
         <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
         <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="AU8" t="n">
         <v>4.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="AW8" t="n">
         <v>7.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AY8" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BA8" t="n">
         <v>7.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
         <v>8</v>
       </c>
       <c r="BF8" t="n">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
         <v>8</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,25 +2561,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR8" t="n">
         <v>40</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU8" t="n">
         <v>4.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -2638,106 +2638,106 @@
         <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
       </c>
       <c r="L9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.53</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.55</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.52</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
         <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X9" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
         <v>500</v>
@@ -2746,13 +2746,13 @@
         <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.8</v>
+        <v>1.51</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>1.61</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>1.63</v>
       </c>
       <c r="AT9" t="n">
         <v>3.85</v>
@@ -2761,104 +2761,104 @@
         <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.9</v>
+        <v>1.61</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>1.62</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.6</v>
+        <v>1.51</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.9</v>
+        <v>1.51</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.2</v>
+        <v>1.59</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.6</v>
+        <v>1.62</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.4</v>
+        <v>1.59</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>1.62</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.8</v>
+        <v>1.63</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>1.63</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.8</v>
+        <v>1.63</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -2889,94 +2889,94 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="G10" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="I10" t="n">
-        <v>2.86</v>
+        <v>7.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
       <c r="K10" t="n">
         <v>2.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="M10" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="O10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
         <v>6.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
         <v>900</v>
@@ -2994,125 +2994,125 @@
         <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.65</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.65</v>
+        <v>1.28</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.9</v>
+        <v>1.28</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>1.27</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.3</v>
+        <v>1.28</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.65</v>
+        <v>1.25</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.8</v>
+        <v>1.22</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>1.27</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.6</v>
+        <v>1.25</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.2</v>
+        <v>1.28</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.8</v>
+        <v>1.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>1.28</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.8</v>
+        <v>1.28</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.6</v>
+        <v>1.27</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.8</v>
+        <v>1.28</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>1.28</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.8</v>
+        <v>1.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>1.55</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.56</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -3143,73 +3143,73 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H11" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="I11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J11" t="n">
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
         <v>1.49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
         <v>2.24</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
         <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
         <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X11" t="n">
         <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB11" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
@@ -3218,10 +3218,10 @@
         <v>11.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG11" t="n">
         <v>19.5</v>
@@ -3236,7 +3236,7 @@
         <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AL11" t="n">
         <v>500</v>
@@ -3248,22 +3248,22 @@
         <v>500</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
         <v>5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS11" t="n">
         <v>6.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AU11" t="n">
         <v>4.3</v>
@@ -3275,7 +3275,7 @@
         <v>6.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY11" t="n">
         <v>6.2</v>
@@ -3284,7 +3284,7 @@
         <v>6.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
         <v>8.6</v>
@@ -3299,7 +3299,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
         <v>6.4</v>
@@ -3308,13 +3308,13 @@
         <v>3.05</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="BJ11" t="n">
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3332,7 +3332,7 @@
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3344,13 +3344,13 @@
         <v>4.7</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BV11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX11" t="n">
         <v>36</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>4.4</v>
@@ -3415,16 +3415,16 @@
         <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N12" t="n">
         <v>8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P12" t="n">
         <v>3.5</v>
@@ -3436,19 +3436,19 @@
         <v>2.02</v>
       </c>
       <c r="S12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X12" t="n">
         <v>120</v>
@@ -3466,7 +3466,7 @@
         <v>21</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
         <v>22</v>
@@ -3478,25 +3478,25 @@
         <v>19.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>48</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>5.7</v>
@@ -3505,64 +3505,64 @@
         <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT12" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS12" t="n">
+      <c r="AU12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA12" t="n">
         <v>7</v>
       </c>
-      <c r="AT12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="BB12" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA12" t="n">
+      <c r="BC12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD12" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH12" t="n">
         <v>6.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BJ12" t="n">
         <v>9</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -3651,52 +3651,52 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G13" t="n">
         <v>1.76</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="O13" t="n">
         <v>1.08</v>
       </c>
       <c r="P13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
         <v>1.24</v>
       </c>
       <c r="R13" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="S13" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="T13" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V13" t="n">
         <v>1.25</v>
@@ -3711,10 +3711,10 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
         <v>950</v>
@@ -3726,7 +3726,7 @@
         <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
         <v>500</v>
@@ -3738,7 +3738,7 @@
         <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
         <v>500</v>
@@ -3750,85 +3750,85 @@
         <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>44</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.96</v>
+        <v>2.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.92</v>
+        <v>4.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.94</v>
+        <v>2.26</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.8</v>
+        <v>2.34</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.62</v>
+        <v>4.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.86</v>
+        <v>4.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.6</v>
+        <v>3.95</v>
       </c>
       <c r="AY13" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.76</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.54</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.68</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.82</v>
+        <v>4.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
@@ -3840,31 +3840,31 @@
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="I14" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="J14" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
@@ -3935,28 +3935,28 @@
         <v>1.09</v>
       </c>
       <c r="P14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="T14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="U14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V14" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="W14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
         <v>950</v>
@@ -4007,22 +4007,22 @@
         <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO14" t="n">
         <v>15</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AQ14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR14" t="n">
         <v>6</v>
       </c>
-      <c r="AR14" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AS14" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
         <v>4.2</v>
@@ -4034,19 +4034,19 @@
         <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX14" t="n">
         <v>4.2</v>
       </c>
       <c r="AY14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>6.2</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="BB14" t="n">
         <v>4.2</v>
@@ -4058,16 +4058,16 @@
         <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="BF14" t="n">
         <v>4.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BI14" t="n">
         <v>4.8</v>
@@ -4076,59 +4076,59 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>1.54</v>
       </c>
       <c r="G15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H15" t="n">
         <v>5.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="K15" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L15" t="n">
         <v>1.23</v>
@@ -4186,31 +4186,31 @@
         <v>7.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R15" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="S15" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="T15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U15" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V15" t="n">
         <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X15" t="n">
         <v>38</v>
@@ -4222,7 +4222,7 @@
         <v>350</v>
       </c>
       <c r="AA15" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB15" t="n">
         <v>16</v>
@@ -4249,7 +4249,7 @@
         <v>120</v>
       </c>
       <c r="AJ15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK15" t="n">
         <v>15</v>
@@ -4258,61 +4258,61 @@
         <v>24</v>
       </c>
       <c r="AM15" t="n">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
         <v>5.1</v>
       </c>
       <c r="AO15" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AP15" t="n">
         <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AV15" t="n">
         <v>19.5</v>
       </c>
       <c r="AW15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY15" t="n">
         <v>9.4</v>
       </c>
-      <c r="AX15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BD15" t="n">
         <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF15" t="n">
         <v>4.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -4413,25 +4413,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M16" t="n">
         <v>1.14</v>
@@ -4440,28 +4440,28 @@
         <v>2.46</v>
       </c>
       <c r="O16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
         <v>1.7</v>
@@ -4473,49 +4473,49 @@
         <v>10.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
         <v>700</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>170</v>
       </c>
       <c r="AF16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG16" t="n">
         <v>14</v>
       </c>
-      <c r="AG16" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH16" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
         <v>700</v>
       </c>
       <c r="AJ16" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AL16" t="n">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="AM16" t="n">
         <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
         <v>700</v>
@@ -4530,13 +4530,13 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV16" t="n">
         <v>15</v>
@@ -4554,7 +4554,7 @@
         <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB16" t="n">
         <v>11.5</v>
@@ -4563,10 +4563,10 @@
         <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF16" t="n">
         <v>7.6</v>
@@ -4593,16 +4593,16 @@
         <v>10</v>
       </c>
       <c r="BN16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BP16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ16" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4611,32 +4611,32 @@
         <v>8.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -4667,61 +4667,61 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.99</v>
+        <v>1.39</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>2.92</v>
+        <v>1.69</v>
       </c>
       <c r="O17" t="n">
         <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.79</v>
+        <v>1.23</v>
       </c>
       <c r="X17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
         <v>950</v>
@@ -4748,7 +4748,7 @@
         <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH17" t="n">
         <v>950</v>
@@ -4775,70 +4775,70 @@
         <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.76</v>
+        <v>1.68</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.88</v>
+        <v>1.64</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.1</v>
+        <v>1.79</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.9</v>
+        <v>1.59</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.84</v>
+        <v>1.71</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.86</v>
+        <v>1.66</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.94</v>
+        <v>1.67</v>
       </c>
       <c r="AY17" t="n">
-        <v>2.94</v>
+        <v>1.64</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.94</v>
+        <v>1.75</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.98</v>
+        <v>1.67</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.3</v>
+        <v>1.69</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.68</v>
+        <v>1.68</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.56</v>
+        <v>1.79</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.56</v>
+        <v>1.67</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.98</v>
+        <v>1.67</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4850,25 +4850,25 @@
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -4921,88 +4921,88 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.05</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.98</v>
       </c>
       <c r="K18" t="n">
         <v>3.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="O18" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P18" t="n">
         <v>1.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
         <v>23</v>
@@ -5011,76 +5011,76 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
         <v>160</v>
       </c>
       <c r="AM18" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AN18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AP18" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AX18" t="n">
         <v>15</v>
       </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BB18" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BD18" t="n">
         <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BH18" t="n">
         <v>2.76</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -5187,37 +5187,37 @@
         <v>2.74</v>
       </c>
       <c r="J19" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="O19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q19" t="n">
         <v>2.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
         <v>1.79</v>
@@ -5229,19 +5229,19 @@
         <v>1.41</v>
       </c>
       <c r="X19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
         <v>44</v>
       </c>
       <c r="AB19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC19" t="n">
         <v>7.4</v>
@@ -5253,22 +5253,22 @@
         <v>40</v>
       </c>
       <c r="AF19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ19" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AK19" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
         <v>460</v>
@@ -5277,7 +5277,7 @@
         <v>500</v>
       </c>
       <c r="AN19" t="n">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AO19" t="n">
         <v>44</v>
@@ -5292,7 +5292,7 @@
         <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
@@ -5316,22 +5316,22 @@
         <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG19" t="n">
         <v>29</v>
@@ -5346,59 +5346,59 @@
         <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BR19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX19" t="n">
         <v>48</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ19" t="n">
         <v>55</v>
       </c>
       <c r="CA19" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -5429,82 +5429,82 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
         <v>3.45</v>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N20" t="n">
         <v>2.72</v>
       </c>
       <c r="O20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P20" t="n">
         <v>1.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA20" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB20" t="n">
         <v>7.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF20" t="n">
         <v>12.5</v>
@@ -5513,10 +5513,10 @@
         <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AJ20" t="n">
         <v>28</v>
@@ -5534,19 +5534,19 @@
         <v>27</v>
       </c>
       <c r="AO20" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT20" t="n">
         <v>5.9</v>
@@ -5555,104 +5555,104 @@
         <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>15</v>
+        <v>5.1</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>19.5</v>
+        <v>5.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF20" t="n">
         <v>5.3</v>
       </c>
-      <c r="BF20" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG20" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="BJ20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BP20" t="n">
         <v>17</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BT20" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -5683,82 +5683,82 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="H21" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.65</v>
       </c>
-      <c r="J21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="X21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB21" t="n">
         <v>970</v>
       </c>
-      <c r="Y21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AC21" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
         <v>970</v>
@@ -5767,10 +5767,10 @@
         <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ21" t="n">
         <v>40</v>
@@ -5779,100 +5779,100 @@
         <v>32</v>
       </c>
       <c r="AL21" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AR21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV21" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AW21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF21" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV21" t="n">
+      <c r="BG21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>10</v>
-      </c>
       <c r="BK21" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
@@ -5881,10 +5881,10 @@
         <v>7.6</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5896,7 +5896,7 @@
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H22" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I22" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="J22" t="n">
         <v>3.45</v>
@@ -5955,16 +5955,16 @@
         <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
         <v>2.16</v>
@@ -5973,22 +5973,22 @@
         <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
         <v>1.63</v>
       </c>
       <c r="U22" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
         <v>970</v>
@@ -6006,7 +6006,7 @@
         <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
         <v>970</v>
@@ -6033,43 +6033,43 @@
         <v>30</v>
       </c>
       <c r="AL22" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AM22" t="n">
         <v>85</v>
       </c>
       <c r="AN22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO22" t="n">
         <v>25</v>
       </c>
-      <c r="AO22" t="n">
-        <v>26</v>
-      </c>
       <c r="AP22" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="AQ22" t="n">
         <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="AY22" t="n">
         <v>9.199999999999999</v>
@@ -6078,37 +6078,37 @@
         <v>11.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.6</v>
+        <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH22" t="n">
         <v>3.9</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK22" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6120,7 +6120,7 @@
         <v>6.2</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
@@ -6132,10 +6132,10 @@
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>2.94</v>
+        <v>7.4</v>
       </c>
       <c r="BT22" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
         <v>5.1</v>
@@ -6150,7 +6150,7 @@
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.4</v>
+        <v>3.35</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -6194,16 +6194,16 @@
         <v>1.54</v>
       </c>
       <c r="G23" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="H23" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
         <v>4.7</v>
@@ -6212,46 +6212,46 @@
         <v>1.41</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
         <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T23" t="n">
         <v>2.12</v>
       </c>
       <c r="U23" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V23" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W23" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="X23" t="n">
         <v>16.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z23" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA23" t="n">
         <v>270</v>
@@ -6275,7 +6275,7 @@
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI23" t="n">
         <v>130</v>
@@ -6284,19 +6284,19 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
         <v>48</v>
       </c>
       <c r="AM23" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO23" t="n">
         <v>210</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>230</v>
       </c>
       <c r="AP23" t="n">
         <v>11.5</v>
@@ -6305,7 +6305,7 @@
         <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS23" t="n">
         <v>7.2</v>
@@ -6329,7 +6329,7 @@
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA23" t="n">
         <v>7</v>
@@ -6347,74 +6347,74 @@
         <v>7.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG23" t="n">
         <v>7.2</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ23" t="n">
         <v>11.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BP23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR23" t="n">
         <v>28</v>
       </c>
       <c r="BS23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CA23" t="n">
         <v>8.6</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -6445,230 +6445,230 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G24" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I24" t="n">
         <v>3.05</v>
       </c>
-      <c r="I24" t="n">
-        <v>3.5</v>
-      </c>
       <c r="J24" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="T24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U24" t="n">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>7</v>
-      </c>
       <c r="BZ24" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -6699,67 +6699,67 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="G25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H25" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I25" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K25" t="n">
         <v>3.25</v>
       </c>
       <c r="L25" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="M25" t="n">
         <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O25" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="R25" t="n">
         <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T25" t="n">
         <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V25" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X25" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z25" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AA25" t="n">
         <v>55</v>
@@ -6768,19 +6768,19 @@
         <v>970</v>
       </c>
       <c r="AC25" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>950</v>
@@ -6789,34 +6789,34 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL25" t="n">
         <v>80</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO25" t="n">
         <v>50</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT25" t="n">
         <v>7.2</v>
@@ -6825,40 +6825,40 @@
         <v>6.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>11.5</v>
+        <v>4.7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="BE25" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.65</v>
+        <v>5.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH25" t="n">
         <v>2.84</v>
@@ -6867,7 +6867,7 @@
         <v>2.32</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK25" t="n">
         <v>5.5</v>
@@ -6876,53 +6876,53 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.94</v>
+        <v>10</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>3.55</v>
+        <v>7.8</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>2.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT25" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>2.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>2.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="H2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.1</v>
       </c>
-      <c r="I2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.96</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
@@ -884,7 +884,7 @@
         <v>2.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P2" t="n">
         <v>1.61</v>
@@ -893,28 +893,28 @@
         <v>2.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -923,25 +923,25 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
         <v>950</v>
       </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
@@ -953,10 +953,10 @@
         <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>600</v>
@@ -965,7 +965,7 @@
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>7.8</v>
@@ -974,113 +974,113 @@
         <v>8.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
         <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="AY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.8</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
         <v>2.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="V3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
         <v>1.37</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z3" t="n">
         <v>16</v>
@@ -1177,34 +1177,34 @@
         <v>36</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
         <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ3" t="n">
         <v>70</v>
       </c>
       <c r="AK3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL3" t="n">
         <v>130</v>
@@ -1213,7 +1213,7 @@
         <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
         <v>27</v>
@@ -1222,73 +1222,73 @@
         <v>5.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF3" t="n">
         <v>7.6</v>
       </c>
-      <c r="BF3" t="n">
-        <v>7</v>
-      </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BH3" t="n">
         <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN3" t="n">
         <v>6.8</v>
@@ -1297,19 +1297,19 @@
         <v>4.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>46</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BU3" t="n">
         <v>4</v>
@@ -1318,23 +1318,23 @@
         <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX3" t="n">
         <v>38</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>36</v>
       </c>
       <c r="CA3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H4" t="n">
         <v>1.66</v>
       </c>
       <c r="I4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
@@ -1392,10 +1392,10 @@
         <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
         <v>2.16</v>
@@ -1410,7 +1410,7 @@
         <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V4" t="n">
         <v>2.36</v>
@@ -1419,7 +1419,7 @@
         <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
         <v>7.2</v>
@@ -1473,58 +1473,58 @@
         <v>13</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
         <v>7.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT4" t="n">
         <v>15.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY4" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
         <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE4" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>12</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.25</v>
@@ -1566,7 +1566,7 @@
         <v>4.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV4" t="n">
         <v>12</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
         <v>4.7</v>
@@ -1661,10 +1661,10 @@
         <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
         <v>1.27</v>
@@ -1727,7 +1727,7 @@
         <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>13.5</v>
@@ -1736,49 +1736,49 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU5" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7</v>
       </c>
       <c r="AV5" t="n">
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC5" t="n">
         <v>17</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>16</v>
       </c>
       <c r="BD5" t="n">
         <v>18</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="n">
         <v>3.7</v>
@@ -1802,7 +1802,7 @@
         <v>4.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP5" t="n">
         <v>13.5</v>
@@ -1811,22 +1811,22 @@
         <v>6</v>
       </c>
       <c r="BR5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -1873,88 +1873,88 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="G6" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="I6" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J6" t="n">
         <v>2.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N6" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="O6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>50</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
         <v>950</v>
@@ -1966,7 +1966,7 @@
         <v>420</v>
       </c>
       <c r="AK6" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
         <v>500</v>
@@ -1984,119 +1984,119 @@
         <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.56</v>
+        <v>3.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.66</v>
+        <v>6.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.59</v>
+        <v>2.4</v>
       </c>
       <c r="AT6" t="n">
         <v>4.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.75</v>
+        <v>7.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.59</v>
+        <v>2.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.48</v>
+        <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.78</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.6</v>
+        <v>2.42</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.59</v>
+        <v>2.42</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.84</v>
+        <v>2.44</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.24</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>6.2</v>
       </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN6" t="n">
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BO6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G7" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -2157,7 +2157,7 @@
         <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
         <v>2.26</v>
@@ -2169,22 +2169,22 @@
         <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
         <v>25</v>
@@ -2193,7 +2193,7 @@
         <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
@@ -2205,19 +2205,19 @@
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -2235,58 +2235,58 @@
         <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BC7" t="n">
         <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="n">
         <v>3.15</v>
@@ -2298,37 +2298,37 @@
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G8" t="n">
         <v>1.95</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
         <v>1.54</v>
@@ -2405,31 +2405,31 @@
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q8" t="n">
         <v>2.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
         <v>4.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
         <v>2.04</v>
@@ -2438,7 +2438,7 @@
         <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" t="n">
         <v>44</v>
@@ -2450,25 +2450,25 @@
         <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
         <v>24</v>
       </c>
       <c r="AE8" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF8" t="n">
         <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>28</v>
       </c>
       <c r="AI8" t="n">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
@@ -2477,7 +2477,7 @@
         <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
@@ -2489,22 +2489,22 @@
         <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
         <v>6.2</v>
@@ -2513,34 +2513,34 @@
         <v>7.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
         <v>7.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="n">
         <v>2.94</v>
@@ -2549,19 +2549,19 @@
         <v>2.36</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>9</v>
       </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BN8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
         <v>3.4</v>
@@ -2573,13 +2573,13 @@
         <v>5.9</v>
       </c>
       <c r="BR8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU8" t="n">
         <v>4.7</v>
@@ -2588,13 +2588,13 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
         <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.51</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.61</v>
+        <v>17.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.63</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AU9" t="n">
         <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.61</v>
+        <v>15.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.62</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.51</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.51</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.59</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.62</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.59</v>
+        <v>14.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.62</v>
+        <v>7.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.63</v>
+        <v>8.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.63</v>
+        <v>7.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.63</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -2889,40 +2889,40 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.66</v>
+        <v>4.6</v>
       </c>
       <c r="G10" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="I10" t="n">
-        <v>7.6</v>
+        <v>2.28</v>
       </c>
       <c r="J10" t="n">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="N10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O10" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
         <v>1.12</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="X10" t="n">
         <v>970</v>
@@ -2994,55 +2994,55 @@
         <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BF10" t="n">
         <v>1.55</v>
@@ -3051,68 +3051,68 @@
         <v>1.55</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Atletico Cearense</t>
+          <t>CF Atlet Tirol</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Piaui EC</t>
+          <t>Ferroviario</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="I11" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.5</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
-        <v>27</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>13.5</v>
+        <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="AD11" t="n">
-        <v>11.5</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>19.5</v>
+        <v>500</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
         <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
         <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.4</v>
+        <v>1.55</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.4</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,244 +3383,244 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>FC Atletico Cearense</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ymir</t>
+          <t>Piaui EC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.71</v>
+        <v>4.1</v>
       </c>
       <c r="G12" t="n">
-        <v>1.81</v>
+        <v>4.9</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>1.97</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>2.14</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y12" t="n">
         <v>8</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X12" t="n">
-        <v>120</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>85</v>
-      </c>
       <c r="Z12" t="n">
-        <v>120</v>
+        <v>12.5</v>
       </c>
       <c r="AA12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>900</v>
       </c>
-      <c r="AB12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>23</v>
-      </c>
       <c r="AK12" t="n">
-        <v>17</v>
+        <v>200</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>5.7</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA12" t="n">
         <v>8</v>
       </c>
-      <c r="AT12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ12" t="n">
+      <c r="BB12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK12" t="n">
         <v>5.7</v>
       </c>
-      <c r="BA12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>7.4</v>
+        <v>2.38</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.8</v>
+        <v>2.28</v>
       </c>
       <c r="BR12" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.7</v>
+        <v>2.32</v>
       </c>
       <c r="BT12" t="n">
-        <v>9.4</v>
+        <v>4.7</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="BV12" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.4</v>
+        <v>2.26</v>
       </c>
       <c r="BZ12" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.5</v>
+        <v>2.26</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -3642,67 +3642,67 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="G13" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="R13" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="T13" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="U13" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3711,177 +3711,177 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA13" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AC13" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AK13" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AL13" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO13" t="n">
         <v>4.4</v>
       </c>
-      <c r="AO13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY13" t="n">
+      <c r="BP13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA13" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,67 +3896,67 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J14" t="n">
         <v>5.4</v>
       </c>
-      <c r="G14" t="n">
+      <c r="K14" t="n">
         <v>6.4</v>
       </c>
-      <c r="H14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6.2</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="R14" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="T14" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>2.74</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>2.44</v>
       </c>
       <c r="X14" t="n">
         <v>950</v>
@@ -3968,174 +3968,174 @@
         <v>500</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
         <v>950</v>
       </c>
       <c r="AC14" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE14" t="n">
         <v>500</v>
       </c>
-      <c r="AE14" t="n">
-        <v>65</v>
-      </c>
       <c r="AF14" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AG14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK14" t="n">
-        <v>260</v>
+        <v>970</v>
       </c>
       <c r="AL14" t="n">
-        <v>120</v>
+        <v>970</v>
       </c>
       <c r="AM14" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>34</v>
+        <v>3.95</v>
       </c>
       <c r="AO14" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5</v>
+        <v>1.96</v>
       </c>
       <c r="AR14" t="n">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.2</v>
+        <v>1.98</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.8</v>
+        <v>1.92</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.2</v>
+        <v>1.99</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="BD14" t="n">
         <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="BF14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO14" t="n">
         <v>4.3</v>
       </c>
-      <c r="BG14" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
         <v>5.6</v>
       </c>
-      <c r="BU14" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.4</v>
+        <v>1.68</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.86</v>
+        <v>1.57</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.54</v>
+        <v>5.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.57</v>
+        <v>6.4</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>1.55</v>
       </c>
       <c r="J15" t="n">
         <v>5.1</v>
       </c>
       <c r="K15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X15" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>260</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA15" t="n">
         <v>5.5</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="BB15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
         <v>7.2</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="X15" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>350</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BN15" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="BP15" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
         <v>6.6</v>
       </c>
       <c r="BT15" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BV15" t="n">
-        <v>38</v>
+        <v>9.6</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BX15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BZ15" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.34</v>
+        <v>1.54</v>
       </c>
       <c r="G16" t="n">
-        <v>2.42</v>
+        <v>1.56</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>2.96</v>
+        <v>5.2</v>
       </c>
       <c r="K16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P16" t="n">
         <v>3.15</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.46</v>
-      </c>
       <c r="Q16" t="n">
-        <v>2.92</v>
+        <v>1.42</v>
       </c>
       <c r="R16" t="n">
-        <v>1.17</v>
+        <v>1.87</v>
       </c>
       <c r="S16" t="n">
-        <v>6.2</v>
+        <v>2.04</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>1.54</v>
       </c>
       <c r="U16" t="n">
-        <v>1.69</v>
+        <v>2.54</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7</v>
+        <v>2.78</v>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="Z16" t="n">
-        <v>27</v>
+        <v>350</v>
       </c>
       <c r="AA16" t="n">
         <v>700</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AF16" t="n">
         <v>14.5</v>
       </c>
       <c r="AG16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB16" t="n">
         <v>14</v>
       </c>
-      <c r="AH16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS16" t="n">
+      <c r="BC16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG16" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA16" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Peruvian Segunda Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sport Huancayo Res</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ayacucho Futbol Club</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.39</v>
+        <v>2.32</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>2.44</v>
       </c>
       <c r="H17" t="n">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="I17" t="n">
-        <v>44</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>3.15</v>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="N17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.69</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.11</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="X17" t="n">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB17" t="n">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>42</v>
+        <v>7.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AF17" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
         <v>950</v>
       </c>
       <c r="AI17" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>500</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>900</v>
-      </c>
       <c r="AK17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM17" t="n">
         <v>500</v>
       </c>
-      <c r="AL17" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>580</v>
-      </c>
       <c r="AN17" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO17" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.67</v>
+        <v>6.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.68</v>
+        <v>8.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.64</v>
+        <v>9.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.66</v>
+        <v>10</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.79</v>
+        <v>6.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.59</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.71</v>
+        <v>15.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.66</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.67</v>
+        <v>11.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.64</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.75</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.67</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.69</v>
+        <v>11.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.68</v>
+        <v>30</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.79</v>
+        <v>10.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.67</v>
+        <v>10.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Peruvian Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Huancayo Res</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ayacucho Futbol Club</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.84</v>
+        <v>1.99</v>
       </c>
       <c r="G18" t="n">
-        <v>2.96</v>
+        <v>2.28</v>
       </c>
       <c r="H18" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N18" t="n">
         <v>3.1</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.72</v>
-      </c>
       <c r="O18" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>5.7</v>
+        <v>3.55</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="X18" t="n">
-        <v>8.6</v>
+        <v>90</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="AD18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BN18" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BO18" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="BP18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.6</v>
+        <v>2</v>
       </c>
       <c r="BR18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="BT18" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BV18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>10</v>
+        <v>1.32</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,246 +5166,246 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="H19" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="I19" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P19" t="n">
         <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="R19" t="n">
         <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V19" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="X19" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG19" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
       </c>
       <c r="AI19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL19" t="n">
         <v>160</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK19" t="n">
+      <c r="AM19" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN19" t="n">
         <v>55</v>
       </c>
-      <c r="AL19" t="n">
-        <v>460</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>210</v>
-      </c>
       <c r="AO19" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AY19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BB19" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BC19" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="BE19" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BH19" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ19" t="n">
         <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>27</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
         <v>10.5</v>
       </c>
-      <c r="BN19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>9</v>
-      </c>
       <c r="BZ19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>2.84</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2</v>
+        <v>2.92</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="I20" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O20" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="R20" t="n">
         <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Y20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG20" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH20" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AK20" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AL20" t="n">
         <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AO20" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.6</v>
+        <v>15.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.3</v>
+        <v>44</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.3</v>
+        <v>40</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="BJ20" t="n">
         <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>2.26</v>
+        <v>11</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP20" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS20" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW20" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA20" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,239 +5674,239 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Club Deportes Santa Cruz</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54</v>
+        <v>2.24</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="I21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY21" t="n">
         <v>3.55</v>
       </c>
-      <c r="J21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AZ21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>14</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -5928,229 +5928,229 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Club Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="H22" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="I22" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="U22" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="X22" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA22" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AB22" t="n">
         <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF22" t="n">
         <v>970</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK22" t="n">
         <v>32</v>
       </c>
-      <c r="AF22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>30</v>
-      </c>
       <c r="AL22" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AP22" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN22" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU22" t="n">
+      <c r="BO22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>3.35</v>
+        <v>8</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,246 +6182,246 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.54</v>
       </c>
-      <c r="G23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="W23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X23" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK23" t="n">
         <v>6.8</v>
       </c>
-      <c r="I23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW23" t="n">
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
         <v>7</v>
       </c>
-      <c r="AX23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH23" t="n">
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
         <v>3.45</v>
       </c>
-      <c r="BI23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BT23" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="BU23" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>12.5</v>
+        <v>3.45</v>
       </c>
       <c r="BZ23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CA23" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,251 +6431,251 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.46</v>
+        <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="H24" t="n">
-        <v>2.86</v>
+        <v>6.2</v>
       </c>
       <c r="I24" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.55</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="V24" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>1.63</v>
+        <v>2.56</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO24" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,244 +6685,498 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="H25" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I25" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>2.72</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>1.55</v>
+        <v>2.44</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.66</v>
+        <v>1.63</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="S25" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="U25" t="n">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="V25" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="X25" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AA25" t="n">
         <v>55</v>
       </c>
       <c r="AB25" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG25" t="n">
         <v>15</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AH25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>44</v>
       </c>
-      <c r="AF25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>65</v>
-      </c>
       <c r="AK25" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AL25" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="AN25" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AO25" t="n">
-        <v>50</v>
+        <v>19.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="AR25" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="BA25" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BH25" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="BJ25" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN25" t="n">
         <v>6.2</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-01 05:18:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
         <v>7.8</v>
       </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>2026-06-01 03:10:36</t>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>9</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
@@ -875,73 +875,73 @@
         <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.5</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.52</v>
-      </c>
       <c r="X2" t="n">
-        <v>9.6</v>
+        <v>90</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH2" t="n">
         <v>950</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>500</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
@@ -953,7 +953,7 @@
         <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
@@ -965,122 +965,122 @@
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.4</v>
+        <v>1.61</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>1.74</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>3.85</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>32</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.8</v>
+        <v>1.66</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>1.74</v>
       </c>
       <c r="BB2" t="n">
-        <v>38</v>
+        <v>1.73</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.6</v>
+        <v>1.74</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.4</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>1.75</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>38</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
         <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
         <v>5.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.6</v>
+        <v>1.63</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.5</v>
+        <v>1.73</v>
       </c>
       <c r="AS3" t="n">
-        <v>7</v>
+        <v>1.74</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.1</v>
+        <v>1.64</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>1.71</v>
       </c>
       <c r="AX3" t="n">
-        <v>19.5</v>
+        <v>1.75</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>1.74</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>1.66</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>1.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>1.75</v>
       </c>
       <c r="BC3" t="n">
-        <v>8</v>
+        <v>1.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>1.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.6</v>
+        <v>1.77</v>
       </c>
       <c r="BG3" t="n">
-        <v>21</v>
+        <v>1.66</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1392,61 +1392,61 @@
         <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
         <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
         <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="V4" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X4" t="n">
         <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AB4" t="n">
-        <v>40</v>
+        <v>17.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
         <v>10.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AG4" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
         <v>42</v>
@@ -1470,125 +1470,125 @@
         <v>700</v>
       </c>
       <c r="AO4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT4" t="n">
         <v>14.5</v>
       </c>
-      <c r="AT4" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="AZ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
         <v>12.5</v>
       </c>
-      <c r="BA4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BN4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BT4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
@@ -1637,7 +1637,7 @@
         <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
@@ -1646,139 +1646,139 @@
         <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.5</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>16</v>
+        <v>2.04</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.800000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>15</v>
+        <v>2.1</v>
       </c>
       <c r="AW5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC5" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AX5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>17</v>
-      </c>
       <c r="BD5" t="n">
-        <v>18</v>
+        <v>2.04</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.800000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>3.15</v>
       </c>
       <c r="BG5" t="n">
-        <v>11</v>
+        <v>2.06</v>
       </c>
       <c r="BH5" t="n">
         <v>3.7</v>
@@ -1802,7 +1802,7 @@
         <v>4.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP5" t="n">
         <v>13.5</v>
@@ -1820,7 +1820,7 @@
         <v>8.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -1873,58 +1873,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.6</v>
       </c>
-      <c r="K6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.52</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
         <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -1990,7 +1990,7 @@
         <v>6.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AT6" t="n">
         <v>4.9</v>
@@ -2002,10 +2002,10 @@
         <v>7.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY6" t="n">
         <v>6.2</v>
@@ -2014,22 +2014,22 @@
         <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.44</v>
+        <v>1.91</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="BG6" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>3.3</v>
       </c>
       <c r="G7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I7" t="n">
         <v>2.52</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -2169,37 +2169,37 @@
         <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V7" t="n">
         <v>1.66</v>
       </c>
       <c r="W7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AB7" t="n">
         <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -2211,7 +2211,7 @@
         <v>14.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -2220,7 +2220,7 @@
         <v>500</v>
       </c>
       <c r="AK7" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AL7" t="n">
         <v>500</v>
@@ -2232,125 +2232,125 @@
         <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AY7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
         <v>6.6</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>9</v>
-      </c>
       <c r="BT7" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -2381,28 +2381,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
         <v>2.78</v>
@@ -2411,136 +2411,136 @@
         <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>1.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>1.99</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>2.32</v>
       </c>
       <c r="BA8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>21</v>
+        <v>2.28</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.4</v>
+        <v>1.99</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>16.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="BH8" t="n">
         <v>2.94</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
@@ -2656,7 +2656,7 @@
         <v>1.64</v>
       </c>
       <c r="M9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
         <v>2.3</v>
@@ -2665,200 +2665,200 @@
         <v>1.63</v>
       </c>
       <c r="P9" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>17.5</v>
+        <v>2.84</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.7</v>
+        <v>3.85</v>
       </c>
       <c r="AU9" t="n">
         <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16.5</v>
+        <v>2.92</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>2.84</v>
       </c>
       <c r="BC9" t="n">
-        <v>14.5</v>
+        <v>1.72</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>1.63</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.4</v>
+        <v>1.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.6</v>
+        <v>2.74</v>
       </c>
       <c r="G10" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I10" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="J10" t="n">
         <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.67</v>
@@ -2913,19 +2913,19 @@
         <v>1.15</v>
       </c>
       <c r="N10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Q10" t="n">
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
         <v>6.2</v>
@@ -2937,7 +2937,7 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="W10" t="n">
         <v>1.21</v>
@@ -2952,13 +2952,13 @@
         <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
@@ -2976,143 +2976,143 @@
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM10" t="n">
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.24</v>
+        <v>3.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.32</v>
+        <v>3.85</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.36</v>
+        <v>2.66</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.36</v>
+        <v>4.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.32</v>
+        <v>4.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.29</v>
+        <v>2.22</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CF Atlet Tirol</t>
+          <t>Centro de Formacao de Atletas Tirol</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3155,7 +3155,7 @@
         <v>2.44</v>
       </c>
       <c r="J11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
@@ -3167,7 +3167,7 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
         <v>1.5</v>
@@ -3179,7 +3179,7 @@
         <v>2.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -3251,52 +3251,52 @@
         <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BF11" t="n">
         <v>1.55</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -3397,100 +3397,100 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="G12" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="I12" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="K12" t="n">
         <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
         <v>2.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V12" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="W12" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="Y12" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AA12" t="n">
-        <v>27</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AD12" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
         <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3502,125 +3502,125 @@
         <v>600</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>1.66</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.3</v>
+        <v>1.65</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.8</v>
+        <v>1.73</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.5</v>
+        <v>1.77</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.1</v>
+        <v>1.66</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.8</v>
+        <v>1.76</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.2</v>
+        <v>1.77</v>
       </c>
       <c r="AY12" t="n">
-        <v>6.2</v>
+        <v>1.72</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.6</v>
+        <v>1.72</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.6</v>
+        <v>1.79</v>
       </c>
       <c r="BC12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.4</v>
+        <v>1.79</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.4</v>
+        <v>1.79</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.4</v>
+        <v>1.75</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
         <v>4.5</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.2</v>
@@ -3675,10 +3675,10 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P13" t="n">
         <v>3.6</v>
@@ -3690,13 +3690,13 @@
         <v>2.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="T13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
         <v>1.28</v>
@@ -3711,170 +3711,170 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AO13" t="n">
-        <v>21</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.4</v>
+        <v>1.95</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8</v>
+        <v>1.99</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.4</v>
+        <v>1.96</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.199999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="AT13" t="n">
-        <v>15.5</v>
+        <v>1.95</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.9</v>
+        <v>2.18</v>
       </c>
       <c r="AV13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.6</v>
+        <v>1.94</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.6</v>
+        <v>1.93</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.2</v>
+        <v>2.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>8</v>
+        <v>1.99</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>1.94</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.4</v>
+        <v>1.91</v>
       </c>
       <c r="BD13" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.3</v>
+        <v>1.71</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>2.02</v>
       </c>
       <c r="BH13" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -3905,61 +3905,61 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
         <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="K14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.07</v>
       </c>
       <c r="P14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q14" t="n">
         <v>1.23</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="S14" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="T14" t="n">
         <v>1.36</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y14" t="n">
         <v>950</v>
@@ -3995,7 +3995,7 @@
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
         <v>970</v>
@@ -4007,128 +4007,128 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.95</v>
+        <v>29</v>
       </c>
       <c r="AO14" t="n">
         <v>970</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.96</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.96</v>
+        <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.98</v>
+        <v>7.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BG14" t="n">
         <v>2</v>
       </c>
-      <c r="AW14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J15" t="n">
         <v>5.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.1</v>
       </c>
       <c r="K15" t="n">
         <v>6.2</v>
@@ -4183,16 +4183,16 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P15" t="n">
         <v>4.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R15" t="n">
         <v>2.28</v>
@@ -4201,25 +4201,25 @@
         <v>1.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V15" t="n">
         <v>2.88</v>
       </c>
-      <c r="V15" t="n">
-        <v>2.78</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="n">
         <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
@@ -4228,10 +4228,10 @@
         <v>950</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
         <v>65</v>
@@ -4264,22 +4264,22 @@
         <v>600</v>
       </c>
       <c r="AO15" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
@@ -4288,37 +4288,37 @@
         <v>7</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AX15" t="n">
         <v>4.2</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD15" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BE15" t="n">
-        <v>5</v>
+        <v>2.28</v>
       </c>
       <c r="BF15" t="n">
         <v>4.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.35</v>
+        <v>1.9</v>
       </c>
       <c r="BH15" t="n">
         <v>7</v>
@@ -4327,7 +4327,7 @@
         <v>4.9</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK15" t="n">
         <v>4.4</v>
@@ -4336,25 +4336,25 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT15" t="n">
         <v>5.6</v>
@@ -4363,16 +4363,16 @@
         <v>4</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>8</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G16" t="n">
         <v>1.56</v>
@@ -4428,7 +4428,7 @@
         <v>5.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.23</v>
@@ -4437,19 +4437,19 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.13</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R16" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S16" t="n">
         <v>2.04</v>
@@ -4458,7 +4458,7 @@
         <v>1.54</v>
       </c>
       <c r="U16" t="n">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
         <v>1.2</v>
@@ -4467,176 +4467,176 @@
         <v>2.78</v>
       </c>
       <c r="X16" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="Y16" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="Z16" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
         <v>700</v>
       </c>
       <c r="AB16" t="n">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="AC16" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF16" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AI16" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17.5</v>
+        <v>46</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AL16" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>5.1</v>
+        <v>15</v>
       </c>
       <c r="AO16" t="n">
-        <v>40</v>
+        <v>700</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AT16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV16" t="n">
         <v>13</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AW16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD16" t="n">
         <v>11.5</v>
       </c>
-      <c r="AV16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>20</v>
-      </c>
       <c r="BE16" t="n">
-        <v>20</v>
+        <v>3.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -4667,64 +4667,64 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="H17" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="M17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O17" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="P17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="R17" t="n">
         <v>1.17</v>
       </c>
       <c r="S17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
         <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="X17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z17" t="n">
         <v>48</v>
@@ -4733,164 +4733,164 @@
         <v>700</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>700</v>
       </c>
       <c r="AF17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AI17" t="n">
         <v>700</v>
       </c>
       <c r="AJ17" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AL17" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
         <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AO17" t="n">
         <v>700</v>
       </c>
       <c r="AP17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB17" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="BC17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE17" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="BI17" t="n">
         <v>2.2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>6.6</v>
       </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BN17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -4921,61 +4921,61 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H18" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
         <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X18" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y18" t="n">
         <v>970</v>
@@ -4999,7 +4999,7 @@
         <v>500</v>
       </c>
       <c r="AF18" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG18" t="n">
         <v>500</v>
@@ -5023,128 +5023,128 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AO18" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AS18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>2.56</v>
       </c>
-      <c r="AT18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.88</v>
-      </c>
       <c r="BA18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="BC18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD18" t="n">
         <v>2.36</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BE18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI18" t="n">
         <v>2.54</v>
       </c>
-      <c r="BE18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BN18" t="n">
         <v>5</v>
       </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BO18" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -5175,64 +5175,64 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H19" t="n">
         <v>2.96</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.98</v>
       </c>
       <c r="I19" t="n">
         <v>3.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
         <v>3.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M19" t="n">
         <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O19" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P19" t="n">
         <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
         <v>1.81</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Z19" t="n">
         <v>18</v>
@@ -5241,40 +5241,40 @@
         <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>46</v>
+        <v>230</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL19" t="n">
         <v>75</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>160</v>
-      </c>
       <c r="AM19" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
         <v>55</v>
@@ -5283,31 +5283,31 @@
         <v>60</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ19" t="n">
         <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV19" t="n">
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AX19" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AY19" t="n">
         <v>12</v>
@@ -5319,86 +5319,86 @@
         <v>28</v>
       </c>
       <c r="BB19" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BC19" t="n">
         <v>36</v>
       </c>
       <c r="BD19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BE19" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BH19" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -5429,127 +5429,127 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G20" t="n">
         <v>2.84</v>
       </c>
-      <c r="G20" t="n">
-        <v>2.92</v>
-      </c>
       <c r="H20" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="I20" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
         <v>3.35</v>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="AA20" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB20" t="n">
         <v>8.6</v>
       </c>
       <c r="AC20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>460</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT20" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7.4</v>
       </c>
       <c r="AU20" t="n">
         <v>6.6</v>
@@ -5561,98 +5561,98 @@
         <v>34</v>
       </c>
       <c r="AX20" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>55</v>
+        <v>7.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BC20" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BE20" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG20" t="n">
-        <v>38</v>
+        <v>7.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.82</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT20" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -5683,25 +5683,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G21" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H21" t="n">
         <v>3.95</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M21" t="n">
         <v>1.12</v>
@@ -5710,10 +5710,10 @@
         <v>2.74</v>
       </c>
       <c r="O21" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q21" t="n">
         <v>2.58</v>
@@ -5722,191 +5722,191 @@
         <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U21" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
         <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>32</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>34</v>
       </c>
       <c r="AK21" t="n">
         <v>36</v>
       </c>
       <c r="AL21" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
         <v>32</v>
       </c>
       <c r="AO21" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.35</v>
+        <v>1.16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.5</v>
+        <v>1.16</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.1</v>
+        <v>1.16</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.6</v>
+        <v>1.16</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.05</v>
+        <v>1.16</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>1.85</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.85</v>
+        <v>1.1</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.6</v>
+        <v>1.16</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.1</v>
+        <v>1.16</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.1</v>
+        <v>1.12</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.2</v>
+        <v>1.13</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.6</v>
+        <v>1.16</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.8</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.6</v>
+        <v>1.16</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -5937,220 +5937,220 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G22" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I22" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -6194,13 +6194,13 @@
         <v>2.64</v>
       </c>
       <c r="G23" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H23" t="n">
         <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J23" t="n">
         <v>3.5</v>
@@ -6212,7 +6212,7 @@
         <v>1.35</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
         <v>4.4</v>
@@ -6233,7 +6233,7 @@
         <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U23" t="n">
         <v>2.3</v>
@@ -6242,13 +6242,13 @@
         <v>1.54</v>
       </c>
       <c r="W23" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X23" t="n">
         <v>970</v>
       </c>
       <c r="Y23" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z23" t="n">
         <v>24</v>
@@ -6257,43 +6257,43 @@
         <v>46</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH23" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AI23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AK23" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM23" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO23" t="n">
         <v>24</v>
@@ -6302,109 +6302,109 @@
         <v>13</v>
       </c>
       <c r="AQ23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT23" t="n">
         <v>10</v>
       </c>
-      <c r="AR23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AU23" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.1</v>
+        <v>19</v>
       </c>
       <c r="AX23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="BB23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>970</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>3.45</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -6448,19 +6448,19 @@
         <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H24" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.42</v>
@@ -6472,13 +6472,13 @@
         <v>3.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
         <v>1.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
         <v>1.33</v>
@@ -6487,188 +6487,188 @@
         <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V24" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X24" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y24" t="n">
         <v>22</v>
       </c>
       <c r="Z24" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA24" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM24" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AO24" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC24" t="n">
         <v>16</v>
       </c>
-      <c r="AR24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BD24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.6</v>
+        <v>1.33</v>
       </c>
       <c r="BF24" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.6</v>
+        <v>1.34</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BN24" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -6699,25 +6699,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G25" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H25" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="I25" t="n">
         <v>2.98</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M25" t="n">
         <v>1.04</v>
@@ -6738,13 +6738,13 @@
         <v>1.58</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T25" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="U25" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="V25" t="n">
         <v>1.5</v>
@@ -6753,176 +6753,176 @@
         <v>1.62</v>
       </c>
       <c r="X25" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>27</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>6.2</v>
-      </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G26" t="n">
         <v>3.05</v>
@@ -6962,43 +6962,43 @@
         <v>2.72</v>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J26" t="n">
         <v>3.15</v>
       </c>
       <c r="K26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L26" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M26" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="O26" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P26" t="n">
         <v>1.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
         <v>1.53</v>
@@ -7007,176 +7007,176 @@
         <v>1.48</v>
       </c>
       <c r="X26" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z26" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AA26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
         <v>970</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE26" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
         <v>22</v>
       </c>
       <c r="AG26" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.2</v>
+        <v>1.11</v>
       </c>
       <c r="AQ26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>2.46</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.57</v>
@@ -881,76 +881,76 @@
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
         <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="X2" t="n">
-        <v>90</v>
+        <v>9.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
@@ -962,125 +962,125 @@
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.61</v>
+        <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.74</v>
+        <v>16.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.85</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO2" t="n">
         <v>5.1</v>
       </c>
-      <c r="AX2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
-        <v>38</v>
+        <v>2.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
         <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.63</v>
+        <v>7.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.73</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.74</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.66</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.64</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.71</v>
+        <v>13.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.75</v>
+        <v>19.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.74</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.66</v>
+        <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.75</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.75</v>
+        <v>7.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.75</v>
+        <v>7.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.75</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.77</v>
+        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.66</v>
+        <v>21</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.45</v>
@@ -1392,10 +1392,10 @@
         <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
         <v>2.18</v>
@@ -1407,7 +1407,7 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
         <v>1.87</v>
@@ -1416,7 +1416,7 @@
         <v>2.24</v>
       </c>
       <c r="W4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>13</v>
@@ -1425,7 +1425,7 @@
         <v>7.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>19</v>
@@ -1440,19 +1440,19 @@
         <v>10.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AG4" t="n">
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ4" t="n">
         <v>900</v>
@@ -1494,10 +1494,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AY4" t="n">
         <v>19.5</v>
@@ -1506,10 +1506,10 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
         <v>10</v>
@@ -1518,10 +1518,10 @@
         <v>10</v>
       </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
         <v>11.5</v>
@@ -1530,7 +1530,7 @@
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1566,7 +1566,7 @@
         <v>4.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV4" t="n">
         <v>12.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="H5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I5" t="n">
         <v>4.2</v>
       </c>
-      <c r="I5" t="n">
-        <v>5.1</v>
-      </c>
       <c r="J5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.75</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.4</v>
@@ -1646,139 +1646,139 @@
         <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>27</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>280</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.04</v>
+        <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.1</v>
+        <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.08</v>
+        <v>15.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA5" t="n">
         <v>8.4</v>
       </c>
-      <c r="BA5" t="n">
-        <v>2.08</v>
-      </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.04</v>
+        <v>18.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.08</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.15</v>
+        <v>11.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.7</v>
@@ -1787,10 +1787,10 @@
         <v>2.96</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,34 +1799,34 @@
         <v>10</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1835,14 +1835,14 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K6" t="n">
         <v>2.76</v>
       </c>
-      <c r="I6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.82</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
         <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
         <v>1.56</v>
@@ -1906,13 +1906,13 @@
         <v>1.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T6" t="n">
         <v>1.82</v>
@@ -1921,13 +1921,13 @@
         <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
         <v>970</v>
@@ -1990,7 +1990,7 @@
         <v>6.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AT6" t="n">
         <v>4.9</v>
@@ -1999,10 +1999,10 @@
         <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AX6" t="n">
         <v>8.800000000000001</v>
@@ -2014,22 +2014,22 @@
         <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="BG6" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -2133,94 +2133,94 @@
         <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="U7" t="n">
         <v>1.97</v>
       </c>
       <c r="V7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
         <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD7" t="n">
         <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
         <v>14.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ7" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AK7" t="n">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="AL7" t="n">
         <v>500</v>
@@ -2229,7 +2229,7 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="AO7" t="n">
         <v>55</v>
@@ -2238,7 +2238,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
         <v>12.5</v>
@@ -2247,110 +2247,110 @@
         <v>21</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX7" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BB7" t="n">
         <v>42</v>
       </c>
       <c r="BC7" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BD7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BE7" t="n">
         <v>65</v>
       </c>
       <c r="BF7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BG7" t="n">
         <v>21</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW7" t="n">
         <v>7.6</v>
       </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -2381,52 +2381,52 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G8" t="n">
         <v>1.94</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
         <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
         <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
         <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
         <v>1.19</v>
@@ -2435,112 +2435,112 @@
         <v>2.06</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.99</v>
+        <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.99</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.02</v>
+        <v>7.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.3</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.32</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.28</v>
+        <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.99</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.1</v>
+        <v>16.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="n">
         <v>2.94</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
@@ -2656,209 +2656,209 @@
         <v>1.64</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="O9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="R9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>2.26</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="AO9" t="n">
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK9" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AX9" t="n">
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU9" t="n">
         <v>5.6</v>
       </c>
-      <c r="AY9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -2889,91 +2889,91 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="G10" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="H10" t="n">
         <v>2.06</v>
       </c>
       <c r="I10" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="J10" t="n">
         <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.67</v>
       </c>
       <c r="M10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N10" t="n">
         <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="P10" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y10" t="n">
         <v>6.2</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X10" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>970</v>
-      </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>500</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AI10" t="n">
         <v>540</v>
@@ -2994,125 +2994,125 @@
         <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AQ10" t="n">
         <v>3.85</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.66</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU10" t="n">
         <v>4.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.22</v>
+        <v>5.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.69</v>
+        <v>7.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.92</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.87</v>
+        <v>6.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.76</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.77</v>
+        <v>8</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.76</v>
+        <v>7.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.77</v>
+        <v>8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.77</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.77</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BI10" t="n">
         <v>2</v>
       </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>2.44</v>
       </c>
       <c r="J11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
@@ -3176,7 +3176,7 @@
         <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R11" t="n">
         <v>1.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -3397,100 +3397,100 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="G12" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="I12" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="J12" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
         <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
         <v>2.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
         <v>1.84</v>
       </c>
       <c r="V12" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="W12" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X12" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>27</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AF12" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
         <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3502,125 +3502,125 @@
         <v>600</v>
       </c>
       <c r="AO12" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.66</v>
+        <v>5.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.65</v>
+        <v>5.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.73</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.77</v>
+        <v>5.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.66</v>
+        <v>5.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.76</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.77</v>
+        <v>7.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.72</v>
+        <v>6.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.72</v>
+        <v>6.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.79</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.79</v>
+        <v>8.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.79</v>
+        <v>8.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.79</v>
+        <v>8.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.75</v>
+        <v>6.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.2</v>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.11</v>
@@ -3687,194 +3687,194 @@
         <v>1.34</v>
       </c>
       <c r="R13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S13" t="n">
         <v>1.84</v>
       </c>
       <c r="T13" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="U13" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X13" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z13" t="n">
         <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AI13" t="n">
         <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK13" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AL13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM13" t="n">
         <v>500</v>
       </c>
-      <c r="AM13" t="n">
-        <v>580</v>
-      </c>
       <c r="AN13" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>600</v>
+        <v>21</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.95</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.99</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.96</v>
+        <v>7.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.02</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.95</v>
+        <v>17.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.18</v>
+        <v>11.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.95</v>
+        <v>16.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.94</v>
+        <v>16</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.93</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.2</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.99</v>
+        <v>14</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.94</v>
+        <v>18.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.91</v>
+        <v>13.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.95</v>
+        <v>17.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.38</v>
+        <v>18.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.71</v>
+        <v>4.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.02</v>
+        <v>17</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -3905,58 +3905,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="G14" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
         <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
         <v>5.6</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R14" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="S14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W14" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="X14" t="n">
         <v>500</v>
@@ -3968,13 +3968,13 @@
         <v>500</v>
       </c>
       <c r="AA14" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB14" t="n">
         <v>500</v>
       </c>
-      <c r="AB14" t="n">
-        <v>950</v>
-      </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
@@ -3995,10 +3995,10 @@
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK14" t="n">
         <v>500</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>970</v>
       </c>
       <c r="AL14" t="n">
         <v>970</v>
@@ -4007,7 +4007,7 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>29</v>
+        <v>3.75</v>
       </c>
       <c r="AO14" t="n">
         <v>970</v>
@@ -4016,7 +4016,7 @@
         <v>7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.98</v>
+        <v>22</v>
       </c>
       <c r="AR14" t="n">
         <v>6.6</v>
@@ -4025,110 +4025,110 @@
         <v>7.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.99</v>
+        <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.93</v>
+        <v>27</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.97</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.1</v>
+        <v>14.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.99</v>
+        <v>5.4</v>
       </c>
       <c r="BC14" t="n">
         <v>7.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.04</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.16</v>
+        <v>20</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.78</v>
+        <v>3.05</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="J15" t="n">
         <v>5.5</v>
@@ -4195,22 +4195,22 @@
         <v>1.27</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2.98</v>
       </c>
       <c r="V15" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
         <v>80</v>
@@ -4222,7 +4222,7 @@
         <v>970</v>
       </c>
       <c r="AA15" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="AB15" t="n">
         <v>950</v>
@@ -4231,10 +4231,10 @@
         <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
         <v>180</v>
@@ -4249,7 +4249,7 @@
         <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK15" t="n">
         <v>260</v>
@@ -4264,10 +4264,10 @@
         <v>600</v>
       </c>
       <c r="AO15" t="n">
-        <v>55</v>
+        <v>3.9</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ15" t="n">
         <v>9.800000000000001</v>
@@ -4282,7 +4282,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV15" t="n">
         <v>7</v>
@@ -4297,7 +4297,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BA15" t="n">
         <v>9.199999999999999</v>
@@ -4309,55 +4309,55 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15" t="n">
         <v>4.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="BH15" t="n">
         <v>7</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU15" t="n">
         <v>4</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G16" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="H16" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.23</v>
@@ -4443,7 +4443,7 @@
         <v>1.13</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q16" t="n">
         <v>1.41</v>
@@ -4452,191 +4452,191 @@
         <v>1.89</v>
       </c>
       <c r="S16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T16" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U16" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="X16" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="Y16" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="Z16" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AA16" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AB16" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>700</v>
+        <v>48</v>
       </c>
       <c r="AJ16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW16" t="n">
         <v>46</v>
       </c>
-      <c r="AK16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN16" t="n">
+      <c r="AX16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>15</v>
       </c>
-      <c r="AO16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO16" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
         <v>3.3</v>
@@ -4691,16 +4691,16 @@
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P17" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
         <v>1.17</v>
@@ -4712,34 +4712,34 @@
         <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="n">
         <v>700</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>700</v>
@@ -4751,16 +4751,16 @@
         <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AI17" t="n">
         <v>700</v>
       </c>
       <c r="AJ17" t="n">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="AK17" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AL17" t="n">
         <v>500</v>
@@ -4769,34 +4769,34 @@
         <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AO17" t="n">
         <v>700</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AQ17" t="n">
         <v>10</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX17" t="n">
         <v>9.199999999999999</v>
@@ -4805,92 +4805,92 @@
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN17" t="n">
         <v>4.7</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP17" t="n">
         <v>19</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -4921,37 +4921,37 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H18" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
         <v>3.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
         <v>1.47</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O18" t="n">
         <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
         <v>2.18</v>
@@ -4960,25 +4960,25 @@
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X18" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y18" t="n">
         <v>500</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>970</v>
       </c>
       <c r="Z18" t="n">
         <v>500</v>
@@ -4987,10 +4987,10 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC18" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD18" t="n">
         <v>970</v>
@@ -5002,7 +5002,7 @@
         <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AH18" t="n">
         <v>950</v>
@@ -5023,7 +5023,7 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AO18" t="n">
         <v>600</v>
@@ -5035,22 +5035,22 @@
         <v>7</v>
       </c>
       <c r="AR18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS18" t="n">
         <v>3.9</v>
       </c>
-      <c r="AS18" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AT18" t="n">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="AU18" t="n">
         <v>4.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.68</v>
+        <v>5.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="AX18" t="n">
         <v>6.2</v>
@@ -5059,28 +5059,28 @@
         <v>7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.56</v>
+        <v>7.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.64</v>
+        <v>11.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.2</v>
+        <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.36</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF18" t="n">
         <v>5.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="BH18" t="n">
         <v>3.15</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -5175,64 +5175,64 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G19" t="n">
         <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
         <v>1.13</v>
       </c>
       <c r="N19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.72</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.68</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
         <v>5.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X19" t="n">
-        <v>16.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="Z19" t="n">
         <v>18</v>
@@ -5241,34 +5241,34 @@
         <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="AD19" t="n">
         <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="AF19" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG19" t="n">
         <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AK19" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AL19" t="n">
         <v>75</v>
@@ -5283,122 +5283,122 @@
         <v>60</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AQ19" t="n">
         <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
         <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX19" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>20</v>
       </c>
       <c r="BA19" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP19" t="n">
         <v>28</v>
       </c>
-      <c r="BB19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD19" t="n">
+      <c r="BQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS19" t="n">
         <v>12</v>
       </c>
-      <c r="BE19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>40</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G20" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H20" t="n">
         <v>2.96</v>
@@ -5444,7 +5444,7 @@
         <v>3.15</v>
       </c>
       <c r="K20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L20" t="n">
         <v>1.58</v>
@@ -5453,28 +5453,28 @@
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R20" t="n">
         <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="T20" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="V20" t="n">
         <v>1.48</v>
@@ -5483,49 +5483,49 @@
         <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>9</v>
       </c>
       <c r="Y20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z20" t="n">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC20" t="n">
         <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>210</v>
+        <v>46</v>
       </c>
       <c r="AF20" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
         <v>50</v>
       </c>
       <c r="AK20" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AL20" t="n">
-        <v>460</v>
+        <v>70</v>
       </c>
       <c r="AM20" t="n">
         <v>200</v>
@@ -5534,125 +5534,125 @@
         <v>50</v>
       </c>
       <c r="AO20" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ20" t="n">
         <v>8</v>
       </c>
       <c r="AR20" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.1</v>
+        <v>48</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU20" t="n">
         <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AX20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.4</v>
+        <v>48</v>
       </c>
       <c r="BB20" t="n">
         <v>40</v>
       </c>
       <c r="BC20" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="BD20" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.8</v>
+        <v>85</v>
       </c>
       <c r="BF20" t="n">
         <v>38</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>46</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -5683,34 +5683,34 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
         <v>1.12</v>
       </c>
       <c r="N21" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O21" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P21" t="n">
         <v>1.58</v>
@@ -5719,194 +5719,194 @@
         <v>2.58</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
         <v>5.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="V21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="X21" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF21" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ21" t="n">
         <v>32</v>
       </c>
       <c r="AK21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN21" t="n">
         <v>32</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.16</v>
+        <v>6</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.85</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.1</v>
+        <v>15.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.16</v>
+        <v>4.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.16</v>
+        <v>22</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.12</v>
+        <v>22</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.13</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.16</v>
+        <v>4.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.16</v>
+        <v>4.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>22</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H22" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
@@ -5961,16 +5961,16 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
         <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
         <v>1.3</v>
@@ -5979,178 +5979,178 @@
         <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W22" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G23" t="n">
         <v>2.8</v>
       </c>
       <c r="H23" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I23" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J23" t="n">
         <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
         <v>1.35</v>
@@ -6227,61 +6227,61 @@
         <v>1.79</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U23" t="n">
         <v>2.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W23" t="n">
         <v>1.56</v>
       </c>
       <c r="X23" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y23" t="n">
         <v>16</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AB23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC23" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
         <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF23" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI23" t="n">
         <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK23" t="n">
         <v>34</v>
@@ -6296,115 +6296,115 @@
         <v>25</v>
       </c>
       <c r="AO23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP23" t="n">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="AR23" t="n">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
         <v>10</v>
       </c>
-      <c r="AU23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO23" t="n">
-        <v>2.92</v>
+        <v>4.5</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H24" t="n">
         <v>6.8</v>
@@ -6460,7 +6460,7 @@
         <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.42</v>
@@ -6469,76 +6469,76 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R24" t="n">
         <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V24" t="n">
         <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X24" t="n">
         <v>17.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB24" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF24" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
         <v>46</v>
@@ -6547,22 +6547,22 @@
         <v>200</v>
       </c>
       <c r="AN24" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.32</v>
+        <v>7.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.34</v>
+        <v>6.8</v>
       </c>
       <c r="AT24" t="n">
         <v>6.4</v>
@@ -6571,104 +6571,104 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.35</v>
+        <v>22</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.35</v>
+        <v>6.8</v>
       </c>
       <c r="AX24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA24" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.34</v>
-      </c>
       <c r="BB24" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC24" t="n">
         <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.33</v>
+        <v>6.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.34</v>
+        <v>6.8</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS24" t="n">
         <v>10</v>
       </c>
-      <c r="BN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -6699,230 +6699,230 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="H25" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="I25" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="J25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K25" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L25" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M25" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="R25" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="S25" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK25" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>2.84</v>
+        <v>4.1</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS25" t="n">
-        <v>2.38</v>
+        <v>7.6</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW25" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BX25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY25" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -6953,28 +6953,28 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I26" t="n">
         <v>2.92</v>
       </c>
-      <c r="G26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.88</v>
-      </c>
       <c r="J26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N26" t="n">
         <v>2.84</v>
@@ -6983,10 +6983,10 @@
         <v>1.52</v>
       </c>
       <c r="P26" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R26" t="n">
         <v>1.22</v>
@@ -6995,188 +6995,188 @@
         <v>5.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V26" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W26" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X26" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB26" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.11</v>
+        <v>7.2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.72</v>
+        <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.11</v>
+        <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.06</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.11</v>
+        <v>17.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.11</v>
+        <v>5.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.05</v>
+        <v>5.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.05</v>
+        <v>5.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.05</v>
+        <v>5.6</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BR26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
         <v>7.6</v>
       </c>
-      <c r="BT26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,28 +857,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="G2" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
         <v>2.8</v>
@@ -890,133 +890,133 @@
         <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="V2" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="W2" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR2" t="n">
         <v>15.5</v>
       </c>
-      <c r="AA2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AS2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW2" t="n">
         <v>36</v>
       </c>
-      <c r="AF2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO2" t="n">
+      <c r="AX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA2" t="n">
         <v>38</v>
       </c>
-      <c r="AP2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY2" t="n">
+      <c r="BB2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE2" t="n">
         <v>13.5</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF2" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BH2" t="n">
         <v>2.86</v>
@@ -1034,53 +1034,53 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BP2" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
         <v>48</v>
       </c>
       <c r="CA2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1111,61 +1111,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
         <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V3" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
         <v>9.6</v>
@@ -1174,13 +1174,13 @@
         <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
@@ -1189,22 +1189,22 @@
         <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
         <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
         <v>110</v>
       </c>
       <c r="AK3" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
@@ -1216,13 +1216,13 @@
         <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>12.5</v>
@@ -1231,82 +1231,82 @@
         <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="AX3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP3" t="n">
         <v>32</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>5.4</v>
@@ -1315,26 +1315,26 @@
         <v>4</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX3" t="n">
         <v>38</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.45</v>
@@ -1389,52 +1389,52 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
         <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>1.87</v>
       </c>
       <c r="V4" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X4" t="n">
         <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB4" t="n">
         <v>17.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>10.5</v>
@@ -1449,7 +1449,7 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AI4" t="n">
         <v>95</v>
@@ -1458,10 +1458,10 @@
         <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AL4" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
@@ -1470,7 +1470,7 @@
         <v>700</v>
       </c>
       <c r="AO4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1479,13 +1479,13 @@
         <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
         <v>7.4</v>
@@ -1494,7 +1494,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX4" t="n">
         <v>24</v>
@@ -1512,55 +1512,55 @@
         <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG4" t="n">
         <v>11.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN4" t="n">
         <v>9.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
         <v>11</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>11.5</v>
       </c>
       <c r="BT4" t="n">
         <v>4.2</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
         <v>2.08</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.12</v>
-      </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
         <v>3.75</v>
@@ -1649,64 +1649,64 @@
         <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
         <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
         <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB5" t="n">
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
         <v>25</v>
@@ -1715,79 +1715,79 @@
         <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
         <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>280</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>15.5</v>
       </c>
-      <c r="AX5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>14</v>
-      </c>
       <c r="BA5" t="n">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="BB5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.6</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
         <v>11.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
         <v>5.1</v>
@@ -1796,28 +1796,28 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO5" t="n">
         <v>4.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU5" t="n">
         <v>4.5</v>
@@ -1832,17 +1832,17 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="K6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="L6" t="n">
         <v>1.62</v>
@@ -1897,7 +1897,7 @@
         <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
         <v>1.56</v>
@@ -1906,28 +1906,28 @@
         <v>1.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="T6" t="n">
         <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
         <v>970</v>
@@ -1990,7 +1990,7 @@
         <v>6.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AT6" t="n">
         <v>4.9</v>
@@ -2002,7 +2002,7 @@
         <v>6.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AX6" t="n">
         <v>8.800000000000001</v>
@@ -2014,25 +2014,25 @@
         <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BG6" t="n">
-        <v>5</v>
+        <v>1.63</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H7" t="n">
         <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -2154,10 +2154,10 @@
         <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
         <v>2.3</v>
@@ -2169,13 +2169,13 @@
         <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
         <v>1.97</v>
       </c>
       <c r="V7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W7" t="n">
         <v>1.4</v>
@@ -2184,13 +2184,13 @@
         <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AB7" t="n">
         <v>10.5</v>
@@ -2202,7 +2202,7 @@
         <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
@@ -2214,7 +2214,7 @@
         <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>230</v>
@@ -2229,22 +2229,22 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
         <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AT7" t="n">
         <v>9.800000000000001</v>
@@ -2274,19 +2274,19 @@
         <v>42</v>
       </c>
       <c r="BC7" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BD7" t="n">
         <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="BF7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH7" t="n">
         <v>3.05</v>
@@ -2298,13 +2298,13 @@
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11.5</v>
+        <v>130</v>
       </c>
       <c r="BN7" t="n">
         <v>6.6</v>
@@ -2313,7 +2313,7 @@
         <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ7" t="n">
         <v>8.800000000000001</v>
@@ -2322,7 +2322,7 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
         <v>5.4</v>
@@ -2334,23 +2334,23 @@
         <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G8" t="n">
         <v>1.94</v>
@@ -2405,10 +2405,10 @@
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
         <v>1.62</v>
@@ -2417,7 +2417,7 @@
         <v>2.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
         <v>4.9</v>
@@ -2447,7 +2447,7 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC8" t="n">
         <v>8.6</v>
@@ -2498,7 +2498,7 @@
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
         <v>5.4</v>
@@ -2510,7 +2510,7 @@
         <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
         <v>8.199999999999999</v>
@@ -2522,7 +2522,7 @@
         <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB8" t="n">
         <v>17.5</v>
@@ -2531,16 +2531,16 @@
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>28</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>130</v>
       </c>
       <c r="BF8" t="n">
         <v>16.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="n">
         <v>2.94</v>
@@ -2552,19 +2552,19 @@
         <v>13</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9</v>
+        <v>160</v>
       </c>
       <c r="BN8" t="n">
         <v>4.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP8" t="n">
         <v>15.5</v>
@@ -2573,7 +2573,7 @@
         <v>5.9</v>
       </c>
       <c r="BR8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS8" t="n">
         <v>7.6</v>
@@ -2588,13 +2588,13 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -2635,40 +2635,40 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="H9" t="n">
         <v>3.85</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M9" t="n">
         <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="P9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
         <v>1.14</v>
@@ -2683,16 +2683,16 @@
         <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="X9" t="n">
         <v>7.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
         <v>30</v>
@@ -2731,7 +2731,7 @@
         <v>40</v>
       </c>
       <c r="AL9" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
@@ -2746,49 +2746,49 @@
         <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AS9" t="n">
         <v>8.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="BC9" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.800000000000001</v>
+        <v>160</v>
       </c>
       <c r="BF9" t="n">
         <v>7.6</v>
@@ -2806,19 +2806,19 @@
         <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="BN9" t="n">
         <v>5.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP9" t="n">
         <v>23</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -2889,31 +2889,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="G10" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H10" t="n">
         <v>2.06</v>
       </c>
       <c r="I10" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="J10" t="n">
         <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M10" t="n">
         <v>1.16</v>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O10" t="n">
         <v>1.69</v>
@@ -2922,25 +2922,25 @@
         <v>1.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
         <v>6.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="U10" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="V10" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="W10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X10" t="n">
         <v>7</v>
@@ -2949,19 +2949,19 @@
         <v>6.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
         <v>120</v>
@@ -2970,10 +2970,10 @@
         <v>60</v>
       </c>
       <c r="AG10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI10" t="n">
         <v>540</v>
@@ -2997,122 +2997,122 @@
         <v>150</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="AR10" t="n">
         <v>7</v>
       </c>
       <c r="AS10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>200</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>250</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ10" t="n">
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BA10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>1.96</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G11" t="n">
         <v>4.3</v>
@@ -3158,7 +3158,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
         <v>1.55</v>
@@ -3173,7 +3173,7 @@
         <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
         <v>2.56</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -3403,25 +3403,25 @@
         <v>4.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>2.18</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
         <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O12" t="n">
         <v>1.42</v>
@@ -3436,10 +3436,10 @@
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>3.85</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
         <v>1.84</v>
@@ -3448,7 +3448,7 @@
         <v>1.84</v>
       </c>
       <c r="W12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X12" t="n">
         <v>11</v>
@@ -3598,7 +3598,7 @@
         <v>4.7</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BV12" t="n">
         <v>16.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J13" t="n">
         <v>4.6</v>
       </c>
-      <c r="J13" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.2</v>
@@ -3681,28 +3681,28 @@
         <v>1.11</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S13" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="T13" t="n">
         <v>1.47</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X13" t="n">
         <v>500</v>
@@ -3717,19 +3717,19 @@
         <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
         <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
         <v>14</v>
@@ -3741,10 +3741,10 @@
         <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL13" t="n">
         <v>22</v>
@@ -3753,25 +3753,25 @@
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU13" t="n">
         <v>11.5</v>
@@ -3780,10 +3780,10 @@
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
@@ -3807,10 +3807,10 @@
         <v>18.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH13" t="n">
         <v>6.2</v>
@@ -3819,46 +3819,46 @@
         <v>4.7</v>
       </c>
       <c r="BJ13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP13" t="n">
         <v>11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR13" t="n">
         <v>17</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
@@ -3870,11 +3870,11 @@
         <v>9.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -3905,61 +3905,61 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
         <v>5.6</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="R14" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="S14" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="T14" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X14" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
         <v>950</v>
@@ -3968,13 +3968,13 @@
         <v>500</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC14" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
@@ -3998,7 +3998,7 @@
         <v>85</v>
       </c>
       <c r="AK14" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL14" t="n">
         <v>970</v>
@@ -4007,16 +4007,16 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AO14" t="n">
         <v>970</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="AQ14" t="n">
-        <v>22</v>
+        <v>1.65</v>
       </c>
       <c r="AR14" t="n">
         <v>6.6</v>
@@ -4025,49 +4025,49 @@
         <v>7.4</v>
       </c>
       <c r="AT14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB14" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.4</v>
       </c>
       <c r="BC14" t="n">
         <v>7.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.28</v>
+        <v>6.2</v>
       </c>
       <c r="BH14" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
         <v>6.8</v>
@@ -4082,25 +4082,25 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.5</v>
+        <v>28</v>
       </c>
       <c r="BN14" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
@@ -4112,30 +4112,30 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.66</v>
+        <v>4.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="CA14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.6</v>
+        <v>1.71</v>
       </c>
       <c r="G15" t="n">
-        <v>6.4</v>
+        <v>1.75</v>
       </c>
       <c r="H15" t="n">
-        <v>1.48</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.53</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="P15" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="R15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W15" t="n">
         <v>2.32</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="X15" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="Y15" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="Z15" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AA15" t="n">
-        <v>970</v>
+        <v>120</v>
       </c>
       <c r="AB15" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>180</v>
+        <v>16.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
-        <v>260</v>
+        <v>14.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="AM15" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AN15" t="n">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="AO15" t="n">
-        <v>3.9</v>
+        <v>28</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AT15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
       <c r="BK15" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.8</v>
+        <v>55</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS15" t="n">
         <v>7.6</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU15" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CA15" t="n">
         <v>6</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>5.5</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,239 +4404,239 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.57</v>
+        <v>7.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.61</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4</v>
+        <v>1.34</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>1.38</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="O16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.13</v>
       </c>
-      <c r="P16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.62</v>
-      </c>
       <c r="X16" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="Y16" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>160</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AF16" t="n">
         <v>140</v>
       </c>
-      <c r="AB16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17.5</v>
+        <v>270</v>
       </c>
       <c r="AK16" t="n">
-        <v>14.5</v>
+        <v>100</v>
       </c>
       <c r="AL16" t="n">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="AM16" t="n">
         <v>60</v>
       </c>
       <c r="AN16" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="AO16" t="n">
-        <v>36</v>
+        <v>2.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AQ16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR16" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="AS16" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AV16" t="n">
         <v>14.5</v>
       </c>
-      <c r="AU16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV16" t="n">
+      <c r="AW16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>20</v>
       </c>
-      <c r="AW16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>15</v>
-      </c>
       <c r="BA16" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="BB16" t="n">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.5</v>
+        <v>42</v>
       </c>
       <c r="BE16" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>16</v>
+        <v>2.42</v>
       </c>
       <c r="BH16" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="BI16" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BJ16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BK16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO16" t="n">
+      <c r="BW16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>6</v>
+      </c>
+      <c r="CA16" t="n">
         <v>4.3</v>
       </c>
-      <c r="BP16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>5.8</v>
-      </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>2.16</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
         <v>4.9</v>
@@ -4682,7 +4682,7 @@
         <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L17" t="n">
         <v>1.62</v>
@@ -4709,10 +4709,10 @@
         <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
         <v>1.26</v>
@@ -4736,10 +4736,10 @@
         <v>6.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>700</v>
@@ -4760,7 +4760,7 @@
         <v>44</v>
       </c>
       <c r="AK17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL17" t="n">
         <v>500</v>
@@ -4784,10 +4784,10 @@
         <v>27</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AU17" t="n">
         <v>6.4</v>
@@ -4796,7 +4796,7 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17" t="n">
         <v>9.199999999999999</v>
@@ -4808,7 +4808,7 @@
         <v>22</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>17</v>
@@ -4817,19 +4817,19 @@
         <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="BE17" t="n">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="BF17" t="n">
-        <v>25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BI17" t="n">
         <v>2.24</v>
@@ -4838,34 +4838,34 @@
         <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11.5</v>
+        <v>180</v>
       </c>
       <c r="BN17" t="n">
         <v>4.7</v>
       </c>
       <c r="BO17" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BP17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU17" t="n">
         <v>6.2</v>
@@ -4874,7 +4874,7 @@
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -4963,7 +4963,7 @@
         <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U18" t="n">
         <v>1.87</v>
@@ -5074,7 +5074,7 @@
         <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.4</v>
+        <v>95</v>
       </c>
       <c r="BF18" t="n">
         <v>5.5</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.4</v>
+        <v>120</v>
       </c>
       <c r="BN18" t="n">
         <v>5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="I19" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="J19" t="n">
         <v>2.98</v>
@@ -5193,7 +5193,7 @@
         <v>3.05</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
         <v>1.13</v>
@@ -5205,97 +5205,97 @@
         <v>1.55</v>
       </c>
       <c r="P19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
         <v>5.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
         <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="W19" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC19" t="n">
         <v>6.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
         <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ19" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AN19" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AO19" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AP19" t="n">
         <v>8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT19" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
         <v>6.4</v>
@@ -5304,101 +5304,101 @@
         <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AX19" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
         <v>20</v>
       </c>
       <c r="BA19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD19" t="n">
         <v>60</v>
       </c>
-      <c r="BB19" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>40</v>
-      </c>
       <c r="BE19" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="BF19" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BG19" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BH19" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="BJ19" t="n">
         <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>14.5</v>
+        <v>170</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP19" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BQ19" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR19" t="n">
         <v>55</v>
       </c>
       <c r="BS19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV19" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BW19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY19" t="n">
         <v>10</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>12</v>
       </c>
       <c r="BZ19" t="n">
         <v>55</v>
       </c>
       <c r="CA19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -5432,19 +5432,19 @@
         <v>2.76</v>
       </c>
       <c r="G20" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J20" t="n">
         <v>3.1</v>
       </c>
-      <c r="J20" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L20" t="n">
         <v>1.58</v>
@@ -5453,7 +5453,7 @@
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O20" t="n">
         <v>1.56</v>
@@ -5477,13 +5477,13 @@
         <v>1.78</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W20" t="n">
         <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y20" t="n">
         <v>8.800000000000001</v>
@@ -5492,10 +5492,10 @@
         <v>18.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC20" t="n">
         <v>7.2</v>
@@ -5516,7 +5516,7 @@
         <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
         <v>50</v>
@@ -5534,13 +5534,13 @@
         <v>50</v>
       </c>
       <c r="AO20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR20" t="n">
         <v>16.5</v>
@@ -5549,7 +5549,7 @@
         <v>48</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU20" t="n">
         <v>6.6</v>
@@ -5570,7 +5570,7 @@
         <v>21</v>
       </c>
       <c r="BA20" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BB20" t="n">
         <v>40</v>
@@ -5579,16 +5579,16 @@
         <v>36</v>
       </c>
       <c r="BD20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BE20" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="BF20" t="n">
         <v>38</v>
       </c>
       <c r="BG20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH20" t="n">
         <v>2.78</v>
@@ -5600,19 +5600,19 @@
         <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10.5</v>
+        <v>170</v>
       </c>
       <c r="BN20" t="n">
         <v>5.8</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP20" t="n">
         <v>27</v>
@@ -5624,16 +5624,16 @@
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT20" t="n">
         <v>6.2</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW20" t="n">
         <v>8.199999999999999</v>
@@ -5642,17 +5642,17 @@
         <v>55</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ20" t="n">
         <v>55</v>
       </c>
       <c r="CA20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G21" t="n">
         <v>2.12</v>
@@ -5692,13 +5692,13 @@
         <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
         <v>1.57</v>
@@ -5707,43 +5707,43 @@
         <v>1.12</v>
       </c>
       <c r="N21" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O21" t="n">
         <v>1.53</v>
       </c>
       <c r="P21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
         <v>120</v>
@@ -5752,67 +5752,67 @@
         <v>8.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE21" t="n">
         <v>80</v>
       </c>
       <c r="AF21" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI21" t="n">
         <v>110</v>
       </c>
       <c r="AJ21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK21" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM21" t="n">
         <v>240</v>
       </c>
       <c r="AN21" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO21" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.5</v>
+        <v>27</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.4</v>
+        <v>30</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
@@ -5821,34 +5821,34 @@
         <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BB21" t="n">
         <v>22</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
         <v>22</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ21" t="n">
         <v>12</v>
@@ -5860,7 +5860,7 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BN21" t="n">
         <v>4.5</v>
@@ -5869,13 +5869,13 @@
         <v>3.5</v>
       </c>
       <c r="BP21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS21" t="n">
         <v>11.5</v>
@@ -5902,18 +5902,18 @@
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,239 +5928,239 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Club Deportes Santa Cruz</t>
+          <t>Maguary</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Sousa EC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="G22" t="n">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="H22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J22" t="n">
         <v>3.3</v>
       </c>
-      <c r="I22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>1.69</v>
+        <v>2.14</v>
       </c>
       <c r="X22" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB22" t="n">
         <v>14</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="BC22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF22" t="n">
         <v>14</v>
       </c>
-      <c r="Z22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG22" t="n">
+      <c r="BG22" t="n">
+        <v>170</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ22" t="n">
         <v>13</v>
       </c>
-      <c r="AH22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN22" t="n">
+      <c r="BK22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
         <v>27</v>
       </c>
-      <c r="AO22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT22" t="n">
+      <c r="BT22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU22" t="n">
         <v>7</v>
       </c>
-      <c r="AU22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BV22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.8</v>
+        <v>48</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.6</v>
+        <v>60</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -6182,187 +6182,187 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Club Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="G23" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="H23" t="n">
-        <v>2.64</v>
+        <v>3.45</v>
       </c>
       <c r="I23" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.5</v>
       </c>
-      <c r="K23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="P23" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="V23" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="X23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH23" t="n">
         <v>22</v>
       </c>
-      <c r="Y23" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>970</v>
-      </c>
       <c r="AI23" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AJ23" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AK23" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO23" t="n">
         <v>55</v>
       </c>
-      <c r="AM23" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>21</v>
-      </c>
       <c r="AP23" t="n">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.7</v>
+        <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="BJ23" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6371,40 +6371,40 @@
         <v>10</v>
       </c>
       <c r="BN23" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BT23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,246 +6436,246 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.58</v>
+        <v>2.64</v>
       </c>
       <c r="G24" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="H24" t="n">
-        <v>6.8</v>
+        <v>2.64</v>
       </c>
       <c r="I24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X24" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU24" t="n">
         <v>4.5</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
         <v>14.5</v>
       </c>
-      <c r="BN24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>13</v>
-      </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="BZ24" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CA24" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,251 +6685,251 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.32</v>
+        <v>1.58</v>
       </c>
       <c r="G25" t="n">
-        <v>2.36</v>
+        <v>1.61</v>
       </c>
       <c r="H25" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="I25" t="n">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="X25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y25" t="n">
         <v>20</v>
       </c>
-      <c r="Y25" t="n">
-        <v>75</v>
-      </c>
       <c r="Z25" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AB25" t="n">
-        <v>15.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AD25" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AE25" t="n">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="AF25" t="n">
-        <v>550</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
         <v>12</v>
       </c>
-      <c r="AH25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS25" t="n">
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ25" t="n">
         <v>22</v>
       </c>
-      <c r="AT25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>27</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>20</v>
-      </c>
       <c r="CA25" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,244 +6939,752 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Marcilio</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Azuriz FC</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.82</v>
+        <v>1.53</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="H26" t="n">
-        <v>2.76</v>
+        <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.92</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="M26" t="n">
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="O26" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P26" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q26" t="n">
         <v>2.58</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="U26" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>1.51</v>
+        <v>2.66</v>
       </c>
       <c r="X26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.5</v>
+        <v>120</v>
       </c>
       <c r="AA26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="AE26" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH26" t="n">
         <v>48</v>
       </c>
-      <c r="AF26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>950</v>
-      </c>
       <c r="AI26" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="AJ26" t="n">
-        <v>65</v>
+        <v>16.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AL26" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM26" t="n">
-        <v>210</v>
+        <v>480</v>
       </c>
       <c r="AN26" t="n">
-        <v>65</v>
+        <v>16.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.5</v>
+        <v>200</v>
       </c>
       <c r="AX26" t="n">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.7</v>
+        <v>180</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.8</v>
+        <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>6</v>
+        <v>270</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="BI26" t="n">
         <v>2.32</v>
       </c>
       <c r="BJ26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BP26" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
         <v>7.8</v>
       </c>
       <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>28</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>21</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:43:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>19</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:43:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA28" t="n">
         <v>55</v>
       </c>
-      <c r="BS26" t="n">
+      <c r="AB28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP28" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BT26" t="n">
+      <c r="AQ28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT28" t="n">
         <v>5.9</v>
       </c>
-      <c r="BU26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW26" t="n">
+      <c r="BU28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
         <v>7.6</v>
       </c>
-      <c r="BX26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>2026-06-01 09:35:19</t>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-01.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="H2" t="n">
-        <v>2.88</v>
+        <v>3.95</v>
       </c>
       <c r="I2" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>2.24</v>
       </c>
       <c r="K2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S2" t="n">
+        <v>44</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X2" t="n">
         <v>3.15</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="Y2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB2" t="n">
         <v>5.2</v>
       </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AC2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>38</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>280</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="AH2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>470</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR2" t="n">
         <v>22</v>
       </c>
-      <c r="AI2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AS2" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="AW2" t="n">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>90</v>
       </c>
       <c r="BA2" t="n">
-        <v>38</v>
+        <v>290</v>
       </c>
       <c r="BB2" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="BC2" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="BD2" t="n">
-        <v>38</v>
+        <v>360</v>
       </c>
       <c r="BE2" t="n">
-        <v>13.5</v>
+        <v>350</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>1.06</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6</v>
+        <v>1.31</v>
       </c>
       <c r="H3" t="n">
-        <v>2.36</v>
+        <v>14.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2.68</v>
+        <v>680</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>5.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>250</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.38</v>
+        <v>4</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>24</v>
+        <v>5.5</v>
       </c>
       <c r="AG3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>80</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC3" t="n">
         <v>15</v>
       </c>
-      <c r="AH3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="BD3" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE3" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>630</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>32</v>
+        <v>800</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>2</v>
       </c>
       <c r="BR3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="BX3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="BZ3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1365,46 +1365,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="I4" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
@@ -1413,55 +1413,55 @@
         <v>1.87</v>
       </c>
       <c r="V4" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD4" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AA4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
         <v>110</v>
       </c>
       <c r="AG4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
         <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AL4" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
@@ -1470,125 +1470,125 @@
         <v>700</v>
       </c>
       <c r="AO4" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX4" t="n">
         <v>24</v>
       </c>
       <c r="AY4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AZ4" t="n">
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE4" t="n">
         <v>10.5</v>
       </c>
-      <c r="BD4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>11</v>
-      </c>
       <c r="BF4" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO4" t="n">
         <v>6</v>
       </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>12</v>
       </c>
-      <c r="BN4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV4" t="n">
         <v>11</v>
       </c>
-      <c r="BT4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BW4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1619,76 +1619,76 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
         <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V5" t="n">
         <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
         <v>17.5</v>
@@ -1697,40 +1697,40 @@
         <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR5" t="n">
         <v>27</v>
@@ -1739,16 +1739,16 @@
         <v>32</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
@@ -1766,37 +1766,37 @@
         <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
         <v>48</v>
       </c>
       <c r="BF5" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
         <v>4.9</v>
@@ -1805,44 +1805,44 @@
         <v>4.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT5" t="n">
         <v>8</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="G6" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="K6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.62</v>
@@ -1897,142 +1897,142 @@
         <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T6" t="n">
         <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AA6" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>6.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AJ6" t="n">
-        <v>420</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.63</v>
+        <v>30</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.63</v>
+        <v>28</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.64</v>
+        <v>28</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.64</v>
+        <v>28</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.64</v>
+        <v>25</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.65</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.65</v>
+        <v>46</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.64</v>
+        <v>16</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.63</v>
+        <v>15</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
@@ -2151,34 +2151,34 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
         <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V7" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
         <v>11.5</v>
@@ -2190,19 +2190,19 @@
         <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
@@ -2214,79 +2214,79 @@
         <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN7" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AO7" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AP7" t="n">
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY7" t="n">
         <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BC7" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BE7" t="n">
         <v>100</v>
       </c>
       <c r="BF7" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BG7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BH7" t="n">
         <v>3.05</v>
@@ -2298,7 +2298,7 @@
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,22 +2307,22 @@
         <v>130</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO7" t="n">
         <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT7" t="n">
         <v>5.4</v>
@@ -2334,23 +2334,23 @@
         <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.54</v>
@@ -2408,7 +2408,7 @@
         <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P8" t="n">
         <v>1.62</v>
@@ -2417,22 +2417,22 @@
         <v>2.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
         <v>4.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
         <v>10</v>
@@ -2450,10 +2450,10 @@
         <v>6.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
@@ -2462,10 +2462,10 @@
         <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
         <v>450</v>
@@ -2477,7 +2477,7 @@
         <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
@@ -2495,34 +2495,34 @@
         <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
         <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="AX8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="BB8" t="n">
         <v>17.5</v>
@@ -2531,7 +2531,7 @@
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BE8" t="n">
         <v>130</v>
@@ -2540,19 +2540,19 @@
         <v>16.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BI8" t="n">
         <v>2.36</v>
       </c>
       <c r="BJ8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2567,34 +2567,34 @@
         <v>3.45</v>
       </c>
       <c r="BP8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BR8" t="n">
         <v>40</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -2635,67 +2635,67 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
         <v>3.85</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N9" t="n">
         <v>2.28</v>
       </c>
       <c r="O9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="R9" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S9" t="n">
         <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X9" t="n">
         <v>7.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
@@ -2746,13 +2746,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>5.5</v>
@@ -2764,7 +2764,7 @@
         <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="AX9" t="n">
         <v>10.5</v>
@@ -2776,7 +2776,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
         <v>22</v>
@@ -2791,13 +2791,13 @@
         <v>160</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI9" t="n">
         <v>2.12</v>
@@ -2806,7 +2806,7 @@
         <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,47 +2818,47 @@
         <v>5.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BP9" t="n">
         <v>23</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -2889,37 +2889,37 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="G10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H10" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="I10" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J10" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N10" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="P10" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Q10" t="n">
         <v>3.05</v>
@@ -2934,46 +2934,46 @@
         <v>2.36</v>
       </c>
       <c r="U10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y10" t="n">
         <v>6.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
         <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
         <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AI10" t="n">
         <v>540</v>
@@ -2994,73 +2994,73 @@
         <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
         <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="BE10" t="n">
         <v>200</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="BH10" t="n">
         <v>2.52</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="BJ10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,50 +3069,50 @@
         <v>250</v>
       </c>
       <c r="BN10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -3143,46 +3143,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="G11" t="n">
         <v>4.3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="I11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3191,7 +3191,7 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W11" t="n">
         <v>1.32</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -3397,52 +3397,52 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I12" t="n">
         <v>2.18</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
         <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V12" t="n">
         <v>1.84</v>
@@ -3481,10 +3481,10 @@
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="n">
         <v>900</v>
@@ -3499,64 +3499,64 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="AY12" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BH12" t="n">
         <v>3.05</v>
@@ -3565,62 +3565,62 @@
         <v>2.66</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BN12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BT12" t="n">
         <v>4.7</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BV12" t="n">
         <v>16.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX12" t="n">
         <v>36</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BZ12" t="n">
         <v>36</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -3651,64 +3651,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="G13" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="S13" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="U13" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="W13" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="X13" t="n">
         <v>500</v>
       </c>
       <c r="Y13" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="Z13" t="n">
         <v>500</v>
@@ -3717,112 +3717,112 @@
         <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AE13" t="n">
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AM13" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AO13" t="n">
-        <v>24</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
         <v>11.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BC13" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
         <v>17.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG13" t="n">
         <v>17.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BI13" t="n">
         <v>4.7</v>
       </c>
       <c r="BJ13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3831,50 +3831,50 @@
         <v>42</v>
       </c>
       <c r="BN13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU13" t="n">
         <v>5.6</v>
       </c>
-      <c r="BO13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ13" t="n">
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CA13" t="n">
         <v>5.3</v>
       </c>
-      <c r="BR13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>4.9</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -3905,58 +3905,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="G14" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K14" t="n">
         <v>5.6</v>
       </c>
-      <c r="K14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O14" t="n">
         <v>1.05</v>
       </c>
       <c r="P14" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="R14" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="U14" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="X14" t="n">
         <v>950</v>
@@ -3971,13 +3971,13 @@
         <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC14" t="n">
         <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AE14" t="n">
         <v>500</v>
@@ -3995,7 +3995,7 @@
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
         <v>970</v>
@@ -4007,16 +4007,16 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AO14" t="n">
-        <v>970</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
         <v>75</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.65</v>
+        <v>4.3</v>
       </c>
       <c r="AR14" t="n">
         <v>6.6</v>
@@ -4025,46 +4025,46 @@
         <v>7.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV14" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV14" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>7.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC14" t="n">
         <v>7.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4085,10 +4085,10 @@
         <v>28</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4100,10 +4100,10 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU14" t="n">
         <v>5.6</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ14" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -4159,67 +4159,67 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H15" t="n">
         <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J15" t="n">
         <v>4.7</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.13</v>
       </c>
       <c r="P15" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S15" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="U15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X15" t="n">
         <v>36</v>
       </c>
       <c r="Y15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA15" t="n">
         <v>120</v>
@@ -4228,13 +4228,13 @@
         <v>17.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD15" t="n">
         <v>19.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF15" t="n">
         <v>16.5</v>
@@ -4243,7 +4243,7 @@
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
         <v>40</v>
@@ -4252,31 +4252,31 @@
         <v>21</v>
       </c>
       <c r="AK15" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AL15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM15" t="n">
         <v>55</v>
       </c>
       <c r="AN15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP15" t="n">
         <v>30</v>
       </c>
       <c r="AQ15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR15" t="n">
         <v>36</v>
       </c>
       <c r="AS15" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
@@ -4285,46 +4285,46 @@
         <v>11</v>
       </c>
       <c r="AV15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
         <v>38</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
         <v>34</v>
       </c>
       <c r="BB15" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC15" t="n">
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE15" t="n">
         <v>42</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ15" t="n">
         <v>8.800000000000001</v>
@@ -4369,20 +4369,20 @@
         <v>9</v>
       </c>
       <c r="BX15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="CA15" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>6</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="G16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="I16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K16" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>1.13</v>
@@ -4437,7 +4437,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.05</v>
@@ -4449,40 +4449,40 @@
         <v>1.19</v>
       </c>
       <c r="R16" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="S16" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T16" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="U16" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="V16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="Y16" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Z16" t="n">
         <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="AB16" t="n">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="AC16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AD16" t="n">
         <v>15</v>
@@ -4491,10 +4491,10 @@
         <v>13.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AG16" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AH16" t="n">
         <v>22</v>
@@ -4503,22 +4503,22 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AL16" t="n">
         <v>130</v>
       </c>
       <c r="AM16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AO16" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AP16" t="n">
         <v>60</v>
@@ -4527,64 +4527,64 @@
         <v>30</v>
       </c>
       <c r="AR16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="AU16" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AV16" t="n">
         <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF16" t="n">
         <v>20</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>21</v>
       </c>
       <c r="BG16" t="n">
         <v>2.42</v>
       </c>
       <c r="BH16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4596,47 +4596,47 @@
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>6</v>
-      </c>
       <c r="BT16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BW16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="CA16" t="n">
         <v>4.1</v>
       </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>6</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>4.3</v>
-      </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
         <v>1.62</v>
@@ -4694,70 +4694,70 @@
         <v>2.58</v>
       </c>
       <c r="O17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P17" t="n">
         <v>1.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R17" t="n">
         <v>1.17</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="X17" t="n">
         <v>8.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA17" t="n">
         <v>700</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>700</v>
       </c>
       <c r="AF17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG17" t="n">
         <v>12</v>
       </c>
-      <c r="AG17" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH17" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
         <v>700</v>
       </c>
       <c r="AJ17" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="n">
         <v>46</v>
@@ -4769,52 +4769,52 @@
         <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO17" t="n">
         <v>700</v>
       </c>
       <c r="AP17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU17" t="n">
         <v>7</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AV17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW17" t="n">
         <v>10</v>
       </c>
-      <c r="AR17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD17" t="n">
         <v>40</v>
@@ -4823,22 +4823,22 @@
         <v>140</v>
       </c>
       <c r="BF17" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH17" t="n">
         <v>2.72</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ17" t="n">
         <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4847,50 +4847,50 @@
         <v>180</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP17" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BQ17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU17" t="n">
         <v>7</v>
       </c>
-      <c r="BR17" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
         <v>2.28</v>
@@ -4933,37 +4933,37 @@
         <v>4.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P18" t="n">
         <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U18" t="n">
         <v>1.87</v>
@@ -4978,7 +4978,7 @@
         <v>23</v>
       </c>
       <c r="Y18" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
         <v>500</v>
@@ -5014,7 +5014,7 @@
         <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL18" t="n">
         <v>500</v>
@@ -5023,7 +5023,7 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
         <v>600</v>
@@ -5038,7 +5038,7 @@
         <v>6.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AT18" t="n">
         <v>4.2</v>
@@ -5047,10 +5047,10 @@
         <v>4.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX18" t="n">
         <v>6.2</v>
@@ -5062,16 +5062,16 @@
         <v>7.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BB18" t="n">
         <v>11.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE18" t="n">
         <v>95</v>
@@ -5086,7 +5086,7 @@
         <v>3.15</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
@@ -5110,41 +5110,41 @@
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -5184,10 +5184,10 @@
         <v>2.66</v>
       </c>
       <c r="I19" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
         <v>3.05</v>
@@ -5199,40 +5199,40 @@
         <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T19" t="n">
         <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
         <v>1.58</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="n">
         <v>15</v>
@@ -5241,10 +5241,10 @@
         <v>42</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD19" t="n">
         <v>13.5</v>
@@ -5256,10 +5256,10 @@
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
         <v>70</v>
@@ -5274,13 +5274,13 @@
         <v>80</v>
       </c>
       <c r="AM19" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
         <v>70</v>
       </c>
       <c r="AO19" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AP19" t="n">
         <v>8</v>
@@ -5289,13 +5289,13 @@
         <v>7.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
         <v>36</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU19" t="n">
         <v>6.4</v>
@@ -5304,10 +5304,10 @@
         <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY19" t="n">
         <v>14</v>
@@ -5316,13 +5316,13 @@
         <v>20</v>
       </c>
       <c r="BA19" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB19" t="n">
         <v>55</v>
       </c>
-      <c r="BB19" t="n">
-        <v>50</v>
-      </c>
       <c r="BC19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BD19" t="n">
         <v>60</v>
@@ -5334,19 +5334,19 @@
         <v>55</v>
       </c>
       <c r="BG19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH19" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="BJ19" t="n">
         <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5355,50 +5355,50 @@
         <v>170</v>
       </c>
       <c r="BN19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO19" t="n">
         <v>5.2</v>
       </c>
       <c r="BP19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR19" t="n">
         <v>55</v>
       </c>
       <c r="BS19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX19" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ19" t="n">
         <v>55</v>
       </c>
       <c r="CA19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -5429,25 +5429,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="G20" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H20" t="n">
         <v>2.98</v>
       </c>
       <c r="I20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J20" t="n">
         <v>3.15</v>
       </c>
-      <c r="J20" t="n">
-        <v>3.1</v>
-      </c>
       <c r="K20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
@@ -5459,16 +5459,16 @@
         <v>1.56</v>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T20" t="n">
         <v>2.14</v>
@@ -5477,19 +5477,19 @@
         <v>1.78</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
         <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
         <v>60</v>
@@ -5507,7 +5507,7 @@
         <v>46</v>
       </c>
       <c r="AF20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
         <v>13.5</v>
@@ -5519,7 +5519,7 @@
         <v>75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK20" t="n">
         <v>44</v>
@@ -5537,19 +5537,19 @@
         <v>60</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ20" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS20" t="n">
         <v>48</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU20" t="n">
         <v>6.6</v>
@@ -5558,7 +5558,7 @@
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AX20" t="n">
         <v>14.5</v>
@@ -5591,16 +5591,16 @@
         <v>48</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ20" t="n">
         <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5609,22 +5609,22 @@
         <v>170</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BP20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS20" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT20" t="n">
         <v>6.2</v>
@@ -5633,26 +5633,26 @@
         <v>4.5</v>
       </c>
       <c r="BV20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX20" t="n">
         <v>55</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ20" t="n">
         <v>55</v>
       </c>
       <c r="CA20" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -5689,13 +5689,13 @@
         <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
         <v>3.45</v>
@@ -5713,16 +5713,16 @@
         <v>1.53</v>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T21" t="n">
         <v>2.2</v>
@@ -5731,13 +5731,13 @@
         <v>1.73</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X21" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
@@ -5761,31 +5761,31 @@
         <v>80</v>
       </c>
       <c r="AF21" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI21" t="n">
         <v>110</v>
       </c>
       <c r="AJ21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK21" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL21" t="n">
         <v>65</v>
       </c>
       <c r="AM21" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO21" t="n">
         <v>130</v>
@@ -5800,7 +5800,7 @@
         <v>27</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
         <v>6.4</v>
@@ -5824,7 +5824,7 @@
         <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BB21" t="n">
         <v>22</v>
@@ -5836,13 +5836,13 @@
         <v>23</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
         <v>22</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BH21" t="n">
         <v>2.74</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G22" t="n">
         <v>1.87</v>
@@ -5946,13 +5946,13 @@
         <v>5.9</v>
       </c>
       <c r="I22" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
         <v>3.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.54</v>
@@ -5967,7 +5967,7 @@
         <v>1.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q22" t="n">
         <v>2.5</v>
@@ -5982,52 +5982,52 @@
         <v>2.24</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
         <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA22" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AB22" t="n">
         <v>7.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE22" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG22" t="n">
         <v>13.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI22" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK22" t="n">
         <v>30</v>
@@ -6036,13 +6036,13 @@
         <v>75</v>
       </c>
       <c r="AM22" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AP22" t="n">
         <v>6.8</v>
@@ -6051,10 +6051,10 @@
         <v>11</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT22" t="n">
         <v>4.7</v>
@@ -6063,13 +6063,13 @@
         <v>6</v>
       </c>
       <c r="AV22" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY22" t="n">
         <v>8</v>
@@ -6078,25 +6078,25 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BC22" t="n">
         <v>17.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF22" t="n">
         <v>14</v>
       </c>
       <c r="BG22" t="n">
-        <v>170</v>
+        <v>4.4</v>
       </c>
       <c r="BH22" t="n">
         <v>2.86</v>
@@ -6108,16 +6108,16 @@
         <v>13</v>
       </c>
       <c r="BK22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO22" t="n">
         <v>3.2</v>
@@ -6126,41 +6126,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
         <v>10</v>
       </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>27</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>48</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>60</v>
-      </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G23" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H23" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L23" t="n">
         <v>1.45</v>
@@ -6215,13 +6215,13 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q23" t="n">
         <v>2.1</v>
@@ -6233,22 +6233,22 @@
         <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
         <v>2.04</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y23" t="n">
         <v>14.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>14</v>
       </c>
       <c r="Z23" t="n">
         <v>29</v>
@@ -6257,19 +6257,19 @@
         <v>75</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
         <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE23" t="n">
         <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
         <v>13</v>
@@ -6278,7 +6278,7 @@
         <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ23" t="n">
         <v>34</v>
@@ -6290,7 +6290,7 @@
         <v>50</v>
       </c>
       <c r="AM23" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN23" t="n">
         <v>26</v>
@@ -6299,49 +6299,49 @@
         <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="AS23" t="n">
         <v>5.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW23" t="n">
         <v>5.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="BA23" t="n">
         <v>5.8</v>
       </c>
       <c r="BB23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC23" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC23" t="n">
-        <v>20</v>
-      </c>
       <c r="BD23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE23" t="n">
         <v>6</v>
@@ -6362,7 +6362,7 @@
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6374,13 +6374,13 @@
         <v>5.2</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP23" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR23" t="n">
         <v>36</v>
@@ -6392,7 +6392,7 @@
         <v>7</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G24" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H24" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I24" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J24" t="n">
         <v>3.5</v>
@@ -6481,7 +6481,7 @@
         <v>1.79</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -6490,7 +6490,7 @@
         <v>1.64</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V24" t="n">
         <v>1.54</v>
@@ -6508,7 +6508,7 @@
         <v>21</v>
       </c>
       <c r="AA24" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB24" t="n">
         <v>16</v>
@@ -6541,7 +6541,7 @@
         <v>34</v>
       </c>
       <c r="AL24" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
         <v>90</v>
@@ -6550,13 +6550,13 @@
         <v>21</v>
       </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
         <v>4.3</v>
@@ -6565,16 +6565,16 @@
         <v>4.9</v>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AV24" t="n">
         <v>4</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX24" t="n">
         <v>14</v>
@@ -6586,7 +6586,7 @@
         <v>4.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB24" t="n">
         <v>4.9</v>
@@ -6598,7 +6598,7 @@
         <v>4.9</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF24" t="n">
         <v>4.3</v>
@@ -6616,7 +6616,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK24" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
@@ -6625,10 +6625,10 @@
         <v>10</v>
       </c>
       <c r="BN24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
@@ -6652,13 +6652,13 @@
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G25" t="n">
         <v>1.61</v>
       </c>
       <c r="H25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I25" t="n">
         <v>7.2</v>
@@ -6714,7 +6714,7 @@
         <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.42</v>
@@ -6723,19 +6723,19 @@
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O25" t="n">
         <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="n">
         <v>2.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S25" t="n">
         <v>3.75</v>
@@ -6744,13 +6744,13 @@
         <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V25" t="n">
         <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X25" t="n">
         <v>17.5</v>
@@ -6759,10 +6759,10 @@
         <v>20</v>
       </c>
       <c r="Z25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA25" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB25" t="n">
         <v>8.199999999999999</v>
@@ -6774,7 +6774,7 @@
         <v>30</v>
       </c>
       <c r="AE25" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AF25" t="n">
         <v>8.800000000000001</v>
@@ -6783,7 +6783,7 @@
         <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI25" t="n">
         <v>120</v>
@@ -6795,19 +6795,19 @@
         <v>19</v>
       </c>
       <c r="AL25" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AM25" t="n">
         <v>200</v>
       </c>
       <c r="AN25" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP25" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>17</v>
@@ -6816,19 +6816,19 @@
         <v>7.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU25" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX25" t="n">
         <v>7.6</v>
@@ -6840,7 +6840,7 @@
         <v>6.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB25" t="n">
         <v>13.5</v>
@@ -6852,31 +6852,31 @@
         <v>15</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH25" t="n">
         <v>3.4</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ25" t="n">
         <v>11.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN25" t="n">
         <v>4</v>
@@ -6885,44 +6885,44 @@
         <v>3.6</v>
       </c>
       <c r="BP25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ25" t="n">
         <v>6.2</v>
       </c>
       <c r="BR25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT25" t="n">
         <v>10.5</v>
       </c>
       <c r="BU25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ25" t="n">
         <v>22</v>
       </c>
       <c r="CA25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -7007,31 +7007,31 @@
         <v>2.66</v>
       </c>
       <c r="X26" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z26" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AC26" t="n">
         <v>12</v>
       </c>
       <c r="AD26" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AE26" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AF26" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG26" t="n">
         <v>13.5</v>
@@ -7040,7 +7040,7 @@
         <v>48</v>
       </c>
       <c r="AI26" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AJ26" t="n">
         <v>16.5</v>
@@ -7055,64 +7055,64 @@
         <v>480</v>
       </c>
       <c r="AN26" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR26" t="n">
-        <v>65</v>
+        <v>5.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>30</v>
+        <v>5.9</v>
       </c>
       <c r="AW26" t="n">
-        <v>200</v>
+        <v>5.6</v>
       </c>
       <c r="AX26" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>28</v>
+        <v>5.8</v>
       </c>
       <c r="BA26" t="n">
-        <v>180</v>
+        <v>5.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC26" t="n">
-        <v>16</v>
+        <v>5.3</v>
       </c>
       <c r="BD26" t="n">
-        <v>50</v>
+        <v>5.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>270</v>
+        <v>5.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH26" t="n">
         <v>2.96</v>
@@ -7124,13 +7124,13 @@
         <v>15.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN26" t="n">
         <v>3.8</v>
@@ -7142,41 +7142,41 @@
         <v>11.5</v>
       </c>
       <c r="BQ26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>28</v>
       </c>
       <c r="BT26" t="n">
         <v>13.5</v>
       </c>
       <c r="BU26" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G27" t="n">
         <v>2.64</v>
@@ -7216,13 +7216,13 @@
         <v>2.76</v>
       </c>
       <c r="I27" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L27" t="n">
         <v>1.33</v>
@@ -7246,16 +7246,16 @@
         <v>1.54</v>
       </c>
       <c r="S27" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T27" t="n">
         <v>1.58</v>
       </c>
       <c r="U27" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V27" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W27" t="n">
         <v>1.6</v>
@@ -7264,19 +7264,19 @@
         <v>21</v>
       </c>
       <c r="Y27" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z27" t="n">
         <v>22</v>
       </c>
       <c r="AA27" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AB27" t="n">
         <v>15</v>
       </c>
       <c r="AC27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
         <v>13.5</v>
@@ -7285,25 +7285,25 @@
         <v>28</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH27" t="n">
         <v>14.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ27" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AK27" t="n">
         <v>26</v>
       </c>
       <c r="AL27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM27" t="n">
         <v>65</v>
@@ -7312,7 +7312,7 @@
         <v>16.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AP27" t="n">
         <v>17.5</v>
@@ -7324,7 +7324,7 @@
         <v>18.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT27" t="n">
         <v>12.5</v>
@@ -7342,7 +7342,7 @@
         <v>17.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ27" t="n">
         <v>13.5</v>
@@ -7351,19 +7351,19 @@
         <v>29</v>
       </c>
       <c r="BB27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC27" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE27" t="n">
         <v>24</v>
       </c>
       <c r="BF27" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG27" t="n">
         <v>16</v>
@@ -7378,59 +7378,59 @@
         <v>9</v>
       </c>
       <c r="BK27" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN27" t="n">
         <v>6.4</v>
       </c>
       <c r="BO27" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ27" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR27" t="n">
         <v>28</v>
       </c>
       <c r="BS27" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BT27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV27" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BW27" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="BX27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY27" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BZ27" t="n">
         <v>19</v>
       </c>
       <c r="CA27" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -7467,88 +7467,88 @@
         <v>3.05</v>
       </c>
       <c r="H28" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I28" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P28" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U28" t="n">
         <v>1.9</v>
       </c>
       <c r="V28" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W28" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y28" t="n">
         <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AA28" t="n">
         <v>55</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF28" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG28" t="n">
         <v>15</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ28" t="n">
         <v>55</v>
@@ -7566,19 +7566,19 @@
         <v>46</v>
       </c>
       <c r="AO28" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT28" t="n">
         <v>8.199999999999999</v>
@@ -7590,49 +7590,49 @@
         <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BJ28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7641,10 +7641,10 @@
         <v>10</v>
       </c>
       <c r="BN28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO28" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
@@ -7659,7 +7659,7 @@
         <v>8.6</v>
       </c>
       <c r="BT28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU28" t="n">
         <v>4.5</v>
@@ -7668,7 +7668,7 @@
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
